--- a/docs/itineraries/vaishno-devi-kashmir-8d-plan.xlsx
+++ b/docs/itineraries/vaishno-devi-kashmir-8d-plan.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1056" uniqueCount="601">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1056" uniqueCount="602">
   <si>
     <t xml:space="preserve">8 Days Vaishno Devi &amp; Kashmir Pilgrimage – Overview</t>
   </si>
@@ -130,7 +130,7 @@
     <t xml:space="preserve">Days 1–3 are identical to the 4-day Vaishno Devi package; 4-day yatris leave the group at Jammu Airport on Day 4 morning.</t>
   </si>
   <si>
-    <t xml:space="preserve">Assumptions: arrival at Jammu by 13:00 on Day 1; helicopter slots 10:30 (Day 2) and 11:00 (Day 3); Jammu → Srinagar flight ~11:00 Day 4; Srinagar departure after 17:30 Day 8; Kashmir hotels on MAP (breakfast + dinner). Day 6 is the longest road day (~212 km); start by 07:45 after the 07:15 parana breakfast.</t>
+    <t xml:space="preserve">Assumptions: arrival at Jammu by 14:00 on Day 1; helicopter slots 10:30 (Day 2) and 11:00 (Day 3); Jammu → Srinagar flight ~11:00 Day 4; Srinagar departure after 17:30 Day 8; Kashmir hotels on MAP (breakfast + dinner). Day 6 is the longest road day (~212 km); start by 07:45 after the 07:15 parana breakfast.</t>
   </si>
   <si>
     <t xml:space="preserve">8 Days Vaishno Devi &amp; Kashmir Pilgrimage – Minute-to-Minute Plan</t>
@@ -169,7 +169,7 @@
     <t xml:space="preserve">On own – at home / origin airport / in flight</t>
   </si>
   <si>
-    <t xml:space="preserve">Breakfast on own before or during travel to Jammu (not included)</t>
+    <t xml:space="preserve">Breakfast on own before or during travel to Jammu (not included); carry a light snack, lunch is at 15:15</t>
   </si>
   <si>
     <t xml:space="preserve">Arrival</t>
@@ -211,7 +211,7 @@
     <t xml:space="preserve">Hotel restaurant, Jammu</t>
   </si>
   <si>
-    <t xml:space="preserve">Lunch – at the hotel, pre-ordered pure-veg thali so we leave on time; group pays</t>
+    <t xml:space="preserve">Late lunch – at the hotel, pre-ordered pure-veg thali served on arrival; group pays</t>
   </si>
   <si>
     <t xml:space="preserve">Raghunath Temple</t>
@@ -799,7 +799,7 @@
     <t xml:space="preserve">Not included</t>
   </si>
   <si>
-    <t xml:space="preserve">14:20–15:00</t>
+    <t xml:space="preserve">15:15–15:50</t>
   </si>
   <si>
     <t xml:space="preserve">Hotel, pre-ordered thali</t>
@@ -808,36 +808,39 @@
     <t xml:space="preserve">Group pays</t>
   </si>
   <si>
+    <t xml:space="preserve">20:15–21:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotel, pre-ordered menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06:30–07:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complimentary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:15–13:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shrine Board (SMVDSB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pay at counter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:30–20:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07:00–07:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotel / restaurant</t>
+  </si>
+  <si>
     <t xml:space="preserve">20:00–21:00</t>
   </si>
   <si>
-    <t xml:space="preserve">Hotel, pre-ordered menu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06:30–07:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Complimentary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12:15–13:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shrine Board (SMVDSB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pay at counter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:30–20:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07:00–07:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hotel / restaurant</t>
-  </si>
-  <si>
     <t xml:space="preserve">07:00–07:45</t>
   </si>
   <si>
@@ -1282,7 +1285,7 @@
     <t xml:space="preserve">T−45 days</t>
   </si>
   <si>
-    <t xml:space="preserve">Book flights: home → Jammu (Day 1, arriving by 13:00), Jammu → Srinagar (Day 4 morning), Srinagar → home (Day 8, after 17:30)</t>
+    <t xml:space="preserve">Book flights: home → Jammu (Day 1, arriving by 14:00), Jammu → Srinagar (Day 4 morning), Srinagar → home (Day 8, after 17:30)</t>
   </si>
   <si>
     <t xml:space="preserve">Travel desk</t>
@@ -1798,7 +1801,7 @@
     <t xml:space="preserve">Point to confirm</t>
   </si>
   <si>
-    <t xml:space="preserve">Every yatri's arrival in Jammu by 13:00 on Day 1 and departure flight from Srinagar on Day 8</t>
+    <t xml:space="preserve">Every yatri's arrival in Jammu by 14:00 on Day 1 and departure flight from Srinagar on Day 8</t>
   </si>
   <si>
     <t xml:space="preserve">Jammu → Srinagar flight time on Day 4 (the day plan assumes about 11:00)</t>
@@ -2501,7 +2504,7 @@
       </c>
       <c r="G5" s="9" t="n">
         <f aca="false">_xlfn.MAXIFS('Minute-by-Minute'!$D$5:$D$117,'Minute-by-Minute'!$A$5:$A$117,A5)</f>
-        <v>0.875</v>
+        <v>0.885416666666667</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2752,100 +2755,100 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
   </sheetData>
@@ -2875,91 +2878,91 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C2" s="23"/>
       <c r="D2" s="23"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C3" s="23"/>
       <c r="D3" s="23"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C4" s="23"/>
       <c r="D4" s="23"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C5" s="23"/>
       <c r="D5" s="23"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C6" s="23"/>
       <c r="D6" s="23"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C7" s="23"/>
       <c r="D7" s="23"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C8" s="23"/>
       <c r="D8" s="23"/>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B9" s="14"/>
       <c r="C9" s="23"/>
@@ -2967,7 +2970,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B10" s="14"/>
       <c r="C10" s="23"/>
@@ -2975,17 +2978,17 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C11" s="23"/>
       <c r="D11" s="23"/>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B12" s="14"/>
       <c r="C12" s="23"/>
@@ -2993,24 +2996,24 @@
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C13" s="23"/>
       <c r="D13" s="23"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C14" s="14"/>
       <c r="D14" s="14" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
   </sheetData>
@@ -3040,259 +3043,259 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D5" s="24"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D6" s="24"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
+        <v>554</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>555</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>553</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>554</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>552</v>
       </c>
       <c r="D7" s="24"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D8" s="24"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D9" s="24"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D10" s="24"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D11" s="24"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D12" s="24"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D13" s="24"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D14" s="24"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D15" s="24"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D16" s="24"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D17" s="24"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D18" s="24"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D19" s="24"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D20" s="24"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D21" s="24"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D22" s="24"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D23" s="24"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D24" s="25" t="n">
         <f aca="false">SUMIF(C5:C23,"Yes",D5:D23)</f>
@@ -3301,10 +3304,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D25" s="26" t="n">
         <v>0.05</v>
@@ -3312,7 +3315,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D26" s="25" t="n">
         <f aca="false">D24*(1+D25)</f>
@@ -3321,7 +3324,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
   </sheetData>
@@ -3349,93 +3352,93 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B2" s="23"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B3" s="23"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B4" s="23"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B5" s="23"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B6" s="23"/>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B7" s="23"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B8" s="23"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B9" s="23"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B10" s="23"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B11" s="23"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B12" s="23"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B13" s="23"/>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B14" s="23"/>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B15" s="23"/>
     </row>
@@ -3555,10 +3558,10 @@
         <v>46459</v>
       </c>
       <c r="C6" s="16" t="n">
-        <v>0.541666666666667</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>0.5625</v>
+        <v>0.604166666666667</v>
       </c>
       <c r="E6" s="14" t="n">
         <f aca="false">ROUND((D6-C6)*1440,0)</f>
@@ -3588,10 +3591,10 @@
         <v>46459</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>0.5625</v>
+        <v>0.604166666666667</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>0.576388888888889</v>
+        <v>0.618055555555556</v>
       </c>
       <c r="E7" s="14" t="n">
         <f aca="false">ROUND((D7-C7)*1440,0)</f>
@@ -3625,14 +3628,14 @@
         <v>46459</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>0.576388888888889</v>
+        <v>0.618055555555556</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>0.597222222222222</v>
+        <v>0.635416666666667</v>
       </c>
       <c r="E8" s="14" t="n">
         <f aca="false">ROUND((D8-C8)*1440,0)</f>
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F8" s="14" t="s">
         <v>53</v>
@@ -3658,14 +3661,14 @@
         <v>46459</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>0.597222222222222</v>
+        <v>0.635416666666667</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>0.625</v>
+        <v>0.659722222222222</v>
       </c>
       <c r="E9" s="11" t="n">
         <f aca="false">ROUND((D9-C9)*1440,0)</f>
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F9" s="11" t="s">
         <v>56</v>
@@ -3691,10 +3694,10 @@
         <v>46459</v>
       </c>
       <c r="C10" s="16" t="n">
-        <v>0.625</v>
+        <v>0.659722222222222</v>
       </c>
       <c r="D10" s="16" t="n">
-        <v>0.635416666666667</v>
+        <v>0.670138888888889</v>
       </c>
       <c r="E10" s="14" t="n">
         <f aca="false">ROUND((D10-C10)*1440,0)</f>
@@ -3728,14 +3731,14 @@
         <v>46459</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>0.635416666666667</v>
+        <v>0.670138888888889</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>0.666666666666667</v>
+        <v>0.697916666666667</v>
       </c>
       <c r="E11" s="14" t="n">
         <f aca="false">ROUND((D11-C11)*1440,0)</f>
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F11" s="14" t="s">
         <v>61</v>
@@ -3761,10 +3764,10 @@
         <v>46459</v>
       </c>
       <c r="C12" s="16" t="n">
-        <v>0.666666666666667</v>
+        <v>0.697916666666667</v>
       </c>
       <c r="D12" s="16" t="n">
-        <v>0.673611111111111</v>
+        <v>0.704861111111111</v>
       </c>
       <c r="E12" s="14" t="n">
         <f aca="false">ROUND((D12-C12)*1440,0)</f>
@@ -3798,14 +3801,14 @@
         <v>46459</v>
       </c>
       <c r="C13" s="16" t="n">
-        <v>0.673611111111111</v>
+        <v>0.704861111111111</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>0.694444444444444</v>
+        <v>0.722222222222222</v>
       </c>
       <c r="E13" s="14" t="n">
         <f aca="false">ROUND((D13-C13)*1440,0)</f>
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F13" s="14" t="s">
         <v>61</v>
@@ -3831,10 +3834,10 @@
         <v>46459</v>
       </c>
       <c r="C14" s="16" t="n">
-        <v>0.694444444444444</v>
+        <v>0.722222222222222</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.708333333333333</v>
+        <v>0.736111111111111</v>
       </c>
       <c r="E14" s="14" t="n">
         <f aca="false">ROUND((D14-C14)*1440,0)</f>
@@ -3868,14 +3871,14 @@
         <v>46459</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>0.708333333333333</v>
+        <v>0.736111111111111</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>0.75</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="E15" s="14" t="n">
         <f aca="false">ROUND((D15-C15)*1440,0)</f>
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F15" s="14" t="s">
         <v>61</v>
@@ -3901,10 +3904,10 @@
         <v>46459</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>0.75</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>0.767361111111111</v>
+        <v>0.788194444444444</v>
       </c>
       <c r="E16" s="14" t="n">
         <f aca="false">ROUND((D16-C16)*1440,0)</f>
@@ -3938,10 +3941,10 @@
         <v>46459</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>0.767361111111111</v>
+        <v>0.788194444444444</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>0.791666666666667</v>
+        <v>0.8125</v>
       </c>
       <c r="E17" s="14" t="n">
         <f aca="false">ROUND((D17-C17)*1440,0)</f>
@@ -3971,10 +3974,10 @@
         <v>46459</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>0.791666666666667</v>
+        <v>0.8125</v>
       </c>
       <c r="D18" s="16" t="n">
-        <v>0.805555555555556</v>
+        <v>0.826388888888889</v>
       </c>
       <c r="E18" s="14" t="n">
         <f aca="false">ROUND((D18-C18)*1440,0)</f>
@@ -4008,14 +4011,14 @@
         <v>46459</v>
       </c>
       <c r="C19" s="16" t="n">
-        <v>0.805555555555556</v>
+        <v>0.826388888888889</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>0.833333333333333</v>
+        <v>0.84375</v>
       </c>
       <c r="E19" s="14" t="n">
         <f aca="false">ROUND((D19-C19)*1440,0)</f>
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="F19" s="14" t="s">
         <v>53</v>
@@ -4041,10 +4044,10 @@
         <v>46459</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>0.833333333333333</v>
+        <v>0.84375</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>0.875</v>
+        <v>0.885416666666667</v>
       </c>
       <c r="E20" s="11" t="n">
         <f aca="false">ROUND((D20-C20)*1440,0)</f>
@@ -7713,7 +7716,7 @@
         <v>76</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="D12" s="14" t="s">
         <v>137</v>
@@ -7733,7 +7736,7 @@
         <v>42</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D13" s="14" t="s">
         <v>137</v>
@@ -7753,7 +7756,7 @@
         <v>56</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>149</v>
@@ -7773,16 +7776,16 @@
         <v>76</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7793,16 +7796,16 @@
         <v>42</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D16" s="14" t="s">
         <v>162</v>
       </c>
       <c r="E16" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="F16" s="14" t="s">
         <v>272</v>
-      </c>
-      <c r="F16" s="14" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7813,13 +7816,13 @@
         <v>56</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D17" s="14" t="s">
         <v>167</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F17" s="14" t="s">
         <v>256</v>
@@ -7833,16 +7836,16 @@
         <v>76</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="D18" s="14" t="s">
         <v>169</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7853,16 +7856,16 @@
         <v>42</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D19" s="14" t="s">
         <v>169</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7873,13 +7876,13 @@
         <v>56</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D20" s="14" t="s">
         <v>193</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F20" s="14" t="s">
         <v>256</v>
@@ -7893,16 +7896,16 @@
         <v>76</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="D21" s="14" t="s">
         <v>162</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7913,16 +7916,16 @@
         <v>42</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D22" s="14" t="s">
         <v>162</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7933,7 +7936,7 @@
         <v>56</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D23" s="14" t="s">
         <v>211</v>
@@ -7953,16 +7956,16 @@
         <v>76</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="D24" s="14" t="s">
         <v>209</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7973,16 +7976,16 @@
         <v>42</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D25" s="14" t="s">
         <v>209</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7993,13 +7996,13 @@
         <v>56</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D26" s="14" t="s">
         <v>235</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F26" s="14" t="s">
         <v>256</v>
@@ -8007,7 +8010,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>
@@ -8036,112 +8039,112 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -8171,198 +8174,198 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
   </sheetData>
@@ -8390,207 +8393,207 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="14" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="14" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
   </sheetData>
@@ -8621,231 +8624,231 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E4" s="23"/>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E5" s="23"/>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E6" s="23"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E7" s="23"/>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E8" s="23"/>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E9" s="23"/>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E10" s="23"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E11" s="23"/>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E12" s="23"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E13" s="23"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E14" s="23"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D15" s="14"/>
       <c r="E15" s="23"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E16" s="23"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E17" s="23"/>
     </row>
@@ -8874,146 +8877,146 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
   </sheetData>
@@ -9041,34 +9044,34 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9076,55 +9079,55 @@
         <v>89</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
   </sheetData>

--- a/docs/itineraries/vaishno-devi-kashmir-8d-plan.xlsx
+++ b/docs/itineraries/vaishno-devi-kashmir-8d-plan.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1056" uniqueCount="602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="612">
   <si>
     <t xml:space="preserve">8 Days Vaishno Devi &amp; Kashmir Pilgrimage – Overview</t>
   </si>
@@ -49,6 +49,9 @@
     <t xml:space="preserve">← change this date and every day / row date updates</t>
   </si>
   <si>
+    <t xml:space="preserve">Key dates</t>
+  </si>
+  <si>
     <t xml:space="preserve">Day</t>
   </si>
   <si>
@@ -70,18 +73,27 @@
     <t xml:space="preserve">Last end</t>
   </si>
   <si>
+    <t xml:space="preserve">Registrations close</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jammu arrival, Jammu temples</t>
   </si>
   <si>
     <t xml:space="preserve">Jammu</t>
   </si>
   <si>
+    <t xml:space="preserve">Yatri data to travel agent</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jammu → Katra → Sanjichhat (helicopter) → Bhawan</t>
   </si>
   <si>
     <t xml:space="preserve">Bhawan</t>
   </si>
   <si>
+    <t xml:space="preserve">Helicopter tickets booked</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bhawan → Bhairon → Sanjichhat (helicopter) → Katra</t>
   </si>
   <si>
@@ -1261,21 +1273,39 @@
     <t xml:space="preserve">Check the yatra calendar in the app</t>
   </si>
   <si>
-    <t xml:space="preserve">Collect yatri names, photo ID, age, phone, emergency contact, medical notes; mark who does 4 days and who does 8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name exactly as on ID</t>
+    <t xml:space="preserve">By 25 Dec 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registrations close: collect yatri names, photo ID (Aadhaar / passport), age, weight, phone, emergency contact, medical notes; mark who does 4 days and who does 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Last date 25 Dec 2026; name exactly as on ID; weight needed for the helicopter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 Dec 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Send complete yatri data to the travel agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Names as on ID, ID numbers, ages, weights, phone numbers; who does 4 days and who does 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Jan 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Book helicopter Day 2 (Katra → Sanjichhat) and Day 3 (Sanjichhat → Katra) on the SMVDSB portal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travel agent with yatra coordinator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All yatris together</t>
   </si>
   <si>
     <t xml:space="preserve">Booking opening day</t>
   </si>
   <si>
-    <t xml:space="preserve">Book helicopter Day 2 (Katra → Sanjichhat) and Day 3 (Sanjichhat → Katra) on the SMVDSB portal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All yatris together</t>
-  </si>
-  <si>
     <t xml:space="preserve">Book Bhawan accommodation (Day 2 night), Atka Aarti passes, Bhairon ropeway</t>
   </si>
   <si>
@@ -1807,7 +1837,7 @@
     <t xml:space="preserve">Jammu → Srinagar flight time on Day 4 (the day plan assumes about 11:00)</t>
   </si>
   <si>
-    <t xml:space="preserve">Helicopter slots booked for Day 2 and Day 3, and the reporting time on the tickets</t>
+    <t xml:space="preserve">Helicopter slots booked on 1 Jan 2027 for Day 2 and Day 3, and the reporting time on the tickets</t>
   </si>
   <si>
     <t xml:space="preserve">Helicopter baggage limit; where main luggage waits on Day 2</t>
@@ -2425,7 +2455,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
@@ -2434,6 +2464,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="17"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2456,28 +2488,37 @@
       <c r="C3" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="I3" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4" s="8" t="n">
+        <v>46381</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2489,14 +2530,14 @@
         <v>46459</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D5" s="7" t="n">
         <f aca="false">SUMIF('Minute-by-Minute'!$A$5:$A$117,A5,'Minute-by-Minute'!$I$5:$I$117)</f>
         <v>32</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F5" s="9" t="n">
         <f aca="false">_xlfn.MINIFS('Minute-by-Minute'!$C$5:$C$117,'Minute-by-Minute'!$A$5:$A$117,A5)</f>
@@ -2506,6 +2547,12 @@
         <f aca="false">_xlfn.MAXIFS('Minute-by-Minute'!$D$5:$D$117,'Minute-by-Minute'!$A$5:$A$117,A5)</f>
         <v>0.885416666666667</v>
       </c>
+      <c r="I5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="8" t="n">
+        <v>46386</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="n">
@@ -2516,14 +2563,14 @@
         <v>46460</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D6" s="7" t="n">
         <f aca="false">SUMIF('Minute-by-Minute'!$A$5:$A$117,A6,'Minute-by-Minute'!$I$5:$I$117)</f>
         <v>52</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F6" s="9" t="n">
         <f aca="false">_xlfn.MINIFS('Minute-by-Minute'!$C$5:$C$117,'Minute-by-Minute'!$A$5:$A$117,A6)</f>
@@ -2533,6 +2580,12 @@
         <f aca="false">_xlfn.MAXIFS('Minute-by-Minute'!$D$5:$D$117,'Minute-by-Minute'!$A$5:$A$117,A6)</f>
         <v>0.854166666666667</v>
       </c>
+      <c r="I6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" s="8" t="n">
+        <v>46388</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="n">
@@ -2543,14 +2596,14 @@
         <v>46461</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D7" s="7" t="n">
         <f aca="false">SUMIF('Minute-by-Minute'!$A$5:$A$117,A7,'Minute-by-Minute'!$I$5:$I$117)</f>
         <v>9</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F7" s="9" t="n">
         <f aca="false">_xlfn.MINIFS('Minute-by-Minute'!$C$5:$C$117,'Minute-by-Minute'!$A$5:$A$117,A7)</f>
@@ -2570,14 +2623,14 @@
         <v>46462</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D8" s="7" t="n">
         <f aca="false">SUMIF('Minute-by-Minute'!$A$5:$A$117,A8,'Minute-by-Minute'!$I$5:$I$117)</f>
         <v>64</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F8" s="9" t="n">
         <f aca="false">_xlfn.MINIFS('Minute-by-Minute'!$C$5:$C$117,'Minute-by-Minute'!$A$5:$A$117,A8)</f>
@@ -2597,14 +2650,14 @@
         <v>46463</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D9" s="7" t="n">
         <f aca="false">SUMIF('Minute-by-Minute'!$A$5:$A$117,A9,'Minute-by-Minute'!$I$5:$I$117)</f>
         <v>52</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F9" s="9" t="n">
         <f aca="false">_xlfn.MINIFS('Minute-by-Minute'!$C$5:$C$117,'Minute-by-Minute'!$A$5:$A$117,A9)</f>
@@ -2624,14 +2677,14 @@
         <v>46464</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D10" s="7" t="n">
         <f aca="false">SUMIF('Minute-by-Minute'!$A$5:$A$117,A10,'Minute-by-Minute'!$I$5:$I$117)</f>
         <v>212</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F10" s="9" t="n">
         <f aca="false">_xlfn.MINIFS('Minute-by-Minute'!$C$5:$C$117,'Minute-by-Minute'!$A$5:$A$117,A10)</f>
@@ -2651,14 +2704,14 @@
         <v>46465</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D11" s="7" t="n">
         <f aca="false">SUMIF('Minute-by-Minute'!$A$5:$A$117,A11,'Minute-by-Minute'!$I$5:$I$117)</f>
         <v>105</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F11" s="9" t="n">
         <f aca="false">_xlfn.MINIFS('Minute-by-Minute'!$C$5:$C$117,'Minute-by-Minute'!$A$5:$A$117,A11)</f>
@@ -2678,14 +2731,14 @@
         <v>46466</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D12" s="7" t="n">
         <f aca="false">SUMIF('Minute-by-Minute'!$A$5:$A$117,A12,'Minute-by-Minute'!$I$5:$I$117)</f>
         <v>115</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F12" s="9" t="n">
         <f aca="false">_xlfn.MINIFS('Minute-by-Minute'!$C$5:$C$117,'Minute-by-Minute'!$A$5:$A$117,A12)</f>
@@ -2698,34 +2751,34 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D13" s="3" t="n">
         <f aca="false">SUM(D5:D12)</f>
         <v>641</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -2755,100 +2808,100 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>491</v>
+        <v>501</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>494</v>
+        <v>504</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>496</v>
+        <v>506</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>498</v>
+        <v>508</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>499</v>
+        <v>509</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>500</v>
+        <v>510</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>501</v>
+        <v>511</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>502</v>
+        <v>512</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>503</v>
+        <v>513</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>504</v>
+        <v>514</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>505</v>
+        <v>515</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>506</v>
+        <v>516</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>507</v>
+        <v>517</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>508</v>
+        <v>518</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>511</v>
+        <v>521</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>512</v>
+        <v>522</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>513</v>
+        <v>523</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>514</v>
+        <v>524</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>515</v>
+        <v>525</v>
       </c>
     </row>
   </sheetData>
@@ -2878,91 +2931,91 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>516</v>
+        <v>526</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>517</v>
+        <v>527</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>519</v>
+        <v>529</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>520</v>
+        <v>530</v>
       </c>
       <c r="C2" s="23"/>
       <c r="D2" s="23"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>521</v>
+        <v>531</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="C3" s="23"/>
       <c r="D3" s="23"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>523</v>
+        <v>533</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>524</v>
+        <v>534</v>
       </c>
       <c r="C4" s="23"/>
       <c r="D4" s="23"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>525</v>
+        <v>535</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="C5" s="23"/>
       <c r="D5" s="23"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>528</v>
+        <v>538</v>
       </c>
       <c r="C6" s="23"/>
       <c r="D6" s="23"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>529</v>
+        <v>539</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>530</v>
+        <v>540</v>
       </c>
       <c r="C7" s="23"/>
       <c r="D7" s="23"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>531</v>
+        <v>541</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>532</v>
+        <v>542</v>
       </c>
       <c r="C8" s="23"/>
       <c r="D8" s="23"/>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>533</v>
+        <v>543</v>
       </c>
       <c r="B9" s="14"/>
       <c r="C9" s="23"/>
@@ -2970,7 +3023,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>534</v>
+        <v>544</v>
       </c>
       <c r="B10" s="14"/>
       <c r="C10" s="23"/>
@@ -2978,17 +3031,17 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>535</v>
+        <v>545</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>536</v>
+        <v>546</v>
       </c>
       <c r="C11" s="23"/>
       <c r="D11" s="23"/>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>537</v>
+        <v>547</v>
       </c>
       <c r="B12" s="14"/>
       <c r="C12" s="23"/>
@@ -2996,24 +3049,24 @@
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>538</v>
+        <v>548</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>539</v>
+        <v>549</v>
       </c>
       <c r="C13" s="23"/>
       <c r="D13" s="23"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>541</v>
+        <v>551</v>
       </c>
       <c r="C14" s="14"/>
       <c r="D14" s="14" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
     </row>
   </sheetData>
@@ -3043,259 +3096,259 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>543</v>
+        <v>553</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>544</v>
+        <v>554</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>545</v>
+        <v>555</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>546</v>
+        <v>556</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>547</v>
+        <v>557</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>548</v>
+        <v>558</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>549</v>
+        <v>559</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>550</v>
+        <v>560</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>551</v>
+        <v>561</v>
       </c>
       <c r="D5" s="24"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>552</v>
+        <v>562</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>550</v>
+        <v>560</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>553</v>
+        <v>563</v>
       </c>
       <c r="D6" s="24"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>554</v>
+        <v>564</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>555</v>
+        <v>565</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>553</v>
+        <v>563</v>
       </c>
       <c r="D7" s="24"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>556</v>
+        <v>566</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>557</v>
+        <v>567</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>553</v>
+        <v>563</v>
       </c>
       <c r="D8" s="24"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>558</v>
+        <v>568</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>555</v>
+        <v>565</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>553</v>
+        <v>563</v>
       </c>
       <c r="D9" s="24"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>559</v>
+        <v>569</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>555</v>
+        <v>565</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>553</v>
+        <v>563</v>
       </c>
       <c r="D10" s="24"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>560</v>
+        <v>570</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>555</v>
+        <v>565</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>553</v>
+        <v>563</v>
       </c>
       <c r="D11" s="24"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>561</v>
+        <v>571</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>555</v>
+        <v>565</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>553</v>
+        <v>563</v>
       </c>
       <c r="D12" s="24"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>562</v>
+        <v>572</v>
       </c>
       <c r="B13" s="7" t="s">
+        <v>573</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>563</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>553</v>
       </c>
       <c r="D13" s="24"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>564</v>
+        <v>574</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>550</v>
+        <v>560</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>553</v>
+        <v>563</v>
       </c>
       <c r="D14" s="24"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>565</v>
+        <v>575</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>566</v>
+        <v>576</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>553</v>
+        <v>563</v>
       </c>
       <c r="D15" s="24"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>567</v>
+        <v>577</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>568</v>
+        <v>578</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>553</v>
+        <v>563</v>
       </c>
       <c r="D16" s="24"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>569</v>
+        <v>579</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>570</v>
+        <v>580</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>553</v>
+        <v>563</v>
       </c>
       <c r="D17" s="24"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>571</v>
+        <v>581</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>553</v>
+        <v>563</v>
       </c>
       <c r="D18" s="24"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>573</v>
+        <v>583</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>550</v>
+        <v>560</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="D19" s="24"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>575</v>
+        <v>585</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>576</v>
+        <v>586</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>577</v>
+        <v>587</v>
       </c>
       <c r="D20" s="24"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>578</v>
+        <v>588</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>550</v>
+        <v>560</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>553</v>
+        <v>563</v>
       </c>
       <c r="D21" s="24"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>550</v>
+        <v>560</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>553</v>
+        <v>563</v>
       </c>
       <c r="D22" s="24"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>580</v>
+        <v>590</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>581</v>
+        <v>591</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>553</v>
+        <v>563</v>
       </c>
       <c r="D23" s="24"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>582</v>
+        <v>592</v>
       </c>
       <c r="D24" s="25" t="n">
         <f aca="false">SUMIF(C5:C23,"Yes",D5:D23)</f>
@@ -3304,10 +3357,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>583</v>
+        <v>593</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>584</v>
+        <v>594</v>
       </c>
       <c r="D25" s="26" t="n">
         <v>0.05</v>
@@ -3315,7 +3368,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>585</v>
+        <v>595</v>
       </c>
       <c r="D26" s="25" t="n">
         <f aca="false">D24*(1+D25)</f>
@@ -3324,7 +3377,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>586</v>
+        <v>596</v>
       </c>
     </row>
   </sheetData>
@@ -3352,93 +3405,93 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>587</v>
+        <v>597</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>588</v>
+        <v>598</v>
       </c>
       <c r="B2" s="23"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>589</v>
+        <v>599</v>
       </c>
       <c r="B3" s="23"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>590</v>
+        <v>600</v>
       </c>
       <c r="B4" s="23"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>591</v>
+        <v>601</v>
       </c>
       <c r="B5" s="23"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>592</v>
+        <v>602</v>
       </c>
       <c r="B6" s="23"/>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>593</v>
+        <v>603</v>
       </c>
       <c r="B7" s="23"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>594</v>
+        <v>604</v>
       </c>
       <c r="B8" s="23"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>595</v>
+        <v>605</v>
       </c>
       <c r="B9" s="23"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>596</v>
+        <v>606</v>
       </c>
       <c r="B10" s="23"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>597</v>
+        <v>607</v>
       </c>
       <c r="B11" s="23"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>598</v>
+        <v>608</v>
       </c>
       <c r="B12" s="23"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>599</v>
+        <v>609</v>
       </c>
       <c r="B13" s="23"/>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>600</v>
+        <v>610</v>
       </c>
       <c r="B14" s="23"/>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>601</v>
+        <v>611</v>
       </c>
       <c r="B15" s="23"/>
     </row>
@@ -3475,47 +3528,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3537,15 +3590,15 @@
         <v>30</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H5" s="11"/>
       <c r="I5" s="11"/>
       <c r="J5" s="11" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="K5" s="11"/>
     </row>
@@ -3568,18 +3621,18 @@
         <v>30</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H6" s="14"/>
       <c r="I6" s="14"/>
       <c r="J6" s="14" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="K6" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3601,22 +3654,22 @@
         <v>20</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="I7" s="14" t="n">
         <v>7</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K7" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3638,18 +3691,18 @@
         <v>25</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H8" s="14"/>
       <c r="I8" s="14"/>
       <c r="J8" s="14" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K8" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3671,18 +3724,18 @@
         <v>35</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H9" s="11"/>
       <c r="I9" s="11"/>
       <c r="J9" s="11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K9" s="18" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3704,22 +3757,22 @@
         <v>15</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="I10" s="14" t="n">
         <v>5</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="K10" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3741,18 +3794,18 @@
         <v>40</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H11" s="14"/>
       <c r="I11" s="14"/>
       <c r="J11" s="14" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K11" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3774,22 +3827,22 @@
         <v>10</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="I12" s="14" t="n">
         <v>1</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K12" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3811,18 +3864,18 @@
         <v>25</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="H13" s="14"/>
       <c r="I13" s="14"/>
       <c r="J13" s="14" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="K13" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3844,22 +3897,22 @@
         <v>20</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="I14" s="14" t="n">
         <v>6</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3881,18 +3934,18 @@
         <v>50</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H15" s="14"/>
       <c r="I15" s="14"/>
       <c r="J15" s="14" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="K15" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3914,22 +3967,22 @@
         <v>25</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="I16" s="14" t="n">
         <v>7</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="K16" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3951,18 +4004,18 @@
         <v>35</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="H17" s="14"/>
       <c r="I17" s="14"/>
       <c r="J17" s="14" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="K17" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3984,22 +4037,22 @@
         <v>20</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="H18" s="14" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I18" s="14" t="n">
         <v>6</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="K18" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4021,18 +4074,18 @@
         <v>25</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H19" s="14"/>
       <c r="I19" s="14"/>
       <c r="J19" s="14" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K19" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4054,18 +4107,18 @@
         <v>60</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H20" s="11"/>
       <c r="I20" s="11"/>
       <c r="J20" s="11" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="K20" s="18" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4087,18 +4140,18 @@
         <v>30</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H21" s="11"/>
       <c r="I21" s="11"/>
       <c r="J21" s="11" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="K21" s="18" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4120,18 +4173,18 @@
         <v>15</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H22" s="14"/>
       <c r="I22" s="14"/>
       <c r="J22" s="14" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K22" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4153,22 +4206,22 @@
         <v>90</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I23" s="14" t="n">
         <v>50</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="K23" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4190,18 +4243,18 @@
         <v>30</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H24" s="14"/>
       <c r="I24" s="14"/>
       <c r="J24" s="14" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="K24" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4223,22 +4276,22 @@
         <v>10</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="H25" s="14" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I25" s="14" t="n">
         <v>2</v>
       </c>
       <c r="J25" s="14" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="K25" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4260,18 +4313,18 @@
         <v>65</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H26" s="14"/>
       <c r="I26" s="14"/>
       <c r="J26" s="14" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K26" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4293,20 +4346,20 @@
         <v>10</v>
       </c>
       <c r="F27" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="G27" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="G27" s="19" t="s">
-        <v>85</v>
-      </c>
       <c r="H27" s="19" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="I27" s="19"/>
       <c r="J27" s="19" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="K27" s="22" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4328,20 +4381,20 @@
         <v>65</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="H28" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I28" s="14"/>
       <c r="J28" s="14" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="K28" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4363,18 +4416,18 @@
         <v>30</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G29" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H29" s="14"/>
       <c r="I29" s="14"/>
       <c r="J29" s="14" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="K29" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4396,18 +4449,18 @@
         <v>45</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="H30" s="11"/>
       <c r="I30" s="11"/>
       <c r="J30" s="11" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="K30" s="18" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4429,18 +4482,18 @@
         <v>210</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G31" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H31" s="14"/>
       <c r="I31" s="14"/>
       <c r="J31" s="14" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="K31" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4462,18 +4515,18 @@
         <v>90</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H32" s="14"/>
       <c r="I32" s="14"/>
       <c r="J32" s="14" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="K32" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4495,18 +4548,18 @@
         <v>90</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G33" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H33" s="14"/>
       <c r="I33" s="14"/>
       <c r="J33" s="14" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="K33" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4528,18 +4581,18 @@
         <v>60</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="H34" s="11"/>
       <c r="I34" s="11"/>
       <c r="J34" s="11" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="K34" s="18" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4561,18 +4614,18 @@
         <v>60</v>
       </c>
       <c r="F35" s="14" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G35" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H35" s="14"/>
       <c r="I35" s="14"/>
       <c r="J35" s="14" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="K35" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4594,18 +4647,18 @@
         <v>90</v>
       </c>
       <c r="F36" s="14" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G36" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H36" s="14"/>
       <c r="I36" s="14"/>
       <c r="J36" s="14" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="K36" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4627,18 +4680,18 @@
         <v>30</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="H37" s="11"/>
       <c r="I37" s="11"/>
       <c r="J37" s="11" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="K37" s="18" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4660,18 +4713,18 @@
         <v>15</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G38" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H38" s="14"/>
       <c r="I38" s="14"/>
       <c r="J38" s="14" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K38" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4693,20 +4746,20 @@
         <v>15</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="G39" s="14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H39" s="14" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="I39" s="14"/>
       <c r="J39" s="14" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="K39" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4728,20 +4781,20 @@
         <v>20</v>
       </c>
       <c r="F40" s="19" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G40" s="19" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="H40" s="19" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="I40" s="19"/>
       <c r="J40" s="19" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="K40" s="22" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4763,18 +4816,18 @@
         <v>40</v>
       </c>
       <c r="F41" s="14" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G41" s="14" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="H41" s="14"/>
       <c r="I41" s="14"/>
       <c r="J41" s="14" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K41" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4796,20 +4849,20 @@
         <v>60</v>
       </c>
       <c r="F42" s="14" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G42" s="14" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="H42" s="14" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="I42" s="14"/>
       <c r="J42" s="14" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="K42" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4831,18 +4884,18 @@
         <v>60</v>
       </c>
       <c r="F43" s="14" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G43" s="14" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="H43" s="14"/>
       <c r="I43" s="14"/>
       <c r="J43" s="14" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K43" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4864,20 +4917,20 @@
         <v>10</v>
       </c>
       <c r="F44" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="G44" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="H44" s="19" t="s">
         <v>89</v>
-      </c>
-      <c r="G44" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="H44" s="19" t="s">
-        <v>85</v>
       </c>
       <c r="I44" s="19"/>
       <c r="J44" s="19" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="K44" s="22" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4899,22 +4952,22 @@
         <v>15</v>
       </c>
       <c r="F45" s="14" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G45" s="14" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H45" s="14" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I45" s="14" t="n">
         <v>2</v>
       </c>
       <c r="J45" s="14" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K45" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4936,18 +4989,18 @@
         <v>50</v>
       </c>
       <c r="F46" s="14" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G46" s="14" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="H46" s="14"/>
       <c r="I46" s="14"/>
       <c r="J46" s="14" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K46" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4969,18 +5022,18 @@
         <v>45</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G47" s="11" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="H47" s="11"/>
       <c r="I47" s="11"/>
       <c r="J47" s="11" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="K47" s="18" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5002,18 +5055,18 @@
         <v>180</v>
       </c>
       <c r="F48" s="14" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G48" s="14" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="H48" s="14"/>
       <c r="I48" s="14"/>
       <c r="J48" s="14" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="K48" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5035,22 +5088,22 @@
         <v>15</v>
       </c>
       <c r="F49" s="14" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G49" s="14" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="H49" s="14" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="I49" s="14" t="n">
         <v>3</v>
       </c>
       <c r="J49" s="14" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="K49" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5072,18 +5125,18 @@
         <v>45</v>
       </c>
       <c r="F50" s="14" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G50" s="14" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="H50" s="14"/>
       <c r="I50" s="14"/>
       <c r="J50" s="14" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="K50" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5105,22 +5158,22 @@
         <v>10</v>
       </c>
       <c r="F51" s="14" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G51" s="14" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="H51" s="14" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="I51" s="14" t="n">
         <v>1</v>
       </c>
       <c r="J51" s="14" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="K51" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5142,18 +5195,18 @@
         <v>30</v>
       </c>
       <c r="F52" s="14" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G52" s="14" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="H52" s="14"/>
       <c r="I52" s="14"/>
       <c r="J52" s="14" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="K52" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5175,22 +5228,22 @@
         <v>15</v>
       </c>
       <c r="F53" s="14" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G53" s="14" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="H53" s="14" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="I53" s="14" t="n">
         <v>2</v>
       </c>
       <c r="J53" s="14" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="K53" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5212,18 +5265,18 @@
         <v>95</v>
       </c>
       <c r="F54" s="14" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="G54" s="14" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="H54" s="14"/>
       <c r="I54" s="14"/>
       <c r="J54" s="14" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K54" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5245,22 +5298,22 @@
         <v>15</v>
       </c>
       <c r="F55" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="G55" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="G55" s="14" t="s">
-        <v>131</v>
-      </c>
       <c r="H55" s="14" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I55" s="14" t="n">
         <v>1</v>
       </c>
       <c r="J55" s="14" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="K55" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5282,18 +5335,18 @@
         <v>60</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G56" s="11" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="H56" s="11"/>
       <c r="I56" s="11"/>
       <c r="J56" s="11" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="K56" s="18" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5315,18 +5368,18 @@
         <v>45</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G57" s="11" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="H57" s="11"/>
       <c r="I57" s="11"/>
       <c r="J57" s="11" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="K57" s="18" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5348,18 +5401,18 @@
         <v>15</v>
       </c>
       <c r="F58" s="14" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G58" s="14" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="H58" s="14"/>
       <c r="I58" s="14"/>
       <c r="J58" s="14" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K58" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5381,22 +5434,22 @@
         <v>90</v>
       </c>
       <c r="F59" s="14" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G59" s="14" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="H59" s="14" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="I59" s="14" t="n">
         <v>50</v>
       </c>
       <c r="J59" s="14" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="K59" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5418,18 +5471,18 @@
         <v>90</v>
       </c>
       <c r="F60" s="14" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="G60" s="14" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="H60" s="14"/>
       <c r="I60" s="14"/>
       <c r="J60" s="14" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="K60" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5451,20 +5504,20 @@
         <v>50</v>
       </c>
       <c r="F61" s="19" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="G61" s="19" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="H61" s="19" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="I61" s="19"/>
       <c r="J61" s="19" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="K61" s="22" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5486,18 +5539,18 @@
         <v>25</v>
       </c>
       <c r="F62" s="14" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="G62" s="14" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H62" s="14"/>
       <c r="I62" s="14"/>
       <c r="J62" s="14" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="K62" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5519,22 +5572,22 @@
         <v>45</v>
       </c>
       <c r="F63" s="14" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G63" s="14" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H63" s="14" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I63" s="14" t="n">
         <v>14</v>
       </c>
       <c r="J63" s="14" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="K63" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5556,18 +5609,18 @@
         <v>60</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G64" s="11" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="H64" s="11"/>
       <c r="I64" s="11"/>
       <c r="J64" s="11" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="K64" s="18" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5589,18 +5642,18 @@
         <v>165</v>
       </c>
       <c r="F65" s="14" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G65" s="14" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="H65" s="14"/>
       <c r="I65" s="14"/>
       <c r="J65" s="14" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="K65" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5622,20 +5675,20 @@
         <v>15</v>
       </c>
       <c r="F66" s="14" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="G66" s="14" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="H66" s="14" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="I66" s="14"/>
       <c r="J66" s="14" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="K66" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5657,18 +5710,18 @@
         <v>90</v>
       </c>
       <c r="F67" s="19" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="G67" s="19" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="H67" s="19"/>
       <c r="I67" s="19"/>
       <c r="J67" s="19" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="K67" s="22" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5690,18 +5743,18 @@
         <v>90</v>
       </c>
       <c r="F68" s="14" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G68" s="14" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="H68" s="14"/>
       <c r="I68" s="14"/>
       <c r="J68" s="14" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="K68" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5723,18 +5776,18 @@
         <v>60</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G69" s="11" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="H69" s="11"/>
       <c r="I69" s="11"/>
       <c r="J69" s="11" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="K69" s="18" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5756,18 +5809,18 @@
         <v>45</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G70" s="11" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H70" s="11"/>
       <c r="I70" s="11"/>
       <c r="J70" s="11" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K70" s="18" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5789,22 +5842,22 @@
         <v>105</v>
       </c>
       <c r="F71" s="14" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G71" s="14" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H71" s="14" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I71" s="14" t="n">
         <v>50</v>
       </c>
       <c r="J71" s="14" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="K71" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5826,18 +5879,18 @@
         <v>210</v>
       </c>
       <c r="F72" s="19" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G72" s="19" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="H72" s="19"/>
       <c r="I72" s="19"/>
       <c r="J72" s="19" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="K72" s="22" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5859,18 +5912,18 @@
         <v>60</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G73" s="11" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="H73" s="11"/>
       <c r="I73" s="11"/>
       <c r="J73" s="11" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="K73" s="18" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5892,18 +5945,18 @@
         <v>30</v>
       </c>
       <c r="F74" s="14" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G74" s="14" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="H74" s="14"/>
       <c r="I74" s="14"/>
       <c r="J74" s="14" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="K74" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5925,18 +5978,18 @@
         <v>30</v>
       </c>
       <c r="F75" s="14" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G75" s="14" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="H75" s="14"/>
       <c r="I75" s="14"/>
       <c r="J75" s="14" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="K75" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5958,22 +6011,22 @@
         <v>15</v>
       </c>
       <c r="F76" s="14" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G76" s="14" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="H76" s="14" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="I76" s="14" t="n">
         <v>2</v>
       </c>
       <c r="J76" s="14" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="K76" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5995,18 +6048,18 @@
         <v>45</v>
       </c>
       <c r="F77" s="14" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G77" s="14" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="H77" s="14"/>
       <c r="I77" s="14"/>
       <c r="J77" s="14" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="K77" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6028,18 +6081,18 @@
         <v>90</v>
       </c>
       <c r="F78" s="14" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="G78" s="14" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="H78" s="14"/>
       <c r="I78" s="14"/>
       <c r="J78" s="14" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="K78" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6061,18 +6114,18 @@
         <v>150</v>
       </c>
       <c r="F79" s="14" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G79" s="14" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="H79" s="14"/>
       <c r="I79" s="14"/>
       <c r="J79" s="14" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="K79" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6094,18 +6147,18 @@
         <v>60</v>
       </c>
       <c r="F80" s="11" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G80" s="11" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="H80" s="11"/>
       <c r="I80" s="11"/>
       <c r="J80" s="11" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="K80" s="18" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6127,18 +6180,18 @@
         <v>30</v>
       </c>
       <c r="F81" s="11" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G81" s="11" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="H81" s="11"/>
       <c r="I81" s="11"/>
       <c r="J81" s="11" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="K81" s="18" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6160,22 +6213,22 @@
         <v>105</v>
       </c>
       <c r="F82" s="14" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G82" s="14" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H82" s="14" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="I82" s="14" t="n">
         <v>70</v>
       </c>
       <c r="J82" s="14" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="K82" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6197,18 +6250,18 @@
         <v>45</v>
       </c>
       <c r="F83" s="14" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G83" s="14" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="H83" s="14"/>
       <c r="I83" s="14"/>
       <c r="J83" s="14" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="K83" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6230,22 +6283,22 @@
         <v>120</v>
       </c>
       <c r="F84" s="14" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G84" s="14" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="H84" s="14" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="I84" s="14" t="n">
         <v>60</v>
       </c>
       <c r="J84" s="14" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="K84" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6267,20 +6320,20 @@
         <v>105</v>
       </c>
       <c r="F85" s="14" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="G85" s="14" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="H85" s="14" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="I85" s="14"/>
       <c r="J85" s="14" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="K85" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6302,18 +6355,18 @@
         <v>45</v>
       </c>
       <c r="F86" s="11" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G86" s="11" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="H86" s="11"/>
       <c r="I86" s="11"/>
       <c r="J86" s="11" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="K86" s="18" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6335,18 +6388,18 @@
         <v>45</v>
       </c>
       <c r="F87" s="14" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="G87" s="14" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="H87" s="14"/>
       <c r="I87" s="14"/>
       <c r="J87" s="14" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="K87" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6368,22 +6421,22 @@
         <v>180</v>
       </c>
       <c r="F88" s="14" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G88" s="14" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="H88" s="14" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="I88" s="14" t="n">
         <v>82</v>
       </c>
       <c r="J88" s="14" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="K88" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6405,18 +6458,18 @@
         <v>90</v>
       </c>
       <c r="F89" s="14" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G89" s="14" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H89" s="14"/>
       <c r="I89" s="14"/>
       <c r="J89" s="14" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="K89" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6438,18 +6491,18 @@
         <v>60</v>
       </c>
       <c r="F90" s="11" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G90" s="11" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H90" s="11"/>
       <c r="I90" s="11"/>
       <c r="J90" s="11" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="K90" s="18" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6471,18 +6524,18 @@
         <v>45</v>
       </c>
       <c r="F91" s="11" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G91" s="11" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H91" s="11"/>
       <c r="I91" s="11"/>
       <c r="J91" s="11" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="K91" s="18" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6504,22 +6557,22 @@
         <v>60</v>
       </c>
       <c r="F92" s="14" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G92" s="14" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H92" s="14" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="I92" s="14" t="n">
         <v>30</v>
       </c>
       <c r="J92" s="14" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="K92" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6541,18 +6594,18 @@
         <v>45</v>
       </c>
       <c r="F93" s="14" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="G93" s="14" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="H93" s="14"/>
       <c r="I93" s="14"/>
       <c r="J93" s="14" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="K93" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6574,22 +6627,22 @@
         <v>60</v>
       </c>
       <c r="F94" s="14" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G94" s="14" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="H94" s="14" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="I94" s="14" t="n">
         <v>35</v>
       </c>
       <c r="J94" s="14" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="K94" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6611,18 +6664,18 @@
         <v>45</v>
       </c>
       <c r="F95" s="14" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="G95" s="14" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="H95" s="14"/>
       <c r="I95" s="14"/>
       <c r="J95" s="14" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="K95" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6644,22 +6697,22 @@
         <v>75</v>
       </c>
       <c r="F96" s="14" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G96" s="14" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="H96" s="14" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="I96" s="14" t="n">
         <v>40</v>
       </c>
       <c r="J96" s="14" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="K96" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6681,18 +6734,18 @@
         <v>30</v>
       </c>
       <c r="F97" s="14" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G97" s="14" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="H97" s="14"/>
       <c r="I97" s="14"/>
       <c r="J97" s="14" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="K97" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6714,18 +6767,18 @@
         <v>60</v>
       </c>
       <c r="F98" s="11" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G98" s="11" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="H98" s="11"/>
       <c r="I98" s="11"/>
       <c r="J98" s="11" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="K98" s="18" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6747,18 +6800,18 @@
         <v>15</v>
       </c>
       <c r="F99" s="14" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G99" s="14" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="H99" s="14"/>
       <c r="I99" s="14"/>
       <c r="J99" s="14" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="K99" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6780,20 +6833,20 @@
         <v>40</v>
       </c>
       <c r="F100" s="19" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H100" s="19" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="I100" s="19"/>
       <c r="J100" s="19" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="K100" s="22" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6815,18 +6868,18 @@
         <v>35</v>
       </c>
       <c r="F101" s="14" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="G101" s="14" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="H101" s="14"/>
       <c r="I101" s="14"/>
       <c r="J101" s="14" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="K101" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6848,20 +6901,20 @@
         <v>20</v>
       </c>
       <c r="F102" s="19" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G102" s="19" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="H102" s="19" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="I102" s="19"/>
       <c r="J102" s="19" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="K102" s="22" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6883,18 +6936,18 @@
         <v>40</v>
       </c>
       <c r="F103" s="14" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="G103" s="14" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H103" s="14"/>
       <c r="I103" s="14"/>
       <c r="J103" s="14" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="K103" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6916,20 +6969,20 @@
         <v>50</v>
       </c>
       <c r="F104" s="19" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G104" s="19" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H104" s="19" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I104" s="19"/>
       <c r="J104" s="19" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="K104" s="22" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6951,18 +7004,18 @@
         <v>40</v>
       </c>
       <c r="F105" s="14" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="G105" s="14" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H105" s="14"/>
       <c r="I105" s="14"/>
       <c r="J105" s="14" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="K105" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6984,20 +7037,20 @@
         <v>30</v>
       </c>
       <c r="F106" s="19" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G106" s="19" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H106" s="19" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="I106" s="19"/>
       <c r="J106" s="19" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="K106" s="22" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7019,18 +7072,18 @@
         <v>60</v>
       </c>
       <c r="F107" s="14" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="G107" s="14" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H107" s="14"/>
       <c r="I107" s="14"/>
       <c r="J107" s="14" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="K107" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7052,18 +7105,18 @@
         <v>60</v>
       </c>
       <c r="F108" s="11" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G108" s="11" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="H108" s="11"/>
       <c r="I108" s="11"/>
       <c r="J108" s="11" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="K108" s="18" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7085,18 +7138,18 @@
         <v>45</v>
       </c>
       <c r="F109" s="11" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G109" s="11" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="H109" s="11"/>
       <c r="I109" s="11"/>
       <c r="J109" s="11" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="K109" s="18" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7118,22 +7171,22 @@
         <v>165</v>
       </c>
       <c r="F110" s="14" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G110" s="14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H110" s="14" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="I110" s="14" t="n">
         <v>95</v>
       </c>
       <c r="J110" s="14" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="K110" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7155,18 +7208,18 @@
         <v>75</v>
       </c>
       <c r="F111" s="14" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G111" s="14" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="H111" s="14"/>
       <c r="I111" s="14"/>
       <c r="J111" s="14" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="K111" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7188,22 +7241,22 @@
         <v>15</v>
       </c>
       <c r="F112" s="14" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G112" s="14" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="H112" s="14" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I112" s="14" t="n">
         <v>6</v>
       </c>
       <c r="J112" s="14" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="K112" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7225,18 +7278,18 @@
         <v>40</v>
       </c>
       <c r="F113" s="14" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G113" s="14" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="H113" s="14"/>
       <c r="I113" s="14"/>
       <c r="J113" s="14" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="K113" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7258,18 +7311,18 @@
         <v>60</v>
       </c>
       <c r="F114" s="11" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G114" s="11" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="H114" s="11"/>
       <c r="I114" s="11"/>
       <c r="J114" s="11" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="K114" s="18" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7291,18 +7344,18 @@
         <v>60</v>
       </c>
       <c r="F115" s="14" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="G115" s="14" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="H115" s="14"/>
       <c r="I115" s="14"/>
       <c r="J115" s="14" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="K115" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7324,22 +7377,22 @@
         <v>45</v>
       </c>
       <c r="F116" s="14" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G116" s="14" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="H116" s="14" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="I116" s="14" t="n">
         <v>14</v>
       </c>
       <c r="J116" s="14" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="K116" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7361,23 +7414,23 @@
         <v>30</v>
       </c>
       <c r="F117" s="14" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="G117" s="14" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H117" s="14"/>
       <c r="I117" s="14"/>
       <c r="J117" s="14" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="K117" s="17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="5" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -7525,27 +7578,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7553,19 +7606,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7573,19 +7626,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7593,19 +7646,19 @@
         <v>1</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7613,19 +7666,19 @@
         <v>2</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7633,19 +7686,19 @@
         <v>2</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7653,19 +7706,19 @@
         <v>2</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7673,19 +7726,19 @@
         <v>3</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7693,19 +7746,19 @@
         <v>3</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7713,19 +7766,19 @@
         <v>3</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7733,19 +7786,19 @@
         <v>4</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7753,19 +7806,19 @@
         <v>4</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7773,19 +7826,19 @@
         <v>4</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7793,19 +7846,19 @@
         <v>5</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7813,19 +7866,19 @@
         <v>5</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7833,19 +7886,19 @@
         <v>5</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7853,19 +7906,19 @@
         <v>6</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C19" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="F19" s="14" t="s">
         <v>276</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>271</v>
-      </c>
-      <c r="F19" s="14" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7873,19 +7926,19 @@
         <v>6</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7893,19 +7946,19 @@
         <v>6</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7913,19 +7966,19 @@
         <v>7</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7933,19 +7986,19 @@
         <v>7</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7953,19 +8006,19 @@
         <v>7</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7973,19 +8026,19 @@
         <v>8</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7993,24 +8046,24 @@
         <v>8</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
   </sheetData>
@@ -8039,112 +8092,112 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -8174,198 +8227,198 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
   </sheetData>
@@ -8393,207 +8446,207 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="14" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="14" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
   </sheetData>
@@ -8612,7 +8665,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
@@ -8624,233 +8677,248 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="E4" s="23"/>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="E5" s="23"/>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
+        <v>415</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>416</v>
+      </c>
+      <c r="C6" s="14" t="s">
         <v>410</v>
       </c>
-      <c r="B6" s="14" t="s">
-        <v>411</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>406</v>
-      </c>
       <c r="D6" s="14" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="E6" s="23"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
+        <v>418</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>419</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>420</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>421</v>
+      </c>
+      <c r="E7" s="23"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="s">
+        <v>422</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>423</v>
+      </c>
+      <c r="C8" s="14" t="s">
         <v>410</v>
       </c>
-      <c r="B7" s="14" t="s">
-        <v>413</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>406</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>414</v>
-      </c>
-      <c r="E7" s="23"/>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14" t="s">
-        <v>415</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>416</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>417</v>
-      </c>
       <c r="D8" s="14" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="E8" s="23"/>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="E9" s="23"/>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="E10" s="23"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="E11" s="23"/>
     </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="B12" s="14" t="s">
+        <v>434</v>
+      </c>
+      <c r="C12" s="14" t="s">
         <v>427</v>
       </c>
-      <c r="C12" s="14" t="s">
-        <v>428</v>
-      </c>
       <c r="D12" s="14" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="E12" s="23"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>417</v>
+        <v>438</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="E13" s="23"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="E14" s="23"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>428</v>
-      </c>
-      <c r="D15" s="14"/>
+        <v>438</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>444</v>
+      </c>
       <c r="E15" s="23"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="B16" s="14" t="s">
+        <v>446</v>
+      </c>
+      <c r="C16" s="14" t="s">
         <v>438</v>
       </c>
-      <c r="C16" s="14" t="s">
-        <v>428</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>439</v>
-      </c>
+      <c r="D16" s="14"/>
       <c r="E16" s="23"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="E17" s="23"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="14" t="s">
+        <v>450</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>451</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>438</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>452</v>
+      </c>
+      <c r="E18" s="23"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -8877,146 +8945,146 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>463</v>
+        <v>473</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>465</v>
+        <v>475</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
     </row>
   </sheetData>
@@ -9044,90 +9112,90 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>471</v>
+        <v>481</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>472</v>
+        <v>482</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>473</v>
+        <v>483</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>475</v>
+        <v>485</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>479</v>
+        <v>489</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>480</v>
+        <v>490</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>484</v>
+        <v>494</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>486</v>
+        <v>496</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>488</v>
+        <v>498</v>
       </c>
     </row>
   </sheetData>

--- a/docs/itineraries/vaishno-devi-kashmir-8d-plan.xlsx
+++ b/docs/itineraries/vaishno-devi-kashmir-8d-plan.xlsx
@@ -23,7 +23,7 @@
     <sheet name="Open Points" sheetId="13" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Minute-by-Minute'!$A$4:$K$117</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Minute-by-Minute'!$A$4:$K$121</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="609">
   <si>
     <t xml:space="preserve">8 Days Vaishno Devi &amp; Kashmir Pilgrimage – Overview</t>
   </si>
@@ -139,10 +139,10 @@
     <t xml:space="preserve">Union cab 56 km on Day 7 (Chandanwari, Betaab, Aru) is not counted in car km.</t>
   </si>
   <si>
-    <t xml:space="preserve">Days 1–3 are identical to the 4-day Vaishno Devi package; 4-day yatris leave the group at Jammu Airport on Day 4 morning.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assumptions: arrival at Jammu by 14:00 on Day 1; helicopter slots 10:30 (Day 2) and 11:00 (Day 3); Jammu → Srinagar flight ~11:00 Day 4; Srinagar departure after 17:30 Day 8; Kashmir hotels on MAP (breakfast + dinner). Day 6 is the longest road day (~212 km); start by 07:45 after the 07:15 parana breakfast.</t>
+    <t xml:space="preserve">Days 1–3 are identical to the 4-day Vaishno Devi package; 4-day yatris leave the group at Jammu Airport on Day 4.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumptions: arrival at Jammu by 14:00 on Day 1; breakfast 07:30–08:30 and departure from the hotel at 09:00 every day; helicopter slots 12:15 (Day 2) and 12:15 (Day 3); Jammu → Srinagar flight around 12:00 on Day 4; departure from Srinagar after 18:45 on Day 8; Kashmir hotels on MAP (breakfast + dinner). Day 6 is the longest road day (~212 km); start 09:00 after breakfast; back in Srinagar about 19:15.</t>
   </si>
   <si>
     <t xml:space="preserve">8 Days Vaishno Devi &amp; Kashmir Pilgrimage – Minute-to-Minute Plan</t>
@@ -283,7 +283,7 @@
     <t xml:space="preserve">Dinner – at the hotel, pre-ordered pure-veg menu; group pays (not in room rate)</t>
   </si>
   <si>
-    <t xml:space="preserve">Breakfast – complimentary with the hotel stay (request 06:30 opening)</t>
+    <t xml:space="preserve">Breakfast – complimentary with the hotel stay</t>
   </si>
   <si>
     <t xml:space="preserve">Check-out, load luggage</t>
@@ -364,7 +364,10 @@
     <t xml:space="preserve">Wake-up, bath, get ready</t>
   </si>
   <si>
-    <t xml:space="preserve">Morning Aarti at the Holy Cave</t>
+    <t xml:space="preserve">Morning Aarti at the Holy Cave (fixed temple timing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rest, pack small bag</t>
   </si>
   <si>
     <t xml:space="preserve">Breakfast – Shrine Board Bhojanalaya; pay at counter (Bhawan rooms do not include meals)</t>
@@ -466,10 +469,7 @@
     <t xml:space="preserve">Dinner – at the hotel, pre-ordered pure-veg menu; group pays; Day 4 briefing</t>
   </si>
   <si>
-    <t xml:space="preserve">Breakfast – complimentary with the hotel stay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drive to Jammu Airport</t>
+    <t xml:space="preserve">Drive to Jammu Airport (4-day yatris are dropped here)</t>
   </si>
   <si>
     <t xml:space="preserve">Airport</t>
@@ -502,9 +502,6 @@
     <t xml:space="preserve">Lunch – at the hotel / houseboat after check-in; group pays</t>
   </si>
   <si>
-    <t xml:space="preserve">Rest after the early start</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hotel</t>
   </si>
   <si>
@@ -532,13 +529,16 @@
     <t xml:space="preserve">Hotel restaurant, Srinagar</t>
   </si>
   <si>
-    <t xml:space="preserve">Breakfast – included (MAP); Amalaki Ekadashi – grain-free items; check-out</t>
+    <t xml:space="preserve">Breakfast – included (MAP); Amalaki Ekadashi – grain-free items</t>
   </si>
   <si>
     <t xml:space="preserve">Hotel, Srinagar</t>
   </si>
   <si>
-    <t xml:space="preserve">Drive via Tangmarg (hire snow boots / coats at Tangmarg in winter)</t>
+    <t xml:space="preserve">Check-out (main luggage can stay at the Srinagar hotel for Day 6 return)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drive via Tangmarg (hire snow boots / coats at Tangmarg)</t>
   </si>
   <si>
     <t xml:space="preserve">Gondola</t>
@@ -562,9 +562,6 @@
     <t xml:space="preserve">Check-in</t>
   </si>
   <si>
-    <t xml:space="preserve">Short rest</t>
-  </si>
-  <si>
     <t xml:space="preserve">Maharani Temple</t>
   </si>
   <si>
@@ -586,7 +583,7 @@
     <t xml:space="preserve">Meadow walk, Himalayan views at sunset, group photo</t>
   </si>
   <si>
-    <t xml:space="preserve">Rest, kirtan; Day 6 briefing (early start, long drive)</t>
+    <t xml:space="preserve">Rest, Ekadashi kirtan; Day 6 briefing (long drive)</t>
   </si>
   <si>
     <t xml:space="preserve">Hotel restaurant, Gulmarg</t>
@@ -595,7 +592,7 @@
     <t xml:space="preserve">Dinner – included (MAP); Ekadashi grain-free menu pre-ordered with the hotel</t>
   </si>
   <si>
-    <t xml:space="preserve">Break fast (parana) 07:14–10:26 – breakfast from 07:15, included (MAP); check-out ready before</t>
+    <t xml:space="preserve">Break fast (parana) 07:14–10:26 – breakfast included (MAP)</t>
   </si>
   <si>
     <t xml:space="preserve">Kheer Bhawani Temple, Tulmulla</t>
@@ -619,6 +616,12 @@
     <t xml:space="preserve">Scenic drive along the Sindh river</t>
   </si>
   <si>
+    <t xml:space="preserve">Pure-veg restaurant, Sonamarg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lunch – pure-veg dhaba / restaurant at Sonamarg market; group pays</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pony / local taxi</t>
   </si>
   <si>
@@ -628,28 +631,19 @@
     <t xml:space="preserve">Thajiwas Glacier by pony (optional, ~3 km; fixed union rates); snow play</t>
   </si>
   <si>
-    <t xml:space="preserve">Pure-veg restaurant, Sonamarg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lunch – pure-veg dhaba / restaurant at Sonamarg market; group pays</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sindh River viewpoints, Sonamarg</t>
   </si>
   <si>
     <t xml:space="preserve">Sindh river banks and snow-peak viewpoints; group photo</t>
   </si>
   <si>
-    <t xml:space="preserve">Return to Srinagar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check-in, rest, kirtan</t>
+    <t xml:space="preserve">Return to Srinagar (last hour after dark – experienced driver)</t>
   </si>
   <si>
     <t xml:space="preserve">Dinner – included (MAP)</t>
   </si>
   <si>
-    <t xml:space="preserve">Breakfast – included (MAP); check-out</t>
+    <t xml:space="preserve">Breakfast – included (MAP)</t>
   </si>
   <si>
     <t xml:space="preserve">Avantipur Temple Ruins</t>
@@ -700,10 +694,10 @@
     <t xml:space="preserve">Chandanwari</t>
   </si>
   <si>
-    <t xml:space="preserve">16 km by union cab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start point of the Amarnath route; snow bridge (season)</t>
+    <t xml:space="preserve">16 km by union cab (if open in March)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start point of the Amarnath route; snow</t>
   </si>
   <si>
     <t xml:space="preserve">Betaab Valley</t>
@@ -721,7 +715,7 @@
     <t xml:space="preserve">21 km via Pahalgam</t>
   </si>
   <si>
-    <t xml:space="preserve">Meadow village, pine forests</t>
+    <t xml:space="preserve">Meadow village, pine forests, sunset</t>
   </si>
   <si>
     <t xml:space="preserve">12 km back to Pahalgam</t>
@@ -730,7 +724,7 @@
     <t xml:space="preserve">Lidder River banks</t>
   </si>
   <si>
-    <t xml:space="preserve">Evening walk by the Lidder river; kirtan</t>
+    <t xml:space="preserve">Short evening walk by the Lidder river; kirtan</t>
   </si>
   <si>
     <t xml:space="preserve">Shankaracharya Temple, Srinagar</t>
@@ -775,7 +769,7 @@
     <t xml:space="preserve">Departure</t>
   </si>
   <si>
-    <t xml:space="preserve">Drop-off, farewell, Jai Mata Di! Har Har Mahadev! (flights after 17:30; reach 2.5 hrs early)</t>
+    <t xml:space="preserve">Drop-off, farewell, Jai Mata Di! Har Har Mahadev! (book flights after 18:45; reach 2.5 hrs early)</t>
   </si>
   <si>
     <t xml:space="preserve">Legend: yellow rows = meals; blue rows = helicopter, ropeway, flight, gondola, shikara, union cab.</t>
@@ -826,13 +820,13 @@
     <t xml:space="preserve">Hotel, pre-ordered menu</t>
   </si>
   <si>
-    <t xml:space="preserve">06:30–07:00</t>
+    <t xml:space="preserve">07:30–08:30</t>
   </si>
   <si>
     <t xml:space="preserve">Complimentary</t>
   </si>
   <si>
-    <t xml:space="preserve">12:15–13:00</t>
+    <t xml:space="preserve">14:00–14:45</t>
   </si>
   <si>
     <t xml:space="preserve">Shrine Board (SMVDSB)</t>
@@ -844,7 +838,7 @@
     <t xml:space="preserve">19:30–20:30</t>
   </si>
   <si>
-    <t xml:space="preserve">07:00–07:30</t>
+    <t xml:space="preserve">13:15–14:00</t>
   </si>
   <si>
     <t xml:space="preserve">Hotel / restaurant</t>
@@ -853,10 +847,7 @@
     <t xml:space="preserve">20:00–21:00</t>
   </si>
   <si>
-    <t xml:space="preserve">07:00–07:45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13:00–14:00</t>
+    <t xml:space="preserve">14:00–15:00</t>
   </si>
   <si>
     <t xml:space="preserve">Hotel / houseboat, Srinagar</t>
@@ -871,22 +862,22 @@
     <t xml:space="preserve">Hotel (MAP), Ekadashi items</t>
   </si>
   <si>
+    <t xml:space="preserve">13:45–14:30</t>
+  </si>
+  <si>
     <t xml:space="preserve">Restaurant, pre-booked (Ekadashi grain-free)</t>
   </si>
   <si>
     <t xml:space="preserve">Hotel (MAP), Ekadashi menu</t>
   </si>
   <si>
-    <t xml:space="preserve">07:15–07:45 (parana)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:00–14:45</t>
+    <t xml:space="preserve">07:30–08:30 (parana)</t>
   </si>
   <si>
     <t xml:space="preserve">Restaurant, pre-booked</t>
   </si>
   <si>
-    <t xml:space="preserve">12:45–13:45</t>
+    <t xml:space="preserve">13:45–14:45</t>
   </si>
   <si>
     <t xml:space="preserve">Pure-veg options are few in Gulmarg and Sonamarg; pre-book for the group size or carry packed lunch from the hotel. Ask every kitchen about no onion-garlic cooking.</t>
@@ -1072,7 +1063,7 @@
     <t xml:space="preserve">Late arrival, fatigue</t>
   </si>
   <si>
-    <t xml:space="preserve">Start by 07:30; comfort stops every 90 min</t>
+    <t xml:space="preserve">Start 09:00 after breakfast; comfort stops every 90 min</t>
   </si>
   <si>
     <t xml:space="preserve">Skip the Thajiwas pony ride; rest at Sonamarg</t>
@@ -1135,7 +1126,7 @@
     <t xml:space="preserve">Reach the airport 2.5 hrs early</t>
   </si>
   <si>
-    <t xml:space="preserve">Book departure after 17:30</t>
+    <t xml:space="preserve">Book departure after 18:45</t>
   </si>
   <si>
     <t xml:space="preserve">Lost yatri in crowd</t>
@@ -1315,7 +1306,7 @@
     <t xml:space="preserve">T−45 days</t>
   </si>
   <si>
-    <t xml:space="preserve">Book flights: home → Jammu (Day 1, arriving by 14:00), Jammu → Srinagar (Day 4 morning), Srinagar → home (Day 8, after 17:30)</t>
+    <t xml:space="preserve">Book flights: home → Jammu (Day 1, arriving by 14:00), Jammu → Srinagar (Day 4, around 12:00), Srinagar → home (Day 8, after 18:45)</t>
   </si>
   <si>
     <t xml:space="preserve">Travel desk</t>
@@ -1834,7 +1825,7 @@
     <t xml:space="preserve">Every yatri's arrival in Jammu by 14:00 on Day 1 and departure flight from Srinagar on Day 8</t>
   </si>
   <si>
-    <t xml:space="preserve">Jammu → Srinagar flight time on Day 4 (the day plan assumes about 11:00)</t>
+    <t xml:space="preserve">Jammu → Srinagar flight time on Day 4 (the day plan assumes about 12:00)</t>
   </si>
   <si>
     <t xml:space="preserve">Helicopter slots booked on 1 Jan 2027 for Day 2 and Day 3, and the reporting time on the tickets</t>
@@ -1867,7 +1858,7 @@
     <t xml:space="preserve">Which 4-day yatris continue to Kashmir, and the drop at Jammu Airport on Day 4 for those who return home</t>
   </si>
   <si>
-    <t xml:space="preserve">Amalaki Ekadashi (17 Mar) grain-free menus confirmed with the Srinagar and Gulmarg hotels; parana breakfast from 07:15 on 18 Mar</t>
+    <t xml:space="preserve">Amalaki Ekadashi (17 Mar) grain-free menus confirmed with the Srinagar and Gulmarg hotels; parana breakfast 07:30–08:30 on 18 Mar (within 07:14–10:26)</t>
   </si>
   <si>
     <t xml:space="preserve">In mid-March Chandanwari, Betaab and Aru may still be snowbound; confirm with the Pahalgam union how far cabs can go</t>
@@ -2533,18 +2524,18 @@
         <v>13</v>
       </c>
       <c r="D5" s="7" t="n">
-        <f aca="false">SUMIF('Minute-by-Minute'!$A$5:$A$117,A5,'Minute-by-Minute'!$I$5:$I$117)</f>
+        <f aca="false">SUMIF('Minute-by-Minute'!$A$5:$A$121,A5,'Minute-by-Minute'!$I$5:$I$121)</f>
         <v>32</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>14</v>
       </c>
       <c r="F5" s="9" t="n">
-        <f aca="false">_xlfn.MINIFS('Minute-by-Minute'!$C$5:$C$117,'Minute-by-Minute'!$A$5:$A$117,A5)</f>
+        <f aca="false">_xlfn.MINIFS('Minute-by-Minute'!$C$5:$C$121,'Minute-by-Minute'!$A$5:$A$121,A5)</f>
         <v>0.333333333333333</v>
       </c>
       <c r="G5" s="9" t="n">
-        <f aca="false">_xlfn.MAXIFS('Minute-by-Minute'!$D$5:$D$117,'Minute-by-Minute'!$A$5:$A$117,A5)</f>
+        <f aca="false">_xlfn.MAXIFS('Minute-by-Minute'!$D$5:$D$121,'Minute-by-Minute'!$A$5:$A$121,A5)</f>
         <v>0.885416666666667</v>
       </c>
       <c r="I5" s="7" t="s">
@@ -2566,18 +2557,18 @@
         <v>16</v>
       </c>
       <c r="D6" s="7" t="n">
-        <f aca="false">SUMIF('Minute-by-Minute'!$A$5:$A$117,A6,'Minute-by-Minute'!$I$5:$I$117)</f>
+        <f aca="false">SUMIF('Minute-by-Minute'!$A$5:$A$121,A6,'Minute-by-Minute'!$I$5:$I$121)</f>
         <v>52</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F6" s="9" t="n">
-        <f aca="false">_xlfn.MINIFS('Minute-by-Minute'!$C$5:$C$117,'Minute-by-Minute'!$A$5:$A$117,A6)</f>
-        <v>0.270833333333333</v>
+        <f aca="false">_xlfn.MINIFS('Minute-by-Minute'!$C$5:$C$121,'Minute-by-Minute'!$A$5:$A$121,A6)</f>
+        <v>0.3125</v>
       </c>
       <c r="G6" s="9" t="n">
-        <f aca="false">_xlfn.MAXIFS('Minute-by-Minute'!$D$5:$D$117,'Minute-by-Minute'!$A$5:$A$117,A6)</f>
+        <f aca="false">_xlfn.MAXIFS('Minute-by-Minute'!$D$5:$D$121,'Minute-by-Minute'!$A$5:$A$121,A6)</f>
         <v>0.854166666666667</v>
       </c>
       <c r="I6" s="7" t="s">
@@ -2599,18 +2590,18 @@
         <v>19</v>
       </c>
       <c r="D7" s="7" t="n">
-        <f aca="false">SUMIF('Minute-by-Minute'!$A$5:$A$117,A7,'Minute-by-Minute'!$I$5:$I$117)</f>
+        <f aca="false">SUMIF('Minute-by-Minute'!$A$5:$A$121,A7,'Minute-by-Minute'!$I$5:$I$121)</f>
         <v>9</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F7" s="9" t="n">
-        <f aca="false">_xlfn.MINIFS('Minute-by-Minute'!$C$5:$C$117,'Minute-by-Minute'!$A$5:$A$117,A7)</f>
+        <f aca="false">_xlfn.MINIFS('Minute-by-Minute'!$C$5:$C$121,'Minute-by-Minute'!$A$5:$A$121,A7)</f>
         <v>0.1875</v>
       </c>
       <c r="G7" s="9" t="n">
-        <f aca="false">_xlfn.MAXIFS('Minute-by-Minute'!$D$5:$D$117,'Minute-by-Minute'!$A$5:$A$117,A7)</f>
+        <f aca="false">_xlfn.MAXIFS('Minute-by-Minute'!$D$5:$D$121,'Minute-by-Minute'!$A$5:$A$121,A7)</f>
         <v>0.875</v>
       </c>
     </row>
@@ -2626,18 +2617,18 @@
         <v>21</v>
       </c>
       <c r="D8" s="7" t="n">
-        <f aca="false">SUMIF('Minute-by-Minute'!$A$5:$A$117,A8,'Minute-by-Minute'!$I$5:$I$117)</f>
+        <f aca="false">SUMIF('Minute-by-Minute'!$A$5:$A$121,A8,'Minute-by-Minute'!$I$5:$I$121)</f>
         <v>64</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>22</v>
       </c>
       <c r="F8" s="9" t="n">
-        <f aca="false">_xlfn.MINIFS('Minute-by-Minute'!$C$5:$C$117,'Minute-by-Minute'!$A$5:$A$117,A8)</f>
-        <v>0.291666666666667</v>
+        <f aca="false">_xlfn.MINIFS('Minute-by-Minute'!$C$5:$C$121,'Minute-by-Minute'!$A$5:$A$121,A8)</f>
+        <v>0.3125</v>
       </c>
       <c r="G8" s="9" t="n">
-        <f aca="false">_xlfn.MAXIFS('Minute-by-Minute'!$D$5:$D$117,'Minute-by-Minute'!$A$5:$A$117,A8)</f>
+        <f aca="false">_xlfn.MAXIFS('Minute-by-Minute'!$D$5:$D$121,'Minute-by-Minute'!$A$5:$A$121,A8)</f>
         <v>0.875</v>
       </c>
     </row>
@@ -2653,18 +2644,18 @@
         <v>23</v>
       </c>
       <c r="D9" s="7" t="n">
-        <f aca="false">SUMIF('Minute-by-Minute'!$A$5:$A$117,A9,'Minute-by-Minute'!$I$5:$I$117)</f>
+        <f aca="false">SUMIF('Minute-by-Minute'!$A$5:$A$121,A9,'Minute-by-Minute'!$I$5:$I$121)</f>
         <v>52</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>24</v>
       </c>
       <c r="F9" s="9" t="n">
-        <f aca="false">_xlfn.MINIFS('Minute-by-Minute'!$C$5:$C$117,'Minute-by-Minute'!$A$5:$A$117,A9)</f>
-        <v>0.291666666666667</v>
+        <f aca="false">_xlfn.MINIFS('Minute-by-Minute'!$C$5:$C$121,'Minute-by-Minute'!$A$5:$A$121,A9)</f>
+        <v>0.3125</v>
       </c>
       <c r="G9" s="9" t="n">
-        <f aca="false">_xlfn.MAXIFS('Minute-by-Minute'!$D$5:$D$117,'Minute-by-Minute'!$A$5:$A$117,A9)</f>
+        <f aca="false">_xlfn.MAXIFS('Minute-by-Minute'!$D$5:$D$121,'Minute-by-Minute'!$A$5:$A$121,A9)</f>
         <v>0.875</v>
       </c>
     </row>
@@ -2680,18 +2671,18 @@
         <v>25</v>
       </c>
       <c r="D10" s="7" t="n">
-        <f aca="false">SUMIF('Minute-by-Minute'!$A$5:$A$117,A10,'Minute-by-Minute'!$I$5:$I$117)</f>
+        <f aca="false">SUMIF('Minute-by-Minute'!$A$5:$A$121,A10,'Minute-by-Minute'!$I$5:$I$121)</f>
         <v>212</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>22</v>
       </c>
       <c r="F10" s="9" t="n">
-        <f aca="false">_xlfn.MINIFS('Minute-by-Minute'!$C$5:$C$117,'Minute-by-Minute'!$A$5:$A$117,A10)</f>
-        <v>0.302083333333333</v>
+        <f aca="false">_xlfn.MINIFS('Minute-by-Minute'!$C$5:$C$121,'Minute-by-Minute'!$A$5:$A$121,A10)</f>
+        <v>0.3125</v>
       </c>
       <c r="G10" s="9" t="n">
-        <f aca="false">_xlfn.MAXIFS('Minute-by-Minute'!$D$5:$D$117,'Minute-by-Minute'!$A$5:$A$117,A10)</f>
+        <f aca="false">_xlfn.MAXIFS('Minute-by-Minute'!$D$5:$D$121,'Minute-by-Minute'!$A$5:$A$121,A10)</f>
         <v>0.875</v>
       </c>
     </row>
@@ -2707,18 +2698,18 @@
         <v>26</v>
       </c>
       <c r="D11" s="7" t="n">
-        <f aca="false">SUMIF('Minute-by-Minute'!$A$5:$A$117,A11,'Minute-by-Minute'!$I$5:$I$117)</f>
+        <f aca="false">SUMIF('Minute-by-Minute'!$A$5:$A$121,A11,'Minute-by-Minute'!$I$5:$I$121)</f>
         <v>105</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>27</v>
       </c>
       <c r="F11" s="9" t="n">
-        <f aca="false">_xlfn.MINIFS('Minute-by-Minute'!$C$5:$C$117,'Minute-by-Minute'!$A$5:$A$117,A11)</f>
-        <v>0.291666666666667</v>
+        <f aca="false">_xlfn.MINIFS('Minute-by-Minute'!$C$5:$C$121,'Minute-by-Minute'!$A$5:$A$121,A11)</f>
+        <v>0.3125</v>
       </c>
       <c r="G11" s="9" t="n">
-        <f aca="false">_xlfn.MAXIFS('Minute-by-Minute'!$D$5:$D$117,'Minute-by-Minute'!$A$5:$A$117,A11)</f>
+        <f aca="false">_xlfn.MAXIFS('Minute-by-Minute'!$D$5:$D$121,'Minute-by-Minute'!$A$5:$A$121,A11)</f>
         <v>0.875</v>
       </c>
     </row>
@@ -2734,19 +2725,19 @@
         <v>28</v>
       </c>
       <c r="D12" s="7" t="n">
-        <f aca="false">SUMIF('Minute-by-Minute'!$A$5:$A$117,A12,'Minute-by-Minute'!$I$5:$I$117)</f>
+        <f aca="false">SUMIF('Minute-by-Minute'!$A$5:$A$121,A12,'Minute-by-Minute'!$I$5:$I$121)</f>
         <v>115</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F12" s="9" t="n">
-        <f aca="false">_xlfn.MINIFS('Minute-by-Minute'!$C$5:$C$117,'Minute-by-Minute'!$A$5:$A$117,A12)</f>
-        <v>0.291666666666667</v>
+        <f aca="false">_xlfn.MINIFS('Minute-by-Minute'!$C$5:$C$121,'Minute-by-Minute'!$A$5:$A$121,A12)</f>
+        <v>0.3125</v>
       </c>
       <c r="G12" s="9" t="n">
-        <f aca="false">_xlfn.MAXIFS('Minute-by-Minute'!$D$5:$D$117,'Minute-by-Minute'!$A$5:$A$117,A12)</f>
-        <v>0.666666666666667</v>
+        <f aca="false">_xlfn.MAXIFS('Minute-by-Minute'!$D$5:$D$121,'Minute-by-Minute'!$A$5:$A$121,A12)</f>
+        <v>0.697916666666667</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2808,100 +2799,100 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
+        <v>496</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>497</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>498</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>499</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>500</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>501</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
+        <v>500</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>501</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>502</v>
+      </c>
+      <c r="D2" s="14" t="s">
         <v>503</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>504</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>505</v>
-      </c>
-      <c r="D2" s="14" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
+        <v>504</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>505</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>506</v>
+      </c>
+      <c r="D3" s="14" t="s">
         <v>507</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>508</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>509</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
+        <v>508</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>509</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>510</v>
+      </c>
+      <c r="D4" s="14" t="s">
         <v>511</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>512</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>513</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
+        <v>512</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>513</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>514</v>
+      </c>
+      <c r="D5" s="14" t="s">
         <v>515</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>516</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>517</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
+        <v>516</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>517</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>518</v>
+      </c>
+      <c r="D6" s="14" t="s">
         <v>519</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>520</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>521</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
@@ -2931,91 +2922,91 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
+        <v>523</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>524</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>525</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>526</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>527</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>528</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="C2" s="23"/>
       <c r="D2" s="23"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="C3" s="23"/>
       <c r="D3" s="23"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="C4" s="23"/>
       <c r="D4" s="23"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="C5" s="23"/>
       <c r="D5" s="23"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="C6" s="23"/>
       <c r="D6" s="23"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="C7" s="23"/>
       <c r="D7" s="23"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="C8" s="23"/>
       <c r="D8" s="23"/>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="B9" s="14"/>
       <c r="C9" s="23"/>
@@ -3023,7 +3014,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="B10" s="14"/>
       <c r="C10" s="23"/>
@@ -3031,17 +3022,17 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="C11" s="23"/>
       <c r="D11" s="23"/>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="B12" s="14"/>
       <c r="C12" s="23"/>
@@ -3049,24 +3040,24 @@
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="C13" s="23"/>
       <c r="D13" s="23"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="C14" s="14"/>
       <c r="D14" s="14" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
   </sheetData>
@@ -3096,259 +3087,259 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
+        <v>552</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>553</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>554</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>555</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>556</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>557</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="D5" s="24"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>560</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>563</v>
       </c>
       <c r="D6" s="24"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="D7" s="24"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="D8" s="24"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="D9" s="24"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="D10" s="24"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="D11" s="24"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="D12" s="24"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="D13" s="24"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="B14" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>560</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>563</v>
       </c>
       <c r="D14" s="24"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="D15" s="24"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="D16" s="24"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="D17" s="24"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="D18" s="24"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="D19" s="24"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="D20" s="24"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="B21" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="C21" s="7" t="s">
         <v>560</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>563</v>
       </c>
       <c r="D21" s="24"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="B22" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>560</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>563</v>
       </c>
       <c r="D22" s="24"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="D23" s="24"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="D24" s="25" t="n">
         <f aca="false">SUMIF(C5:C23,"Yes",D5:D23)</f>
@@ -3357,10 +3348,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="D25" s="26" t="n">
         <v>0.05</v>
@@ -3368,7 +3359,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="D26" s="25" t="n">
         <f aca="false">D24*(1+D25)</f>
@@ -3377,7 +3368,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
     </row>
   </sheetData>
@@ -3405,93 +3396,93 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="B2" s="23"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="B3" s="23"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="B4" s="23"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="B5" s="23"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="B6" s="23"/>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="B7" s="23"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="B8" s="23"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="B9" s="23"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="B10" s="23"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="B11" s="23"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="B12" s="23"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="B13" s="23"/>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="B14" s="23"/>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="B15" s="23"/>
     </row>
@@ -3511,7 +3502,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K119"/>
+  <dimension ref="A1:K123"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -4130,14 +4121,14 @@
         <v>46460</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>0.270833333333333</v>
+        <v>0.3125</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>0.291666666666667</v>
+        <v>0.354166666666667</v>
       </c>
       <c r="E21" s="11" t="n">
         <f aca="false">ROUND((D21-C21)*1440,0)</f>
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F21" s="11" t="s">
         <v>46</v>
@@ -4163,14 +4154,14 @@
         <v>46460</v>
       </c>
       <c r="C22" s="16" t="n">
-        <v>0.291666666666667</v>
+        <v>0.354166666666667</v>
       </c>
       <c r="D22" s="16" t="n">
-        <v>0.302083333333333</v>
+        <v>0.375</v>
       </c>
       <c r="E22" s="14" t="n">
         <f aca="false">ROUND((D22-C22)*1440,0)</f>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F22" s="14" t="s">
         <v>57</v>
@@ -4196,10 +4187,10 @@
         <v>46460</v>
       </c>
       <c r="C23" s="16" t="n">
-        <v>0.302083333333333</v>
+        <v>0.375</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>0.364583333333333</v>
+        <v>0.4375</v>
       </c>
       <c r="E23" s="14" t="n">
         <f aca="false">ROUND((D23-C23)*1440,0)</f>
@@ -4233,10 +4224,10 @@
         <v>46460</v>
       </c>
       <c r="C24" s="16" t="n">
-        <v>0.364583333333333</v>
+        <v>0.4375</v>
       </c>
       <c r="D24" s="16" t="n">
-        <v>0.385416666666667</v>
+        <v>0.458333333333333</v>
       </c>
       <c r="E24" s="14" t="n">
         <f aca="false">ROUND((D24-C24)*1440,0)</f>
@@ -4266,10 +4257,10 @@
         <v>46460</v>
       </c>
       <c r="C25" s="16" t="n">
-        <v>0.385416666666667</v>
+        <v>0.458333333333333</v>
       </c>
       <c r="D25" s="16" t="n">
-        <v>0.392361111111111</v>
+        <v>0.465277777777778</v>
       </c>
       <c r="E25" s="14" t="n">
         <f aca="false">ROUND((D25-C25)*1440,0)</f>
@@ -4303,10 +4294,10 @@
         <v>46460</v>
       </c>
       <c r="C26" s="16" t="n">
-        <v>0.392361111111111</v>
+        <v>0.465277777777778</v>
       </c>
       <c r="D26" s="16" t="n">
-        <v>0.4375</v>
+        <v>0.510416666666667</v>
       </c>
       <c r="E26" s="14" t="n">
         <f aca="false">ROUND((D26-C26)*1440,0)</f>
@@ -4336,10 +4327,10 @@
         <v>46460</v>
       </c>
       <c r="C27" s="21" t="n">
-        <v>0.4375</v>
+        <v>0.510416666666667</v>
       </c>
       <c r="D27" s="21" t="n">
-        <v>0.444444444444444</v>
+        <v>0.517361111111111</v>
       </c>
       <c r="E27" s="19" t="n">
         <f aca="false">ROUND((D27-C27)*1440,0)</f>
@@ -4371,10 +4362,10 @@
         <v>46460</v>
       </c>
       <c r="C28" s="16" t="n">
-        <v>0.444444444444444</v>
+        <v>0.517361111111111</v>
       </c>
       <c r="D28" s="16" t="n">
-        <v>0.489583333333333</v>
+        <v>0.5625</v>
       </c>
       <c r="E28" s="14" t="n">
         <f aca="false">ROUND((D28-C28)*1440,0)</f>
@@ -4406,10 +4397,10 @@
         <v>46460</v>
       </c>
       <c r="C29" s="16" t="n">
-        <v>0.489583333333333</v>
+        <v>0.5625</v>
       </c>
       <c r="D29" s="16" t="n">
-        <v>0.510416666666667</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="E29" s="14" t="n">
         <f aca="false">ROUND((D29-C29)*1440,0)</f>
@@ -4439,10 +4430,10 @@
         <v>46460</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>0.510416666666667</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="D30" s="13" t="n">
-        <v>0.541666666666667</v>
+        <v>0.614583333333333</v>
       </c>
       <c r="E30" s="11" t="n">
         <f aca="false">ROUND((D30-C30)*1440,0)</f>
@@ -4472,14 +4463,14 @@
         <v>46460</v>
       </c>
       <c r="C31" s="16" t="n">
-        <v>0.541666666666667</v>
+        <v>0.614583333333333</v>
       </c>
       <c r="D31" s="16" t="n">
         <v>0.6875</v>
       </c>
       <c r="E31" s="14" t="n">
         <f aca="false">ROUND((D31-C31)*1440,0)</f>
-        <v>210</v>
+        <v>105</v>
       </c>
       <c r="F31" s="14" t="s">
         <v>101</v>
@@ -4661,69 +4652,69 @@
         <v>52</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="11" t="n">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B37" s="12" t="n">
+      <c r="B37" s="15" t="n">
         <f aca="false">Overview!$B$3+A37-1</f>
         <v>46461</v>
       </c>
-      <c r="C37" s="13" t="n">
+      <c r="C37" s="16" t="n">
         <v>0.291666666666667</v>
       </c>
-      <c r="D37" s="13" t="n">
+      <c r="D37" s="16" t="n">
         <v>0.3125</v>
       </c>
-      <c r="E37" s="11" t="n">
+      <c r="E37" s="14" t="n">
         <f aca="false">ROUND((D37-C37)*1440,0)</f>
         <v>30</v>
       </c>
-      <c r="F37" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="G37" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="H37" s="11"/>
-      <c r="I37" s="11"/>
-      <c r="J37" s="11" t="s">
+      <c r="F37" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="G37" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="H37" s="14"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="K37" s="18" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="14" t="n">
+      <c r="K37" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="B38" s="15" t="n">
+      <c r="B38" s="12" t="n">
         <f aca="false">Overview!$B$3+A38-1</f>
         <v>46461</v>
       </c>
-      <c r="C38" s="16" t="n">
+      <c r="C38" s="13" t="n">
         <v>0.3125</v>
       </c>
-      <c r="D38" s="16" t="n">
-        <v>0.322916666666667</v>
-      </c>
-      <c r="E38" s="14" t="n">
+      <c r="D38" s="13" t="n">
+        <v>0.354166666666667</v>
+      </c>
+      <c r="E38" s="11" t="n">
         <f aca="false">ROUND((D38-C38)*1440,0)</f>
-        <v>15</v>
-      </c>
-      <c r="F38" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="G38" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="H38" s="14"/>
-      <c r="I38" s="14"/>
-      <c r="J38" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G38" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
+      <c r="J38" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="K38" s="17" t="s">
+      <c r="K38" s="18" t="s">
         <v>52</v>
       </c>
     </row>
@@ -4736,97 +4727,97 @@
         <v>46461</v>
       </c>
       <c r="C39" s="16" t="n">
-        <v>0.322916666666667</v>
+        <v>0.354166666666667</v>
       </c>
       <c r="D39" s="16" t="n">
-        <v>0.333333333333333</v>
+        <v>0.375</v>
       </c>
       <c r="E39" s="14" t="n">
         <f aca="false">ROUND((D39-C39)*1440,0)</f>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>112</v>
+        <v>57</v>
       </c>
       <c r="G39" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="H39" s="14" t="s">
-        <v>113</v>
-      </c>
+      <c r="H39" s="14"/>
       <c r="I39" s="14"/>
       <c r="J39" s="14" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="K39" s="17" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="19" t="n">
+      <c r="A40" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B40" s="20" t="n">
+      <c r="B40" s="15" t="n">
         <f aca="false">Overview!$B$3+A40-1</f>
         <v>46461</v>
       </c>
-      <c r="C40" s="21" t="n">
-        <v>0.333333333333333</v>
-      </c>
-      <c r="D40" s="21" t="n">
-        <v>0.347222222222222</v>
-      </c>
-      <c r="E40" s="19" t="n">
+      <c r="C40" s="16" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D40" s="16" t="n">
+        <v>0.385416666666667</v>
+      </c>
+      <c r="E40" s="14" t="n">
         <f aca="false">ROUND((D40-C40)*1440,0)</f>
-        <v>20</v>
-      </c>
-      <c r="F40" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F40" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="G40" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="H40" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="I40" s="14"/>
+      <c r="J40" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="G40" s="19" t="s">
-        <v>113</v>
-      </c>
-      <c r="H40" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="I40" s="19"/>
-      <c r="J40" s="19" t="s">
-        <v>117</v>
-      </c>
-      <c r="K40" s="22" t="s">
+      <c r="K40" s="17" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="14" t="n">
+      <c r="A41" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="B41" s="15" t="n">
+      <c r="B41" s="20" t="n">
         <f aca="false">Overview!$B$3+A41-1</f>
         <v>46461</v>
       </c>
-      <c r="C41" s="16" t="n">
-        <v>0.347222222222222</v>
-      </c>
-      <c r="D41" s="16" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E41" s="14" t="n">
+      <c r="C41" s="21" t="n">
+        <v>0.385416666666667</v>
+      </c>
+      <c r="D41" s="21" t="n">
+        <v>0.399305555555556</v>
+      </c>
+      <c r="E41" s="19" t="n">
         <f aca="false">ROUND((D41-C41)*1440,0)</f>
-        <v>40</v>
-      </c>
-      <c r="F41" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="G41" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="F41" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="G41" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="H41" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="I41" s="19"/>
+      <c r="J41" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="H41" s="14"/>
-      <c r="I41" s="14"/>
-      <c r="J41" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="K41" s="17" t="s">
+      <c r="K41" s="22" t="s">
         <v>52</v>
       </c>
     </row>
@@ -4839,27 +4830,25 @@
         <v>46461</v>
       </c>
       <c r="C42" s="16" t="n">
-        <v>0.375</v>
+        <v>0.399305555555556</v>
       </c>
       <c r="D42" s="16" t="n">
-        <v>0.416666666666667</v>
+        <v>0.427083333333333</v>
       </c>
       <c r="E42" s="14" t="n">
         <f aca="false">ROUND((D42-C42)*1440,0)</f>
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="F42" s="14" t="s">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="G42" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="H42" s="14" t="s">
-        <v>94</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="H42" s="14"/>
       <c r="I42" s="14"/>
       <c r="J42" s="14" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K42" s="17" t="s">
         <v>52</v>
@@ -4874,22 +4863,24 @@
         <v>46461</v>
       </c>
       <c r="C43" s="16" t="n">
-        <v>0.416666666666667</v>
+        <v>0.427083333333333</v>
       </c>
       <c r="D43" s="16" t="n">
-        <v>0.458333333333333</v>
+        <v>0.46875</v>
       </c>
       <c r="E43" s="14" t="n">
         <f aca="false">ROUND((D43-C43)*1440,0)</f>
         <v>60</v>
       </c>
       <c r="F43" s="14" t="s">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="G43" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="H43" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="H43" s="14"/>
       <c r="I43" s="14"/>
       <c r="J43" s="14" t="s">
         <v>123</v>
@@ -4899,74 +4890,70 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="19" t="n">
+      <c r="A44" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B44" s="20" t="n">
+      <c r="B44" s="15" t="n">
         <f aca="false">Overview!$B$3+A44-1</f>
         <v>46461</v>
       </c>
-      <c r="C44" s="21" t="n">
-        <v>0.458333333333333</v>
-      </c>
-      <c r="D44" s="21" t="n">
-        <v>0.465277777777778</v>
-      </c>
-      <c r="E44" s="19" t="n">
+      <c r="C44" s="16" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="D44" s="16" t="n">
+        <v>0.510416666666667</v>
+      </c>
+      <c r="E44" s="14" t="n">
         <f aca="false">ROUND((D44-C44)*1440,0)</f>
-        <v>10</v>
-      </c>
-      <c r="F44" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="G44" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="F44" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="G44" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="H44" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="I44" s="19"/>
-      <c r="J44" s="19" t="s">
+      <c r="H44" s="14"/>
+      <c r="I44" s="14"/>
+      <c r="J44" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="K44" s="22" t="s">
+      <c r="K44" s="17" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="14" t="n">
+      <c r="A45" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="B45" s="15" t="n">
+      <c r="B45" s="20" t="n">
         <f aca="false">Overview!$B$3+A45-1</f>
         <v>46461</v>
       </c>
-      <c r="C45" s="16" t="n">
-        <v>0.465277777777778</v>
-      </c>
-      <c r="D45" s="16" t="n">
-        <v>0.475694444444444</v>
-      </c>
-      <c r="E45" s="14" t="n">
+      <c r="C45" s="21" t="n">
+        <v>0.510416666666667</v>
+      </c>
+      <c r="D45" s="21" t="n">
+        <v>0.517361111111111</v>
+      </c>
+      <c r="E45" s="19" t="n">
         <f aca="false">ROUND((D45-C45)*1440,0)</f>
-        <v>15</v>
-      </c>
-      <c r="F45" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G45" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="G45" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="H45" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="H45" s="14" t="s">
+      <c r="I45" s="19"/>
+      <c r="J45" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="I45" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="J45" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="K45" s="17" t="s">
+      <c r="K45" s="22" t="s">
         <v>52</v>
       </c>
     </row>
@@ -4979,93 +4966,97 @@
         <v>46461</v>
       </c>
       <c r="C46" s="16" t="n">
-        <v>0.475694444444444</v>
+        <v>0.517361111111111</v>
       </c>
       <c r="D46" s="16" t="n">
-        <v>0.510416666666667</v>
+        <v>0.527777777777778</v>
       </c>
       <c r="E46" s="14" t="n">
         <f aca="false">ROUND((D46-C46)*1440,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="F46" s="14" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G46" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="H46" s="14"/>
-      <c r="I46" s="14"/>
+        <v>89</v>
+      </c>
+      <c r="H46" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="I46" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="J46" s="14" t="s">
-        <v>59</v>
+        <v>127</v>
       </c>
       <c r="K46" s="17" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="11" t="n">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B47" s="12" t="n">
+      <c r="B47" s="15" t="n">
         <f aca="false">Overview!$B$3+A47-1</f>
         <v>46461</v>
       </c>
-      <c r="C47" s="13" t="n">
-        <v>0.510416666666667</v>
-      </c>
-      <c r="D47" s="13" t="n">
-        <v>0.541666666666667</v>
-      </c>
-      <c r="E47" s="11" t="n">
+      <c r="C47" s="16" t="n">
+        <v>0.527777777777778</v>
+      </c>
+      <c r="D47" s="16" t="n">
+        <v>0.552083333333333</v>
+      </c>
+      <c r="E47" s="14" t="n">
         <f aca="false">ROUND((D47-C47)*1440,0)</f>
-        <v>45</v>
-      </c>
-      <c r="F47" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="G47" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="H47" s="11"/>
-      <c r="I47" s="11"/>
-      <c r="J47" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="K47" s="18" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="F47" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="G47" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="H47" s="14"/>
+      <c r="I47" s="14"/>
+      <c r="J47" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="K47" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="B48" s="15" t="n">
+      <c r="B48" s="12" t="n">
         <f aca="false">Overview!$B$3+A48-1</f>
         <v>46461</v>
       </c>
-      <c r="C48" s="16" t="n">
-        <v>0.541666666666667</v>
-      </c>
-      <c r="D48" s="16" t="n">
-        <v>0.666666666666667</v>
-      </c>
-      <c r="E48" s="14" t="n">
+      <c r="C48" s="13" t="n">
+        <v>0.552083333333333</v>
+      </c>
+      <c r="D48" s="13" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="E48" s="11" t="n">
         <f aca="false">ROUND((D48-C48)*1440,0)</f>
-        <v>180</v>
-      </c>
-      <c r="F48" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="G48" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="H48" s="14"/>
-      <c r="I48" s="14"/>
-      <c r="J48" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="K48" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="G48" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H48" s="11"/>
+      <c r="I48" s="11"/>
+      <c r="J48" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="K48" s="18" t="s">
         <v>52</v>
       </c>
     </row>
@@ -5078,35 +5069,31 @@
         <v>46461</v>
       </c>
       <c r="C49" s="16" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="D49" s="16" t="n">
         <v>0.666666666666667</v>
-      </c>
-      <c r="D49" s="16" t="n">
-        <v>0.677083333333333</v>
       </c>
       <c r="E49" s="14" t="n">
         <f aca="false">ROUND((D49-C49)*1440,0)</f>
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="F49" s="14" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="G49" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="H49" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="I49" s="14" t="n">
-        <v>3</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="H49" s="14"/>
+      <c r="I49" s="14"/>
       <c r="J49" s="14" t="s">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="K49" s="17" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="14" t="n">
         <v>3</v>
       </c>
@@ -5115,23 +5102,27 @@
         <v>46461</v>
       </c>
       <c r="C50" s="16" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="D50" s="16" t="n">
         <v>0.677083333333333</v>
-      </c>
-      <c r="D50" s="16" t="n">
-        <v>0.708333333333333</v>
       </c>
       <c r="E50" s="14" t="n">
         <f aca="false">ROUND((D50-C50)*1440,0)</f>
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="F50" s="14" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="G50" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="H50" s="14"/>
-      <c r="I50" s="14"/>
+        <v>126</v>
+      </c>
+      <c r="H50" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="I50" s="14" t="n">
+        <v>3</v>
+      </c>
       <c r="J50" s="14" t="s">
         <v>131</v>
       </c>
@@ -5139,7 +5130,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="14" t="n">
         <v>3</v>
       </c>
@@ -5148,29 +5139,25 @@
         <v>46461</v>
       </c>
       <c r="C51" s="16" t="n">
+        <v>0.677083333333333</v>
+      </c>
+      <c r="D51" s="16" t="n">
         <v>0.708333333333333</v>
-      </c>
-      <c r="D51" s="16" t="n">
-        <v>0.715277777777778</v>
       </c>
       <c r="E51" s="14" t="n">
         <f aca="false">ROUND((D51-C51)*1440,0)</f>
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="F51" s="14" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="G51" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="H51" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="H51" s="14"/>
+      <c r="I51" s="14"/>
+      <c r="J51" s="14" t="s">
         <v>132</v>
-      </c>
-      <c r="I51" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="J51" s="14" t="s">
-        <v>133</v>
       </c>
       <c r="K51" s="17" t="s">
         <v>52</v>
@@ -5185,23 +5172,27 @@
         <v>46461</v>
       </c>
       <c r="C52" s="16" t="n">
+        <v>0.708333333333333</v>
+      </c>
+      <c r="D52" s="16" t="n">
         <v>0.715277777777778</v>
-      </c>
-      <c r="D52" s="16" t="n">
-        <v>0.736111111111111</v>
       </c>
       <c r="E52" s="14" t="n">
         <f aca="false">ROUND((D52-C52)*1440,0)</f>
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F52" s="14" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="G52" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="H52" s="14"/>
-      <c r="I52" s="14"/>
+        <v>130</v>
+      </c>
+      <c r="H52" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="I52" s="14" t="n">
+        <v>1</v>
+      </c>
       <c r="J52" s="14" t="s">
         <v>134</v>
       </c>
@@ -5218,29 +5209,25 @@
         <v>46461</v>
       </c>
       <c r="C53" s="16" t="n">
+        <v>0.715277777777778</v>
+      </c>
+      <c r="D53" s="16" t="n">
         <v>0.736111111111111</v>
-      </c>
-      <c r="D53" s="16" t="n">
-        <v>0.746527777777778</v>
       </c>
       <c r="E53" s="14" t="n">
         <f aca="false">ROUND((D53-C53)*1440,0)</f>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F53" s="14" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="G53" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="H53" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="H53" s="14"/>
+      <c r="I53" s="14"/>
+      <c r="J53" s="14" t="s">
         <v>135</v>
-      </c>
-      <c r="I53" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="J53" s="14" t="s">
-        <v>136</v>
       </c>
       <c r="K53" s="17" t="s">
         <v>52</v>
@@ -5255,25 +5242,29 @@
         <v>46461</v>
       </c>
       <c r="C54" s="16" t="n">
+        <v>0.736111111111111</v>
+      </c>
+      <c r="D54" s="16" t="n">
         <v>0.746527777777778</v>
-      </c>
-      <c r="D54" s="16" t="n">
-        <v>0.8125</v>
       </c>
       <c r="E54" s="14" t="n">
         <f aca="false">ROUND((D54-C54)*1440,0)</f>
-        <v>95</v>
+        <v>15</v>
       </c>
       <c r="F54" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G54" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="H54" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="I54" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="J54" s="14" t="s">
         <v>137</v>
-      </c>
-      <c r="G54" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="H54" s="14"/>
-      <c r="I54" s="14"/>
-      <c r="J54" s="14" t="s">
-        <v>138</v>
       </c>
       <c r="K54" s="17" t="s">
         <v>52</v>
@@ -5288,90 +5279,90 @@
         <v>46461</v>
       </c>
       <c r="C55" s="16" t="n">
+        <v>0.746527777777778</v>
+      </c>
+      <c r="D55" s="16" t="n">
         <v>0.8125</v>
-      </c>
-      <c r="D55" s="16" t="n">
-        <v>0.822916666666667</v>
       </c>
       <c r="E55" s="14" t="n">
         <f aca="false">ROUND((D55-C55)*1440,0)</f>
-        <v>15</v>
+        <v>95</v>
       </c>
       <c r="F55" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="G55" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="H55" s="14"/>
+      <c r="I55" s="14"/>
+      <c r="J55" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="G55" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="H55" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="I55" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="J55" s="14" t="s">
-        <v>140</v>
-      </c>
       <c r="K55" s="17" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="11" t="n">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B56" s="12" t="n">
+      <c r="B56" s="15" t="n">
         <f aca="false">Overview!$B$3+A56-1</f>
         <v>46461</v>
       </c>
-      <c r="C56" s="13" t="n">
-        <v>0.833333333333333</v>
-      </c>
-      <c r="D56" s="13" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="E56" s="11" t="n">
+      <c r="C56" s="16" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="D56" s="16" t="n">
+        <v>0.822916666666667</v>
+      </c>
+      <c r="E56" s="14" t="n">
         <f aca="false">ROUND((D56-C56)*1440,0)</f>
-        <v>60</v>
-      </c>
-      <c r="F56" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="G56" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F56" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="G56" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="H56" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="I56" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="H56" s="11"/>
-      <c r="I56" s="11"/>
-      <c r="J56" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="K56" s="18" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K56" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B57" s="12" t="n">
         <f aca="false">Overview!$B$3+A57-1</f>
-        <v>46462</v>
+        <v>46461</v>
       </c>
       <c r="C57" s="13" t="n">
-        <v>0.291666666666667</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="D57" s="13" t="n">
-        <v>0.322916666666667</v>
+        <v>0.875</v>
       </c>
       <c r="E57" s="11" t="n">
         <f aca="false">ROUND((D57-C57)*1440,0)</f>
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="G57" s="11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H57" s="11"/>
       <c r="I57" s="11"/>
@@ -5383,35 +5374,35 @@
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="14" t="n">
+      <c r="A58" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="B58" s="15" t="n">
+      <c r="B58" s="12" t="n">
         <f aca="false">Overview!$B$3+A58-1</f>
         <v>46462</v>
       </c>
-      <c r="C58" s="16" t="n">
-        <v>0.322916666666667</v>
-      </c>
-      <c r="D58" s="16" t="n">
-        <v>0.333333333333333</v>
-      </c>
-      <c r="E58" s="14" t="n">
+      <c r="C58" s="13" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="D58" s="13" t="n">
+        <v>0.354166666666667</v>
+      </c>
+      <c r="E58" s="11" t="n">
         <f aca="false">ROUND((D58-C58)*1440,0)</f>
-        <v>15</v>
-      </c>
-      <c r="F58" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="G58" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="H58" s="14"/>
-      <c r="I58" s="14"/>
-      <c r="J58" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="K58" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="F58" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G58" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="H58" s="11"/>
+      <c r="I58" s="11"/>
+      <c r="J58" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="K58" s="18" t="s">
         <v>52</v>
       </c>
     </row>
@@ -5424,29 +5415,25 @@
         <v>46462</v>
       </c>
       <c r="C59" s="16" t="n">
-        <v>0.333333333333333</v>
+        <v>0.354166666666667</v>
       </c>
       <c r="D59" s="16" t="n">
-        <v>0.395833333333333</v>
+        <v>0.375</v>
       </c>
       <c r="E59" s="14" t="n">
         <f aca="false">ROUND((D59-C59)*1440,0)</f>
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="F59" s="14" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G59" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="H59" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="I59" s="14" t="n">
-        <v>50</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="H59" s="14"/>
+      <c r="I59" s="14"/>
       <c r="J59" s="14" t="s">
-        <v>144</v>
+        <v>83</v>
       </c>
       <c r="K59" s="17" t="s">
         <v>52</v>
@@ -5461,95 +5448,99 @@
         <v>46462</v>
       </c>
       <c r="C60" s="16" t="n">
-        <v>0.395833333333333</v>
+        <v>0.375</v>
       </c>
       <c r="D60" s="16" t="n">
-        <v>0.458333333333333</v>
+        <v>0.4375</v>
       </c>
       <c r="E60" s="14" t="n">
         <f aca="false">ROUND((D60-C60)*1440,0)</f>
         <v>90</v>
       </c>
       <c r="F60" s="14" t="s">
-        <v>145</v>
+        <v>53</v>
       </c>
       <c r="G60" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="H60" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="H60" s="14"/>
-      <c r="I60" s="14"/>
+      <c r="I60" s="14" t="n">
+        <v>50</v>
+      </c>
       <c r="J60" s="14" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K60" s="17" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="19" t="n">
+      <c r="A61" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="B61" s="20" t="n">
+      <c r="B61" s="15" t="n">
         <f aca="false">Overview!$B$3+A61-1</f>
         <v>46462</v>
       </c>
-      <c r="C61" s="21" t="n">
-        <v>0.458333333333333</v>
-      </c>
-      <c r="D61" s="21" t="n">
-        <v>0.493055555555556</v>
-      </c>
-      <c r="E61" s="19" t="n">
+      <c r="C61" s="16" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="D61" s="16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E61" s="14" t="n">
         <f aca="false">ROUND((D61-C61)*1440,0)</f>
-        <v>50</v>
-      </c>
-      <c r="F61" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="G61" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="F61" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="G61" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="H61" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="I61" s="19"/>
-      <c r="J61" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="K61" s="22" t="s">
+      <c r="H61" s="14"/>
+      <c r="I61" s="14"/>
+      <c r="J61" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="K61" s="17" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="14" t="n">
+      <c r="A62" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="B62" s="15" t="n">
+      <c r="B62" s="20" t="n">
         <f aca="false">Overview!$B$3+A62-1</f>
         <v>46462</v>
       </c>
-      <c r="C62" s="16" t="n">
-        <v>0.493055555555556</v>
-      </c>
-      <c r="D62" s="16" t="n">
-        <v>0.510416666666667</v>
-      </c>
-      <c r="E62" s="14" t="n">
+      <c r="C62" s="21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D62" s="21" t="n">
+        <v>0.534722222222222</v>
+      </c>
+      <c r="E62" s="19" t="n">
         <f aca="false">ROUND((D62-C62)*1440,0)</f>
-        <v>25</v>
-      </c>
-      <c r="F62" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="G62" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="F62" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="G62" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="H62" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="H62" s="14"/>
-      <c r="I62" s="14"/>
-      <c r="J62" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="K62" s="17" t="s">
+      <c r="I62" s="19"/>
+      <c r="J62" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="K62" s="22" t="s">
         <v>52</v>
       </c>
     </row>
@@ -5562,97 +5553,97 @@
         <v>46462</v>
       </c>
       <c r="C63" s="16" t="n">
-        <v>0.510416666666667</v>
+        <v>0.534722222222222</v>
       </c>
       <c r="D63" s="16" t="n">
-        <v>0.541666666666667</v>
+        <v>0.552083333333333</v>
       </c>
       <c r="E63" s="14" t="n">
         <f aca="false">ROUND((D63-C63)*1440,0)</f>
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="F63" s="14" t="s">
-        <v>53</v>
+        <v>145</v>
       </c>
       <c r="G63" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="H63" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="I63" s="14" t="n">
-        <v>14</v>
-      </c>
+      <c r="H63" s="14"/>
+      <c r="I63" s="14"/>
       <c r="J63" s="14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K63" s="17" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="11" t="n">
+      <c r="A64" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="B64" s="12" t="n">
+      <c r="B64" s="15" t="n">
         <f aca="false">Overview!$B$3+A64-1</f>
         <v>46462</v>
       </c>
-      <c r="C64" s="13" t="n">
-        <v>0.541666666666667</v>
-      </c>
-      <c r="D64" s="13" t="n">
+      <c r="C64" s="16" t="n">
+        <v>0.552083333333333</v>
+      </c>
+      <c r="D64" s="16" t="n">
         <v>0.583333333333333</v>
       </c>
-      <c r="E64" s="11" t="n">
+      <c r="E64" s="14" t="n">
         <f aca="false">ROUND((D64-C64)*1440,0)</f>
-        <v>60</v>
-      </c>
-      <c r="F64" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="G64" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="H64" s="11"/>
-      <c r="I64" s="11"/>
-      <c r="J64" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="K64" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="F64" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G64" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="H64" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="I64" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="J64" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="K64" s="17" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="14" t="n">
+      <c r="A65" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="B65" s="15" t="n">
+      <c r="B65" s="12" t="n">
         <f aca="false">Overview!$B$3+A65-1</f>
         <v>46462</v>
       </c>
-      <c r="C65" s="16" t="n">
+      <c r="C65" s="13" t="n">
         <v>0.583333333333333</v>
       </c>
-      <c r="D65" s="16" t="n">
-        <v>0.697916666666667</v>
-      </c>
-      <c r="E65" s="14" t="n">
+      <c r="D65" s="13" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E65" s="11" t="n">
         <f aca="false">ROUND((D65-C65)*1440,0)</f>
-        <v>165</v>
-      </c>
-      <c r="F65" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="G65" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="H65" s="14"/>
-      <c r="I65" s="14"/>
-      <c r="J65" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="K65" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="F65" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="G65" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="H65" s="11"/>
+      <c r="I65" s="11"/>
+      <c r="J65" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="K65" s="18" t="s">
         <v>52</v>
       </c>
     </row>
@@ -5665,330 +5656,330 @@
         <v>46462</v>
       </c>
       <c r="C66" s="16" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="D66" s="16" t="n">
         <v>0.697916666666667</v>
-      </c>
-      <c r="D66" s="16" t="n">
-        <v>0.708333333333333</v>
       </c>
       <c r="E66" s="14" t="n">
         <f aca="false">ROUND((D66-C66)*1440,0)</f>
-        <v>15</v>
+        <v>105</v>
       </c>
       <c r="F66" s="14" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="G66" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="H66" s="14" t="s">
-        <v>157</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="H66" s="14"/>
       <c r="I66" s="14"/>
       <c r="J66" s="14" t="s">
-        <v>158</v>
+        <v>101</v>
       </c>
       <c r="K66" s="17" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="19" t="n">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="B67" s="20" t="n">
+      <c r="B67" s="15" t="n">
         <f aca="false">Overview!$B$3+A67-1</f>
         <v>46462</v>
       </c>
-      <c r="C67" s="21" t="n">
+      <c r="C67" s="16" t="n">
+        <v>0.697916666666667</v>
+      </c>
+      <c r="D67" s="16" t="n">
         <v>0.708333333333333</v>
       </c>
-      <c r="D67" s="21" t="n">
-        <v>0.770833333333333</v>
-      </c>
-      <c r="E67" s="19" t="n">
+      <c r="E67" s="14" t="n">
         <f aca="false">ROUND((D67-C67)*1440,0)</f>
-        <v>90</v>
-      </c>
-      <c r="F67" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="G67" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="H67" s="19"/>
-      <c r="I67" s="19"/>
-      <c r="J67" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="K67" s="22" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="F67" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="G67" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="H67" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="I67" s="14"/>
+      <c r="J67" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="K67" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="B68" s="15" t="n">
+      <c r="B68" s="20" t="n">
         <f aca="false">Overview!$B$3+A68-1</f>
         <v>46462</v>
       </c>
-      <c r="C68" s="16" t="n">
+      <c r="C68" s="21" t="n">
+        <v>0.708333333333333</v>
+      </c>
+      <c r="D68" s="21" t="n">
         <v>0.770833333333333</v>
       </c>
-      <c r="D68" s="16" t="n">
-        <v>0.833333333333333</v>
-      </c>
-      <c r="E68" s="14" t="n">
+      <c r="E68" s="19" t="n">
         <f aca="false">ROUND((D68-C68)*1440,0)</f>
         <v>90</v>
       </c>
-      <c r="F68" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="G68" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="H68" s="14"/>
-      <c r="I68" s="14"/>
-      <c r="J68" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="K68" s="17" t="s">
+      <c r="F68" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="G68" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="H68" s="19"/>
+      <c r="I68" s="19"/>
+      <c r="J68" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="K68" s="22" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="11" t="n">
+      <c r="A69" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="B69" s="12" t="n">
+      <c r="B69" s="15" t="n">
         <f aca="false">Overview!$B$3+A69-1</f>
         <v>46462</v>
       </c>
-      <c r="C69" s="13" t="n">
+      <c r="C69" s="16" t="n">
+        <v>0.770833333333333</v>
+      </c>
+      <c r="D69" s="16" t="n">
         <v>0.833333333333333</v>
       </c>
-      <c r="D69" s="13" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="E69" s="11" t="n">
+      <c r="E69" s="14" t="n">
         <f aca="false">ROUND((D69-C69)*1440,0)</f>
-        <v>60</v>
-      </c>
-      <c r="F69" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="G69" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="H69" s="11"/>
-      <c r="I69" s="11"/>
-      <c r="J69" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="K69" s="18" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>90</v>
+      </c>
+      <c r="F69" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="G69" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="H69" s="14"/>
+      <c r="I69" s="14"/>
+      <c r="J69" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="K69" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B70" s="12" t="n">
         <f aca="false">Overview!$B$3+A70-1</f>
-        <v>46463</v>
+        <v>46462</v>
       </c>
       <c r="C70" s="13" t="n">
-        <v>0.291666666666667</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="D70" s="13" t="n">
-        <v>0.322916666666667</v>
+        <v>0.875</v>
       </c>
       <c r="E70" s="11" t="n">
         <f aca="false">ROUND((D70-C70)*1440,0)</f>
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="G70" s="11" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="H70" s="11"/>
       <c r="I70" s="11"/>
       <c r="J70" s="11" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K70" s="18" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="14" t="n">
+      <c r="A71" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="B71" s="15" t="n">
+      <c r="B71" s="12" t="n">
         <f aca="false">Overview!$B$3+A71-1</f>
         <v>46463</v>
       </c>
-      <c r="C71" s="16" t="n">
-        <v>0.322916666666667</v>
-      </c>
-      <c r="D71" s="16" t="n">
-        <v>0.395833333333333</v>
-      </c>
-      <c r="E71" s="14" t="n">
+      <c r="C71" s="13" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="D71" s="13" t="n">
+        <v>0.354166666666667</v>
+      </c>
+      <c r="E71" s="11" t="n">
         <f aca="false">ROUND((D71-C71)*1440,0)</f>
-        <v>105</v>
-      </c>
-      <c r="F71" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G71" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="H71" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="I71" s="14" t="n">
-        <v>50</v>
-      </c>
-      <c r="J71" s="14" t="s">
-        <v>167</v>
-      </c>
-      <c r="K71" s="17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="F71" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G71" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="H71" s="11"/>
+      <c r="I71" s="11"/>
+      <c r="J71" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="K71" s="18" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B72" s="20" t="n">
+      <c r="B72" s="15" t="n">
         <f aca="false">Overview!$B$3+A72-1</f>
         <v>46463</v>
       </c>
-      <c r="C72" s="21" t="n">
-        <v>0.395833333333333</v>
-      </c>
-      <c r="D72" s="21" t="n">
-        <v>0.541666666666667</v>
-      </c>
-      <c r="E72" s="19" t="n">
+      <c r="C72" s="16" t="n">
+        <v>0.354166666666667</v>
+      </c>
+      <c r="D72" s="16" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="E72" s="14" t="n">
         <f aca="false">ROUND((D72-C72)*1440,0)</f>
-        <v>210</v>
-      </c>
-      <c r="F72" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="G72" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="H72" s="19"/>
-      <c r="I72" s="19"/>
-      <c r="J72" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="K72" s="22" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="F72" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="G72" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="H72" s="14"/>
+      <c r="I72" s="14"/>
+      <c r="J72" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="K72" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B73" s="12" t="n">
+      <c r="B73" s="15" t="n">
         <f aca="false">Overview!$B$3+A73-1</f>
         <v>46463</v>
       </c>
-      <c r="C73" s="13" t="n">
-        <v>0.541666666666667</v>
-      </c>
-      <c r="D73" s="13" t="n">
-        <v>0.583333333333333</v>
-      </c>
-      <c r="E73" s="11" t="n">
+      <c r="C73" s="16" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D73" s="16" t="n">
+        <v>0.447916666666667</v>
+      </c>
+      <c r="E73" s="14" t="n">
         <f aca="false">ROUND((D73-C73)*1440,0)</f>
-        <v>60</v>
-      </c>
-      <c r="F73" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="G73" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="H73" s="11"/>
-      <c r="I73" s="11"/>
-      <c r="J73" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="K73" s="18" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="14" t="n">
+        <v>105</v>
+      </c>
+      <c r="F73" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G73" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="H73" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="I73" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="J73" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="K73" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="B74" s="15" t="n">
+      <c r="B74" s="20" t="n">
         <f aca="false">Overview!$B$3+A74-1</f>
         <v>46463</v>
       </c>
-      <c r="C74" s="16" t="n">
-        <v>0.583333333333333</v>
-      </c>
-      <c r="D74" s="16" t="n">
-        <v>0.604166666666667</v>
-      </c>
-      <c r="E74" s="14" t="n">
+      <c r="C74" s="21" t="n">
+        <v>0.447916666666667</v>
+      </c>
+      <c r="D74" s="21" t="n">
+        <v>0.572916666666667</v>
+      </c>
+      <c r="E74" s="19" t="n">
         <f aca="false">ROUND((D74-C74)*1440,0)</f>
-        <v>30</v>
-      </c>
-      <c r="F74" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="G74" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="H74" s="14"/>
-      <c r="I74" s="14"/>
-      <c r="J74" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="K74" s="17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="14" t="n">
+        <v>180</v>
+      </c>
+      <c r="F74" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="G74" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="H74" s="19"/>
+      <c r="I74" s="19"/>
+      <c r="J74" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="K74" s="22" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="B75" s="15" t="n">
+      <c r="B75" s="12" t="n">
         <f aca="false">Overview!$B$3+A75-1</f>
         <v>46463</v>
       </c>
-      <c r="C75" s="16" t="n">
+      <c r="C75" s="13" t="n">
+        <v>0.572916666666667</v>
+      </c>
+      <c r="D75" s="13" t="n">
         <v>0.604166666666667</v>
       </c>
-      <c r="D75" s="16" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E75" s="14" t="n">
+      <c r="E75" s="11" t="n">
         <f aca="false">ROUND((D75-C75)*1440,0)</f>
-        <v>30</v>
-      </c>
-      <c r="F75" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="G75" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="H75" s="14"/>
-      <c r="I75" s="14"/>
-      <c r="J75" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="K75" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="F75" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="G75" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="H75" s="11"/>
+      <c r="I75" s="11"/>
+      <c r="J75" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="K75" s="18" t="s">
         <v>52</v>
       </c>
     </row>
@@ -6001,35 +5992,31 @@
         <v>46463</v>
       </c>
       <c r="C76" s="16" t="n">
+        <v>0.604166666666667</v>
+      </c>
+      <c r="D76" s="16" t="n">
         <v>0.625</v>
-      </c>
-      <c r="D76" s="16" t="n">
-        <v>0.635416666666667</v>
       </c>
       <c r="E76" s="14" t="n">
         <f aca="false">ROUND((D76-C76)*1440,0)</f>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F76" s="14" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G76" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="H76" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="I76" s="14" t="n">
-        <v>2</v>
-      </c>
+      <c r="H76" s="14"/>
+      <c r="I76" s="14"/>
       <c r="J76" s="14" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="K76" s="17" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="14" t="n">
         <v>5</v>
       </c>
@@ -6038,31 +6025,35 @@
         <v>46463</v>
       </c>
       <c r="C77" s="16" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="D77" s="16" t="n">
         <v>0.635416666666667</v>
-      </c>
-      <c r="D77" s="16" t="n">
-        <v>0.666666666666667</v>
       </c>
       <c r="E77" s="14" t="n">
         <f aca="false">ROUND((D77-C77)*1440,0)</f>
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="F77" s="14" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="G77" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="H77" s="14"/>
-      <c r="I77" s="14"/>
+        <v>173</v>
+      </c>
+      <c r="H77" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="I77" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="J77" s="14" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="K77" s="17" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="14" t="n">
         <v>5</v>
       </c>
@@ -6071,25 +6062,25 @@
         <v>46463</v>
       </c>
       <c r="C78" s="16" t="n">
+        <v>0.635416666666667</v>
+      </c>
+      <c r="D78" s="16" t="n">
         <v>0.666666666666667</v>
-      </c>
-      <c r="D78" s="16" t="n">
-        <v>0.729166666666667</v>
       </c>
       <c r="E78" s="14" t="n">
         <f aca="false">ROUND((D78-C78)*1440,0)</f>
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="F78" s="14" t="s">
-        <v>180</v>
+        <v>65</v>
       </c>
       <c r="G78" s="14" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="H78" s="14"/>
       <c r="I78" s="14"/>
       <c r="J78" s="14" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="K78" s="17" t="s">
         <v>52</v>
@@ -6104,130 +6095,126 @@
         <v>46463</v>
       </c>
       <c r="C79" s="16" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="D79" s="16" t="n">
         <v>0.729166666666667</v>
-      </c>
-      <c r="D79" s="16" t="n">
-        <v>0.833333333333333</v>
       </c>
       <c r="E79" s="14" t="n">
         <f aca="false">ROUND((D79-C79)*1440,0)</f>
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="F79" s="14" t="s">
-        <v>101</v>
+        <v>179</v>
       </c>
       <c r="G79" s="14" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="H79" s="14"/>
       <c r="I79" s="14"/>
       <c r="J79" s="14" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K79" s="17" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="11" t="n">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B80" s="12" t="n">
+      <c r="B80" s="15" t="n">
         <f aca="false">Overview!$B$3+A80-1</f>
         <v>46463</v>
       </c>
-      <c r="C80" s="13" t="n">
+      <c r="C80" s="16" t="n">
+        <v>0.729166666666667</v>
+      </c>
+      <c r="D80" s="16" t="n">
         <v>0.833333333333333</v>
       </c>
-      <c r="D80" s="13" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="E80" s="11" t="n">
+      <c r="E80" s="14" t="n">
         <f aca="false">ROUND((D80-C80)*1440,0)</f>
-        <v>60</v>
-      </c>
-      <c r="F80" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="G80" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="H80" s="11"/>
-      <c r="I80" s="11"/>
-      <c r="J80" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="K80" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="F80" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="G80" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="H80" s="14"/>
+      <c r="I80" s="14"/>
+      <c r="J80" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="K80" s="17" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B81" s="12" t="n">
         <f aca="false">Overview!$B$3+A81-1</f>
-        <v>46464</v>
+        <v>46463</v>
       </c>
       <c r="C81" s="13" t="n">
-        <v>0.302083333333333</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="D81" s="13" t="n">
-        <v>0.322916666666667</v>
+        <v>0.875</v>
       </c>
       <c r="E81" s="11" t="n">
         <f aca="false">ROUND((D81-C81)*1440,0)</f>
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F81" s="11" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="G81" s="11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H81" s="11"/>
       <c r="I81" s="11"/>
       <c r="J81" s="11" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="K81" s="18" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="14" t="n">
+      <c r="A82" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="B82" s="15" t="n">
+      <c r="B82" s="12" t="n">
         <f aca="false">Overview!$B$3+A82-1</f>
         <v>46464</v>
       </c>
-      <c r="C82" s="16" t="n">
-        <v>0.322916666666667</v>
-      </c>
-      <c r="D82" s="16" t="n">
-        <v>0.395833333333333</v>
-      </c>
-      <c r="E82" s="14" t="n">
+      <c r="C82" s="13" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="D82" s="13" t="n">
+        <v>0.354166666666667</v>
+      </c>
+      <c r="E82" s="11" t="n">
         <f aca="false">ROUND((D82-C82)*1440,0)</f>
-        <v>105</v>
-      </c>
-      <c r="F82" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G82" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="H82" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="I82" s="14" t="n">
-        <v>70</v>
-      </c>
-      <c r="J82" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="K82" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="F82" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G82" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="H82" s="11"/>
+      <c r="I82" s="11"/>
+      <c r="J82" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="K82" s="18" t="s">
         <v>52</v>
       </c>
     </row>
@@ -6240,25 +6227,25 @@
         <v>46464</v>
       </c>
       <c r="C83" s="16" t="n">
-        <v>0.395833333333333</v>
+        <v>0.354166666666667</v>
       </c>
       <c r="D83" s="16" t="n">
-        <v>0.427083333333333</v>
+        <v>0.375</v>
       </c>
       <c r="E83" s="14" t="n">
         <f aca="false">ROUND((D83-C83)*1440,0)</f>
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F83" s="14" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="G83" s="14" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="H83" s="14"/>
       <c r="I83" s="14"/>
       <c r="J83" s="14" t="s">
-        <v>190</v>
+        <v>83</v>
       </c>
       <c r="K83" s="17" t="s">
         <v>52</v>
@@ -6273,10 +6260,10 @@
         <v>46464</v>
       </c>
       <c r="C84" s="16" t="n">
-        <v>0.427083333333333</v>
+        <v>0.375</v>
       </c>
       <c r="D84" s="16" t="n">
-        <v>0.510416666666667</v>
+        <v>0.458333333333333</v>
       </c>
       <c r="E84" s="14" t="n">
         <f aca="false">ROUND((D84-C84)*1440,0)</f>
@@ -6286,16 +6273,16 @@
         <v>53</v>
       </c>
       <c r="G84" s="14" t="s">
-        <v>191</v>
+        <v>24</v>
       </c>
       <c r="H84" s="14" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="I84" s="14" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J84" s="14" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="K84" s="17" t="s">
         <v>52</v>
@@ -6310,95 +6297,97 @@
         <v>46464</v>
       </c>
       <c r="C85" s="16" t="n">
-        <v>0.510416666666667</v>
+        <v>0.458333333333333</v>
       </c>
       <c r="D85" s="16" t="n">
-        <v>0.583333333333333</v>
+        <v>0.489583333333333</v>
       </c>
       <c r="E85" s="14" t="n">
         <f aca="false">ROUND((D85-C85)*1440,0)</f>
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="F85" s="14" t="s">
-        <v>194</v>
+        <v>65</v>
       </c>
       <c r="G85" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="H85" s="14" t="s">
-        <v>195</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="H85" s="14"/>
       <c r="I85" s="14"/>
       <c r="J85" s="14" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="K85" s="17" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="11" t="n">
+      <c r="A86" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B86" s="12" t="n">
+      <c r="B86" s="15" t="n">
         <f aca="false">Overview!$B$3+A86-1</f>
         <v>46464</v>
       </c>
-      <c r="C86" s="13" t="n">
-        <v>0.583333333333333</v>
-      </c>
-      <c r="D86" s="13" t="n">
-        <v>0.614583333333333</v>
-      </c>
-      <c r="E86" s="11" t="n">
+      <c r="C86" s="16" t="n">
+        <v>0.489583333333333</v>
+      </c>
+      <c r="D86" s="16" t="n">
+        <v>0.572916666666667</v>
+      </c>
+      <c r="E86" s="14" t="n">
         <f aca="false">ROUND((D86-C86)*1440,0)</f>
-        <v>45</v>
-      </c>
-      <c r="F86" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="F86" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G86" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="H86" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="I86" s="14" t="n">
         <v>60</v>
       </c>
-      <c r="G86" s="11" t="s">
-        <v>197</v>
-      </c>
-      <c r="H86" s="11"/>
-      <c r="I86" s="11"/>
-      <c r="J86" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="K86" s="18" t="s">
+      <c r="J86" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="K86" s="17" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="14" t="n">
+      <c r="A87" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="B87" s="15" t="n">
+      <c r="B87" s="12" t="n">
         <f aca="false">Overview!$B$3+A87-1</f>
         <v>46464</v>
       </c>
-      <c r="C87" s="16" t="n">
-        <v>0.614583333333333</v>
-      </c>
-      <c r="D87" s="16" t="n">
-        <v>0.645833333333333</v>
-      </c>
-      <c r="E87" s="14" t="n">
+      <c r="C87" s="13" t="n">
+        <v>0.572916666666667</v>
+      </c>
+      <c r="D87" s="13" t="n">
+        <v>0.604166666666667</v>
+      </c>
+      <c r="E87" s="11" t="n">
         <f aca="false">ROUND((D87-C87)*1440,0)</f>
         <v>45</v>
       </c>
-      <c r="F87" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="G87" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="H87" s="14"/>
-      <c r="I87" s="14"/>
-      <c r="J87" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="K87" s="17" t="s">
+      <c r="F87" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="G87" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="H87" s="11"/>
+      <c r="I87" s="11"/>
+      <c r="J87" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="K87" s="18" t="s">
         <v>52</v>
       </c>
     </row>
@@ -6411,29 +6400,27 @@
         <v>46464</v>
       </c>
       <c r="C88" s="16" t="n">
-        <v>0.645833333333333</v>
+        <v>0.604166666666667</v>
       </c>
       <c r="D88" s="16" t="n">
-        <v>0.770833333333333</v>
+        <v>0.65625</v>
       </c>
       <c r="E88" s="14" t="n">
         <f aca="false">ROUND((D88-C88)*1440,0)</f>
-        <v>180</v>
+        <v>75</v>
       </c>
       <c r="F88" s="14" t="s">
-        <v>53</v>
+        <v>195</v>
       </c>
       <c r="G88" s="14" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H88" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="I88" s="14" t="n">
-        <v>82</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="I88" s="14"/>
       <c r="J88" s="14" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="K88" s="17" t="s">
         <v>52</v>
@@ -6448,163 +6435,163 @@
         <v>46464</v>
       </c>
       <c r="C89" s="16" t="n">
-        <v>0.770833333333333</v>
+        <v>0.65625</v>
       </c>
       <c r="D89" s="16" t="n">
-        <v>0.833333333333333</v>
+        <v>0.677083333333333</v>
       </c>
       <c r="E89" s="14" t="n">
         <f aca="false">ROUND((D89-C89)*1440,0)</f>
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="F89" s="14" t="s">
-        <v>101</v>
+        <v>179</v>
       </c>
       <c r="G89" s="14" t="s">
-        <v>166</v>
+        <v>198</v>
       </c>
       <c r="H89" s="14"/>
       <c r="I89" s="14"/>
       <c r="J89" s="14" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="K89" s="17" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="11" t="n">
+      <c r="A90" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B90" s="12" t="n">
+      <c r="B90" s="15" t="n">
         <f aca="false">Overview!$B$3+A90-1</f>
         <v>46464</v>
       </c>
-      <c r="C90" s="13" t="n">
+      <c r="C90" s="16" t="n">
+        <v>0.677083333333333</v>
+      </c>
+      <c r="D90" s="16" t="n">
+        <v>0.802083333333333</v>
+      </c>
+      <c r="E90" s="14" t="n">
+        <f aca="false">ROUND((D90-C90)*1440,0)</f>
+        <v>180</v>
+      </c>
+      <c r="F90" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G90" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H90" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="I90" s="14" t="n">
+        <v>82</v>
+      </c>
+      <c r="J90" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="K90" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B91" s="15" t="n">
+        <f aca="false">Overview!$B$3+A91-1</f>
+        <v>46464</v>
+      </c>
+      <c r="C91" s="16" t="n">
+        <v>0.802083333333333</v>
+      </c>
+      <c r="D91" s="16" t="n">
         <v>0.833333333333333</v>
       </c>
-      <c r="D90" s="13" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="E90" s="11" t="n">
-        <f aca="false">ROUND((D90-C90)*1440,0)</f>
-        <v>60</v>
-      </c>
-      <c r="F90" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="G90" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="H90" s="11"/>
-      <c r="I90" s="11"/>
-      <c r="J90" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="K90" s="18" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="B91" s="12" t="n">
-        <f aca="false">Overview!$B$3+A91-1</f>
-        <v>46465</v>
-      </c>
-      <c r="C91" s="13" t="n">
-        <v>0.291666666666667</v>
-      </c>
-      <c r="D91" s="13" t="n">
-        <v>0.322916666666667</v>
-      </c>
-      <c r="E91" s="11" t="n">
+      <c r="E91" s="14" t="n">
         <f aca="false">ROUND((D91-C91)*1440,0)</f>
         <v>45</v>
       </c>
-      <c r="F91" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="G91" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="H91" s="11"/>
-      <c r="I91" s="11"/>
-      <c r="J91" s="11" t="s">
-        <v>204</v>
-      </c>
-      <c r="K91" s="18" t="s">
+      <c r="F91" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="G91" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="H91" s="14"/>
+      <c r="I91" s="14"/>
+      <c r="J91" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="K91" s="17" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="B92" s="15" t="n">
+      <c r="A92" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B92" s="12" t="n">
         <f aca="false">Overview!$B$3+A92-1</f>
-        <v>46465</v>
-      </c>
-      <c r="C92" s="16" t="n">
-        <v>0.322916666666667</v>
-      </c>
-      <c r="D92" s="16" t="n">
-        <v>0.364583333333333</v>
-      </c>
-      <c r="E92" s="14" t="n">
+        <v>46464</v>
+      </c>
+      <c r="C92" s="13" t="n">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="D92" s="13" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="E92" s="11" t="n">
         <f aca="false">ROUND((D92-C92)*1440,0)</f>
         <v>60</v>
       </c>
-      <c r="F92" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G92" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="H92" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="I92" s="14" t="n">
-        <v>30</v>
-      </c>
-      <c r="J92" s="14" t="s">
-        <v>206</v>
-      </c>
-      <c r="K92" s="17" t="s">
+      <c r="F92" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="G92" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="H92" s="11"/>
+      <c r="I92" s="11"/>
+      <c r="J92" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="K92" s="18" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="14" t="n">
+      <c r="A93" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="B93" s="15" t="n">
+      <c r="B93" s="12" t="n">
         <f aca="false">Overview!$B$3+A93-1</f>
         <v>46465</v>
       </c>
-      <c r="C93" s="16" t="n">
-        <v>0.364583333333333</v>
-      </c>
-      <c r="D93" s="16" t="n">
-        <v>0.395833333333333</v>
-      </c>
-      <c r="E93" s="14" t="n">
+      <c r="C93" s="13" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="D93" s="13" t="n">
+        <v>0.354166666666667</v>
+      </c>
+      <c r="E93" s="11" t="n">
         <f aca="false">ROUND((D93-C93)*1440,0)</f>
-        <v>45</v>
-      </c>
-      <c r="F93" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="G93" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="H93" s="14"/>
-      <c r="I93" s="14"/>
-      <c r="J93" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="K93" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="F93" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G93" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="H93" s="11"/>
+      <c r="I93" s="11"/>
+      <c r="J93" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="K93" s="18" t="s">
         <v>52</v>
       </c>
     </row>
@@ -6617,29 +6604,25 @@
         <v>46465</v>
       </c>
       <c r="C94" s="16" t="n">
-        <v>0.395833333333333</v>
+        <v>0.354166666666667</v>
       </c>
       <c r="D94" s="16" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="E94" s="14" t="n">
         <f aca="false">ROUND((D94-C94)*1440,0)</f>
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F94" s="14" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G94" s="14" t="s">
-        <v>208</v>
-      </c>
-      <c r="H94" s="14" t="s">
-        <v>209</v>
-      </c>
-      <c r="I94" s="14" t="n">
-        <v>35</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="H94" s="14"/>
+      <c r="I94" s="14"/>
       <c r="J94" s="14" t="s">
-        <v>210</v>
+        <v>83</v>
       </c>
       <c r="K94" s="17" t="s">
         <v>52</v>
@@ -6654,25 +6637,29 @@
         <v>46465</v>
       </c>
       <c r="C95" s="16" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="D95" s="16" t="n">
-        <v>0.46875</v>
+        <v>0.416666666666667</v>
       </c>
       <c r="E95" s="14" t="n">
         <f aca="false">ROUND((D95-C95)*1440,0)</f>
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="F95" s="14" t="s">
-        <v>180</v>
+        <v>53</v>
       </c>
       <c r="G95" s="14" t="s">
-        <v>209</v>
-      </c>
-      <c r="H95" s="14"/>
-      <c r="I95" s="14"/>
+        <v>165</v>
+      </c>
+      <c r="H95" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="I95" s="14" t="n">
+        <v>30</v>
+      </c>
       <c r="J95" s="14" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="K95" s="17" t="s">
         <v>52</v>
@@ -6687,29 +6674,25 @@
         <v>46465</v>
       </c>
       <c r="C96" s="16" t="n">
-        <v>0.46875</v>
+        <v>0.416666666666667</v>
       </c>
       <c r="D96" s="16" t="n">
-        <v>0.520833333333333</v>
+        <v>0.447916666666667</v>
       </c>
       <c r="E96" s="14" t="n">
         <f aca="false">ROUND((D96-C96)*1440,0)</f>
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="F96" s="14" t="s">
-        <v>53</v>
+        <v>179</v>
       </c>
       <c r="G96" s="14" t="s">
-        <v>212</v>
-      </c>
-      <c r="H96" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="I96" s="14" t="n">
-        <v>40</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="H96" s="14"/>
+      <c r="I96" s="14"/>
       <c r="J96" s="14" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="K96" s="17" t="s">
         <v>52</v>
@@ -6724,60 +6707,64 @@
         <v>46465</v>
       </c>
       <c r="C97" s="16" t="n">
-        <v>0.520833333333333</v>
+        <v>0.447916666666667</v>
       </c>
       <c r="D97" s="16" t="n">
-        <v>0.541666666666667</v>
+        <v>0.489583333333333</v>
       </c>
       <c r="E97" s="14" t="n">
         <f aca="false">ROUND((D97-C97)*1440,0)</f>
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F97" s="14" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G97" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="H97" s="14"/>
-      <c r="I97" s="14"/>
+        <v>206</v>
+      </c>
+      <c r="H97" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="I97" s="14" t="n">
+        <v>35</v>
+      </c>
       <c r="J97" s="14" t="s">
-        <v>174</v>
+        <v>208</v>
       </c>
       <c r="K97" s="17" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="11" t="n">
+      <c r="A98" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="B98" s="12" t="n">
+      <c r="B98" s="15" t="n">
         <f aca="false">Overview!$B$3+A98-1</f>
         <v>46465</v>
       </c>
-      <c r="C98" s="13" t="n">
-        <v>0.541666666666667</v>
-      </c>
-      <c r="D98" s="13" t="n">
-        <v>0.583333333333333</v>
-      </c>
-      <c r="E98" s="11" t="n">
+      <c r="C98" s="16" t="n">
+        <v>0.489583333333333</v>
+      </c>
+      <c r="D98" s="16" t="n">
+        <v>0.520833333333333</v>
+      </c>
+      <c r="E98" s="14" t="n">
         <f aca="false">ROUND((D98-C98)*1440,0)</f>
-        <v>60</v>
-      </c>
-      <c r="F98" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="G98" s="11" t="s">
-        <v>215</v>
-      </c>
-      <c r="H98" s="11"/>
-      <c r="I98" s="11"/>
-      <c r="J98" s="11" t="s">
-        <v>216</v>
-      </c>
-      <c r="K98" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="F98" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="G98" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="H98" s="14"/>
+      <c r="I98" s="14"/>
+      <c r="J98" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="K98" s="17" t="s">
         <v>52</v>
       </c>
     </row>
@@ -6790,472 +6777,468 @@
         <v>46465</v>
       </c>
       <c r="C99" s="16" t="n">
-        <v>0.583333333333333</v>
+        <v>0.520833333333333</v>
       </c>
       <c r="D99" s="16" t="n">
-        <v>0.59375</v>
+        <v>0.572916666666667</v>
       </c>
       <c r="E99" s="14" t="n">
         <f aca="false">ROUND((D99-C99)*1440,0)</f>
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="F99" s="14" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G99" s="14" t="s">
-        <v>217</v>
-      </c>
-      <c r="H99" s="14"/>
-      <c r="I99" s="14"/>
+        <v>210</v>
+      </c>
+      <c r="H99" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="I99" s="14" t="n">
+        <v>40</v>
+      </c>
       <c r="J99" s="14" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="K99" s="17" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="19" t="n">
+      <c r="A100" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="B100" s="20" t="n">
+      <c r="B100" s="15" t="n">
         <f aca="false">Overview!$B$3+A100-1</f>
         <v>46465</v>
       </c>
-      <c r="C100" s="21" t="n">
-        <v>0.59375</v>
-      </c>
-      <c r="D100" s="21" t="n">
-        <v>0.621527777777778</v>
-      </c>
-      <c r="E100" s="19" t="n">
+      <c r="C100" s="16" t="n">
+        <v>0.572916666666667</v>
+      </c>
+      <c r="D100" s="16" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="E100" s="14" t="n">
         <f aca="false">ROUND((D100-C100)*1440,0)</f>
-        <v>40</v>
-      </c>
-      <c r="F100" s="19" t="s">
-        <v>219</v>
-      </c>
-      <c r="G100" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="H100" s="19" t="s">
-        <v>220</v>
-      </c>
-      <c r="I100" s="19"/>
-      <c r="J100" s="19" t="s">
-        <v>221</v>
-      </c>
-      <c r="K100" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="F100" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="G100" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="H100" s="14"/>
+      <c r="I100" s="14"/>
+      <c r="J100" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="K100" s="17" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="14" t="n">
+      <c r="A101" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="B101" s="15" t="n">
+      <c r="B101" s="12" t="n">
         <f aca="false">Overview!$B$3+A101-1</f>
         <v>46465</v>
       </c>
-      <c r="C101" s="16" t="n">
-        <v>0.621527777777778</v>
-      </c>
-      <c r="D101" s="16" t="n">
-        <v>0.645833333333333</v>
-      </c>
-      <c r="E101" s="14" t="n">
+      <c r="C101" s="13" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="D101" s="13" t="n">
+        <v>0.614583333333333</v>
+      </c>
+      <c r="E101" s="11" t="n">
         <f aca="false">ROUND((D101-C101)*1440,0)</f>
-        <v>35</v>
-      </c>
-      <c r="F101" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="G101" s="14" t="s">
-        <v>220</v>
-      </c>
-      <c r="H101" s="14"/>
-      <c r="I101" s="14"/>
-      <c r="J101" s="14" t="s">
-        <v>222</v>
-      </c>
-      <c r="K101" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="F101" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="G101" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="H101" s="11"/>
+      <c r="I101" s="11"/>
+      <c r="J101" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="K101" s="18" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="19" t="n">
+      <c r="A102" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="B102" s="20" t="n">
+      <c r="B102" s="15" t="n">
         <f aca="false">Overview!$B$3+A102-1</f>
         <v>46465</v>
       </c>
-      <c r="C102" s="21" t="n">
-        <v>0.645833333333333</v>
-      </c>
-      <c r="D102" s="21" t="n">
-        <v>0.659722222222222</v>
-      </c>
-      <c r="E102" s="19" t="n">
+      <c r="C102" s="16" t="n">
+        <v>0.614583333333333</v>
+      </c>
+      <c r="D102" s="16" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E102" s="14" t="n">
         <f aca="false">ROUND((D102-C102)*1440,0)</f>
-        <v>20</v>
-      </c>
-      <c r="F102" s="19" t="s">
-        <v>219</v>
-      </c>
-      <c r="G102" s="19" t="s">
-        <v>220</v>
-      </c>
-      <c r="H102" s="19" t="s">
-        <v>223</v>
-      </c>
-      <c r="I102" s="19"/>
-      <c r="J102" s="19" t="s">
-        <v>224</v>
-      </c>
-      <c r="K102" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="F102" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="G102" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="H102" s="14"/>
+      <c r="I102" s="14"/>
+      <c r="J102" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="K102" s="17" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="14" t="n">
+      <c r="A103" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="B103" s="15" t="n">
+      <c r="B103" s="20" t="n">
         <f aca="false">Overview!$B$3+A103-1</f>
         <v>46465</v>
       </c>
-      <c r="C103" s="16" t="n">
-        <v>0.659722222222222</v>
-      </c>
-      <c r="D103" s="16" t="n">
-        <v>0.6875</v>
-      </c>
-      <c r="E103" s="14" t="n">
+      <c r="C103" s="21" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="D103" s="21" t="n">
+        <v>0.652777777777778</v>
+      </c>
+      <c r="E103" s="19" t="n">
         <f aca="false">ROUND((D103-C103)*1440,0)</f>
         <v>40</v>
       </c>
-      <c r="F103" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="G103" s="14" t="s">
-        <v>223</v>
-      </c>
-      <c r="H103" s="14"/>
-      <c r="I103" s="14"/>
-      <c r="J103" s="14" t="s">
-        <v>225</v>
-      </c>
-      <c r="K103" s="17" t="s">
+      <c r="F103" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="G103" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="H103" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="I103" s="19"/>
+      <c r="J103" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="K103" s="22" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="19" t="n">
+      <c r="A104" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="B104" s="20" t="n">
+      <c r="B104" s="15" t="n">
         <f aca="false">Overview!$B$3+A104-1</f>
         <v>46465</v>
       </c>
-      <c r="C104" s="21" t="n">
-        <v>0.6875</v>
-      </c>
-      <c r="D104" s="21" t="n">
-        <v>0.722222222222222</v>
-      </c>
-      <c r="E104" s="19" t="n">
+      <c r="C104" s="16" t="n">
+        <v>0.652777777777778</v>
+      </c>
+      <c r="D104" s="16" t="n">
+        <v>0.673611111111111</v>
+      </c>
+      <c r="E104" s="14" t="n">
         <f aca="false">ROUND((D104-C104)*1440,0)</f>
-        <v>50</v>
-      </c>
-      <c r="F104" s="19" t="s">
-        <v>219</v>
-      </c>
-      <c r="G104" s="19" t="s">
-        <v>223</v>
-      </c>
-      <c r="H104" s="19" t="s">
-        <v>226</v>
-      </c>
-      <c r="I104" s="19"/>
-      <c r="J104" s="19" t="s">
-        <v>227</v>
-      </c>
-      <c r="K104" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="F104" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="G104" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="H104" s="14"/>
+      <c r="I104" s="14"/>
+      <c r="J104" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="K104" s="17" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="14" t="n">
+      <c r="A105" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="B105" s="15" t="n">
+      <c r="B105" s="20" t="n">
         <f aca="false">Overview!$B$3+A105-1</f>
         <v>46465</v>
       </c>
-      <c r="C105" s="16" t="n">
-        <v>0.722222222222222</v>
-      </c>
-      <c r="D105" s="16" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E105" s="14" t="n">
+      <c r="C105" s="21" t="n">
+        <v>0.673611111111111</v>
+      </c>
+      <c r="D105" s="21" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="E105" s="19" t="n">
         <f aca="false">ROUND((D105-C105)*1440,0)</f>
-        <v>40</v>
-      </c>
-      <c r="F105" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="G105" s="14" t="s">
-        <v>226</v>
-      </c>
-      <c r="H105" s="14"/>
-      <c r="I105" s="14"/>
-      <c r="J105" s="14" t="s">
-        <v>228</v>
-      </c>
-      <c r="K105" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="F105" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="G105" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="H105" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="I105" s="19"/>
+      <c r="J105" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="K105" s="22" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="19" t="n">
+      <c r="A106" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="B106" s="20" t="n">
+      <c r="B106" s="15" t="n">
         <f aca="false">Overview!$B$3+A106-1</f>
         <v>46465</v>
       </c>
-      <c r="C106" s="21" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="D106" s="21" t="n">
-        <v>0.770833333333333</v>
-      </c>
-      <c r="E106" s="19" t="n">
+      <c r="C106" s="16" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="D106" s="16" t="n">
+        <v>0.711805555555556</v>
+      </c>
+      <c r="E106" s="14" t="n">
         <f aca="false">ROUND((D106-C106)*1440,0)</f>
-        <v>30</v>
-      </c>
-      <c r="F106" s="19" t="s">
-        <v>219</v>
-      </c>
-      <c r="G106" s="19" t="s">
-        <v>226</v>
-      </c>
-      <c r="H106" s="19" t="s">
-        <v>213</v>
-      </c>
-      <c r="I106" s="19"/>
-      <c r="J106" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="K106" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="F106" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="G106" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="H106" s="14"/>
+      <c r="I106" s="14"/>
+      <c r="J106" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="K106" s="17" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="14" t="n">
+      <c r="A107" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="B107" s="15" t="n">
+      <c r="B107" s="20" t="n">
         <f aca="false">Overview!$B$3+A107-1</f>
         <v>46465</v>
       </c>
-      <c r="C107" s="16" t="n">
-        <v>0.770833333333333</v>
-      </c>
-      <c r="D107" s="16" t="n">
-        <v>0.8125</v>
-      </c>
-      <c r="E107" s="14" t="n">
+      <c r="C107" s="21" t="n">
+        <v>0.711805555555556</v>
+      </c>
+      <c r="D107" s="21" t="n">
+        <v>0.746527777777778</v>
+      </c>
+      <c r="E107" s="19" t="n">
         <f aca="false">ROUND((D107-C107)*1440,0)</f>
-        <v>60</v>
-      </c>
-      <c r="F107" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="G107" s="14" t="s">
-        <v>230</v>
-      </c>
-      <c r="H107" s="14"/>
-      <c r="I107" s="14"/>
-      <c r="J107" s="14" t="s">
-        <v>231</v>
-      </c>
-      <c r="K107" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F107" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="G107" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="H107" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="I107" s="19"/>
+      <c r="J107" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="K107" s="22" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="11" t="n">
+      <c r="A108" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="B108" s="12" t="n">
+      <c r="B108" s="15" t="n">
         <f aca="false">Overview!$B$3+A108-1</f>
         <v>46465</v>
       </c>
-      <c r="C108" s="13" t="n">
-        <v>0.833333333333333</v>
-      </c>
-      <c r="D108" s="13" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="E108" s="11" t="n">
+      <c r="C108" s="16" t="n">
+        <v>0.746527777777778</v>
+      </c>
+      <c r="D108" s="16" t="n">
+        <v>0.767361111111111</v>
+      </c>
+      <c r="E108" s="14" t="n">
         <f aca="false">ROUND((D108-C108)*1440,0)</f>
-        <v>60</v>
-      </c>
-      <c r="F108" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="G108" s="11" t="s">
-        <v>215</v>
-      </c>
-      <c r="H108" s="11"/>
-      <c r="I108" s="11"/>
-      <c r="J108" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="K108" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="F108" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="G108" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="H108" s="14"/>
+      <c r="I108" s="14"/>
+      <c r="J108" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="K108" s="17" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="B109" s="12" t="n">
+      <c r="A109" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="B109" s="20" t="n">
         <f aca="false">Overview!$B$3+A109-1</f>
-        <v>46466</v>
-      </c>
-      <c r="C109" s="13" t="n">
-        <v>0.291666666666667</v>
-      </c>
-      <c r="D109" s="13" t="n">
-        <v>0.322916666666667</v>
-      </c>
-      <c r="E109" s="11" t="n">
+        <v>46465</v>
+      </c>
+      <c r="C109" s="21" t="n">
+        <v>0.767361111111111</v>
+      </c>
+      <c r="D109" s="21" t="n">
+        <v>0.788194444444444</v>
+      </c>
+      <c r="E109" s="19" t="n">
         <f aca="false">ROUND((D109-C109)*1440,0)</f>
-        <v>45</v>
-      </c>
-      <c r="F109" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="G109" s="11" t="s">
-        <v>215</v>
-      </c>
-      <c r="H109" s="11"/>
-      <c r="I109" s="11"/>
-      <c r="J109" s="11" t="s">
-        <v>204</v>
-      </c>
-      <c r="K109" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="F109" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="G109" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="H109" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="I109" s="19"/>
+      <c r="J109" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="K109" s="22" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B110" s="15" t="n">
         <f aca="false">Overview!$B$3+A110-1</f>
-        <v>46466</v>
+        <v>46465</v>
       </c>
       <c r="C110" s="16" t="n">
-        <v>0.322916666666667</v>
+        <v>0.791666666666667</v>
       </c>
       <c r="D110" s="16" t="n">
-        <v>0.4375</v>
+        <v>0.8125</v>
       </c>
       <c r="E110" s="14" t="n">
         <f aca="false">ROUND((D110-C110)*1440,0)</f>
-        <v>165</v>
+        <v>30</v>
       </c>
       <c r="F110" s="14" t="s">
-        <v>53</v>
+        <v>113</v>
       </c>
       <c r="G110" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="H110" s="14" t="s">
-        <v>232</v>
-      </c>
-      <c r="I110" s="14" t="n">
-        <v>95</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="H110" s="14"/>
+      <c r="I110" s="14"/>
       <c r="J110" s="14" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="K110" s="17" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="14" t="n">
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="B111" s="12" t="n">
+        <f aca="false">Overview!$B$3+A111-1</f>
+        <v>46465</v>
+      </c>
+      <c r="C111" s="13" t="n">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="D111" s="13" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="E111" s="11" t="n">
+        <f aca="false">ROUND((D111-C111)*1440,0)</f>
+        <v>60</v>
+      </c>
+      <c r="F111" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="G111" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="H111" s="11"/>
+      <c r="I111" s="11"/>
+      <c r="J111" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="K111" s="18" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="B111" s="15" t="n">
-        <f aca="false">Overview!$B$3+A111-1</f>
-        <v>46466</v>
-      </c>
-      <c r="C111" s="16" t="n">
-        <v>0.4375</v>
-      </c>
-      <c r="D111" s="16" t="n">
-        <v>0.489583333333333</v>
-      </c>
-      <c r="E111" s="14" t="n">
-        <f aca="false">ROUND((D111-C111)*1440,0)</f>
-        <v>75</v>
-      </c>
-      <c r="F111" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="G111" s="14" t="s">
-        <v>234</v>
-      </c>
-      <c r="H111" s="14"/>
-      <c r="I111" s="14"/>
-      <c r="J111" s="14" t="s">
-        <v>235</v>
-      </c>
-      <c r="K111" s="17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="B112" s="15" t="n">
+      <c r="B112" s="12" t="n">
         <f aca="false">Overview!$B$3+A112-1</f>
         <v>46466</v>
       </c>
-      <c r="C112" s="16" t="n">
-        <v>0.489583333333333</v>
-      </c>
-      <c r="D112" s="16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E112" s="14" t="n">
+      <c r="C112" s="13" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="D112" s="13" t="n">
+        <v>0.354166666666667</v>
+      </c>
+      <c r="E112" s="11" t="n">
         <f aca="false">ROUND((D112-C112)*1440,0)</f>
-        <v>15</v>
-      </c>
-      <c r="F112" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G112" s="14" t="s">
-        <v>234</v>
-      </c>
-      <c r="H112" s="14" t="s">
-        <v>236</v>
-      </c>
-      <c r="I112" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="J112" s="14" t="s">
-        <v>237</v>
-      </c>
-      <c r="K112" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="F112" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G112" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="H112" s="11"/>
+      <c r="I112" s="11"/>
+      <c r="J112" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="K112" s="18" t="s">
         <v>52</v>
       </c>
     </row>
@@ -7268,60 +7251,64 @@
         <v>46466</v>
       </c>
       <c r="C113" s="16" t="n">
-        <v>0.5</v>
+        <v>0.354166666666667</v>
       </c>
       <c r="D113" s="16" t="n">
-        <v>0.527777777777778</v>
+        <v>0.375</v>
       </c>
       <c r="E113" s="14" t="n">
         <f aca="false">ROUND((D113-C113)*1440,0)</f>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F113" s="14" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="G113" s="14" t="s">
-        <v>236</v>
+        <v>211</v>
       </c>
       <c r="H113" s="14"/>
       <c r="I113" s="14"/>
       <c r="J113" s="14" t="s">
-        <v>238</v>
+        <v>83</v>
       </c>
       <c r="K113" s="17" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="11" t="n">
+      <c r="A114" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="B114" s="12" t="n">
+      <c r="B114" s="15" t="n">
         <f aca="false">Overview!$B$3+A114-1</f>
         <v>46466</v>
       </c>
-      <c r="C114" s="13" t="n">
-        <v>0.53125</v>
-      </c>
-      <c r="D114" s="13" t="n">
-        <v>0.572916666666667</v>
-      </c>
-      <c r="E114" s="11" t="n">
+      <c r="C114" s="16" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D114" s="16" t="n">
+        <v>0.489583333333333</v>
+      </c>
+      <c r="E114" s="14" t="n">
         <f aca="false">ROUND((D114-C114)*1440,0)</f>
-        <v>60</v>
-      </c>
-      <c r="F114" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="G114" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="H114" s="11"/>
-      <c r="I114" s="11"/>
-      <c r="J114" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="K114" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="F114" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G114" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="H114" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="I114" s="14" t="n">
+        <v>95</v>
+      </c>
+      <c r="J114" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="K114" s="17" t="s">
         <v>52</v>
       </c>
     </row>
@@ -7334,25 +7321,25 @@
         <v>46466</v>
       </c>
       <c r="C115" s="16" t="n">
-        <v>0.572916666666667</v>
+        <v>0.489583333333333</v>
       </c>
       <c r="D115" s="16" t="n">
-        <v>0.614583333333333</v>
+        <v>0.53125</v>
       </c>
       <c r="E115" s="14" t="n">
         <f aca="false">ROUND((D115-C115)*1440,0)</f>
         <v>60</v>
       </c>
       <c r="F115" s="14" t="s">
-        <v>137</v>
+        <v>65</v>
       </c>
       <c r="G115" s="14" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="H115" s="14"/>
       <c r="I115" s="14"/>
       <c r="J115" s="14" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="K115" s="17" t="s">
         <v>52</v>
@@ -7367,35 +7354,35 @@
         <v>46466</v>
       </c>
       <c r="C116" s="16" t="n">
-        <v>0.614583333333333</v>
+        <v>0.53125</v>
       </c>
       <c r="D116" s="16" t="n">
-        <v>0.645833333333333</v>
+        <v>0.541666666666667</v>
       </c>
       <c r="E116" s="14" t="n">
         <f aca="false">ROUND((D116-C116)*1440,0)</f>
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="F116" s="14" t="s">
         <v>53</v>
       </c>
       <c r="G116" s="14" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="H116" s="14" t="s">
-        <v>148</v>
+        <v>234</v>
       </c>
       <c r="I116" s="14" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J116" s="14" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="K116" s="17" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="14" t="n">
         <v>8</v>
       </c>
@@ -7404,37 +7391,173 @@
         <v>46466</v>
       </c>
       <c r="C117" s="16" t="n">
-        <v>0.645833333333333</v>
+        <v>0.541666666666667</v>
       </c>
       <c r="D117" s="16" t="n">
-        <v>0.666666666666667</v>
+        <v>0.569444444444444</v>
       </c>
       <c r="E117" s="14" t="n">
         <f aca="false">ROUND((D117-C117)*1440,0)</f>
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F117" s="14" t="s">
-        <v>245</v>
+        <v>65</v>
       </c>
       <c r="G117" s="14" t="s">
-        <v>148</v>
+        <v>234</v>
       </c>
       <c r="H117" s="14"/>
       <c r="I117" s="14"/>
       <c r="J117" s="14" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="K117" s="17" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="5" t="s">
-        <v>247</v>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="B118" s="12" t="n">
+        <f aca="false">Overview!$B$3+A118-1</f>
+        <v>46466</v>
+      </c>
+      <c r="C118" s="13" t="n">
+        <v>0.572916666666667</v>
+      </c>
+      <c r="D118" s="13" t="n">
+        <v>0.614583333333333</v>
+      </c>
+      <c r="E118" s="11" t="n">
+        <f aca="false">ROUND((D118-C118)*1440,0)</f>
+        <v>60</v>
+      </c>
+      <c r="F118" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="G118" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="H118" s="11"/>
+      <c r="I118" s="11"/>
+      <c r="J118" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="K118" s="18" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B119" s="15" t="n">
+        <f aca="false">Overview!$B$3+A119-1</f>
+        <v>46466</v>
+      </c>
+      <c r="C119" s="16" t="n">
+        <v>0.614583333333333</v>
+      </c>
+      <c r="D119" s="16" t="n">
+        <v>0.645833333333333</v>
+      </c>
+      <c r="E119" s="14" t="n">
+        <f aca="false">ROUND((D119-C119)*1440,0)</f>
+        <v>45</v>
+      </c>
+      <c r="F119" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="G119" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="H119" s="14"/>
+      <c r="I119" s="14"/>
+      <c r="J119" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="K119" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B120" s="15" t="n">
+        <f aca="false">Overview!$B$3+A120-1</f>
+        <v>46466</v>
+      </c>
+      <c r="C120" s="16" t="n">
+        <v>0.645833333333333</v>
+      </c>
+      <c r="D120" s="16" t="n">
+        <v>0.677083333333333</v>
+      </c>
+      <c r="E120" s="14" t="n">
+        <f aca="false">ROUND((D120-C120)*1440,0)</f>
+        <v>45</v>
+      </c>
+      <c r="F120" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G120" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="H120" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="I120" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="J120" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="K120" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B121" s="15" t="n">
+        <f aca="false">Overview!$B$3+A121-1</f>
+        <v>46466</v>
+      </c>
+      <c r="C121" s="16" t="n">
+        <v>0.677083333333333</v>
+      </c>
+      <c r="D121" s="16" t="n">
+        <v>0.697916666666667</v>
+      </c>
+      <c r="E121" s="14" t="n">
+        <f aca="false">ROUND((D121-C121)*1440,0)</f>
+        <v>30</v>
+      </c>
+      <c r="F121" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="G121" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="H121" s="14"/>
+      <c r="I121" s="14"/>
+      <c r="J121" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="K121" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="5" t="s">
+        <v>245</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:K117"/>
+  <autoFilter ref="A4:K121"/>
   <hyperlinks>
     <hyperlink ref="K6" r:id="rId1" display="Open map"/>
     <hyperlink ref="K7" r:id="rId2" display="Open map"/>
@@ -7548,6 +7671,10 @@
     <hyperlink ref="K115" r:id="rId110" display="Open map"/>
     <hyperlink ref="K116" r:id="rId111" display="Open map"/>
     <hyperlink ref="K117" r:id="rId112" display="Open map"/>
+    <hyperlink ref="K118" r:id="rId113" display="Open map"/>
+    <hyperlink ref="K119" r:id="rId114" display="Open map"/>
+    <hyperlink ref="K120" r:id="rId115" display="Open map"/>
+    <hyperlink ref="K121" r:id="rId116" display="Open map"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -7556,7 +7683,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId113"/>
+  <drawing r:id="rId117"/>
 </worksheet>
 </file>
 
@@ -7578,7 +7705,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7586,19 +7713,19 @@
         <v>5</v>
       </c>
       <c r="B3" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="D3" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="E3" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="F3" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7609,16 +7736,16 @@
         <v>46</v>
       </c>
       <c r="C4" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="E4" s="14" t="s">
         <v>254</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="F4" s="14" t="s">
         <v>255</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="F4" s="14" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7629,16 +7756,16 @@
         <v>60</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D5" s="14" t="s">
         <v>61</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7649,16 +7776,16 @@
         <v>80</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D6" s="14" t="s">
         <v>61</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7669,16 +7796,16 @@
         <v>46</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D7" s="14" t="s">
         <v>61</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7689,16 +7816,16 @@
         <v>60</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D8" s="14" t="s">
         <v>99</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7709,16 +7836,16 @@
         <v>80</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D9" s="14" t="s">
         <v>99</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7729,16 +7856,16 @@
         <v>46</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="D10" s="14" t="s">
         <v>99</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7749,16 +7876,16 @@
         <v>60</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7769,16 +7896,16 @@
         <v>80</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7789,16 +7916,16 @@
         <v>46</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7809,16 +7936,16 @@
         <v>60</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>153</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7829,16 +7956,16 @@
         <v>80</v>
       </c>
       <c r="C15" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="D15" s="14" t="s">
         <v>271</v>
       </c>
-      <c r="D15" s="14" t="s">
-        <v>274</v>
-      </c>
       <c r="E15" s="14" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7849,16 +7976,16 @@
         <v>46</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7869,16 +7996,16 @@
         <v>60</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D17" s="14" t="s">
         <v>171</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7889,16 +8016,16 @@
         <v>80</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D18" s="14" t="s">
         <v>173</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7909,16 +8036,16 @@
         <v>46</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D19" s="14" t="s">
         <v>173</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7929,16 +8056,16 @@
         <v>60</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7949,16 +8076,16 @@
         <v>80</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7969,16 +8096,16 @@
         <v>46</v>
       </c>
       <c r="C22" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="E22" s="14" t="s">
         <v>272</v>
       </c>
-      <c r="D22" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="E22" s="14" t="s">
-        <v>275</v>
-      </c>
       <c r="F22" s="14" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7989,16 +8116,16 @@
         <v>60</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8009,16 +8136,16 @@
         <v>80</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8029,16 +8156,16 @@
         <v>46</v>
       </c>
       <c r="C25" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="E25" s="14" t="s">
         <v>272</v>
       </c>
-      <c r="D25" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="E25" s="14" t="s">
-        <v>275</v>
-      </c>
       <c r="F25" s="14" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8049,21 +8176,21 @@
         <v>60</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
   </sheetData>
@@ -8092,112 +8219,112 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -8227,198 +8354,198 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>315</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>316</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>317</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
+        <v>316</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>317</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>318</v>
+      </c>
+      <c r="D2" s="14" t="s">
         <v>319</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>320</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>321</v>
-      </c>
-      <c r="D2" s="14" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
+        <v>320</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>321</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>322</v>
+      </c>
+      <c r="D3" s="14" t="s">
         <v>323</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>324</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>325</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
+        <v>324</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>325</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>326</v>
+      </c>
+      <c r="D4" s="14" t="s">
         <v>327</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>328</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>329</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
+        <v>328</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>329</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>330</v>
+      </c>
+      <c r="D5" s="14" t="s">
         <v>331</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>332</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>333</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>333</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>334</v>
+      </c>
+      <c r="D6" s="14" t="s">
         <v>335</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>336</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>337</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>337</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>338</v>
+      </c>
+      <c r="D7" s="14" t="s">
         <v>339</v>
       </c>
-      <c r="B7" s="14" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="s">
         <v>340</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="B8" s="14" t="s">
         <v>341</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="C8" s="14" t="s">
         <v>342</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14" t="s">
+      <c r="D8" s="14" t="s">
         <v>343</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>344</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>345</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
+        <v>344</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>345</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>346</v>
+      </c>
+      <c r="D9" s="14" t="s">
         <v>347</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>348</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>349</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
+        <v>348</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>349</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>350</v>
+      </c>
+      <c r="D10" s="14" t="s">
         <v>351</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>352</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>353</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
+        <v>352</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>354</v>
+      </c>
+      <c r="D11" s="14" t="s">
         <v>355</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>356</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>357</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
+        <v>356</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>357</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>358</v>
+      </c>
+      <c r="D12" s="14" t="s">
         <v>359</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>360</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>361</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
+        <v>360</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>361</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>362</v>
+      </c>
+      <c r="D13" s="14" t="s">
         <v>363</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>364</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>365</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>365</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>366</v>
+      </c>
+      <c r="D14" s="14" t="s">
         <v>367</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>368</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>369</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>370</v>
       </c>
     </row>
   </sheetData>
@@ -8446,207 +8573,207 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
+        <v>371</v>
+      </c>
+      <c r="B6" s="14" t="s">
         <v>374</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
+        <v>381</v>
+      </c>
+      <c r="B15" s="14" t="s">
         <v>384</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
+        <v>389</v>
+      </c>
+      <c r="B22" s="14" t="s">
         <v>392</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="14" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="14" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
+        <v>395</v>
+      </c>
+      <c r="B27" s="14" t="s">
         <v>398</v>
-      </c>
-      <c r="B27" s="14" t="s">
-        <v>401</v>
       </c>
     </row>
   </sheetData>
@@ -8677,246 +8804,246 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
+        <v>400</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="D3" s="10" t="s">
         <v>403</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="E3" s="10" t="s">
         <v>404</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>405</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>406</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
+        <v>405</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>406</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>407</v>
+      </c>
+      <c r="D4" s="14" t="s">
         <v>408</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>409</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>410</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>411</v>
       </c>
       <c r="E4" s="23"/>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="E5" s="23"/>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="E6" s="23"/>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
+        <v>415</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>416</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>417</v>
+      </c>
+      <c r="D7" s="14" t="s">
         <v>418</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>419</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>420</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>421</v>
       </c>
       <c r="E7" s="23"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="E8" s="23"/>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
+        <v>422</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>423</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>424</v>
+      </c>
+      <c r="D9" s="14" t="s">
         <v>425</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>426</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>427</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>428</v>
       </c>
       <c r="E9" s="23"/>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C10" s="14" t="s">
+        <v>424</v>
+      </c>
+      <c r="D10" s="14" t="s">
         <v>427</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>430</v>
       </c>
       <c r="E10" s="23"/>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="E11" s="23"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
+        <v>428</v>
+      </c>
+      <c r="B12" s="14" t="s">
         <v>431</v>
       </c>
-      <c r="B12" s="14" t="s">
-        <v>434</v>
-      </c>
       <c r="C12" s="14" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E12" s="23"/>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
+        <v>433</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>434</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>435</v>
+      </c>
+      <c r="D13" s="14" t="s">
         <v>436</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>437</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>438</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>439</v>
       </c>
       <c r="E13" s="23"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E14" s="23"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E15" s="23"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D16" s="14"/>
       <c r="E16" s="23"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="E17" s="23"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E18" s="23"/>
     </row>
@@ -8945,146 +9072,146 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
+        <v>452</v>
+      </c>
+      <c r="B4" s="14" t="s">
         <v>455</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
+        <v>459</v>
+      </c>
+      <c r="B10" s="14" t="s">
         <v>462</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
   </sheetData>
@@ -9112,34 +9239,34 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9147,55 +9274,55 @@
         <v>93</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
     </row>
   </sheetData>

--- a/docs/itineraries/vaishno-devi-kashmir-8d-plan.xlsx
+++ b/docs/itineraries/vaishno-devi-kashmir-8d-plan.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="609">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="616">
   <si>
     <t xml:space="preserve">8 Days Vaishno Devi &amp; Kashmir Pilgrimage – Overview</t>
   </si>
@@ -100,28 +100,40 @@
     <t xml:space="preserve">Katra</t>
   </si>
   <si>
-    <t xml:space="preserve">Katra → Jammu Airport → flight to Srinagar → Dal Lake shikara</t>
+    <t xml:space="preserve">Katra → Jammu Airport → Srinagar; Shankaracharya, Jyeshta Devi, shikara</t>
   </si>
   <si>
     <t xml:space="preserve">Srinagar</t>
   </si>
   <si>
+    <t xml:space="preserve">Flight info</t>
+  </si>
+  <si>
     <t xml:space="preserve">Srinagar → Gulmarg</t>
   </si>
   <si>
     <t xml:space="preserve">Gulmarg</t>
   </si>
   <si>
+    <t xml:space="preserve">Arrival at Jammu Airport on 13 March 2027 before 14:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gulmarg → Kheer Bhawani → Sonamarg → Srinagar</t>
   </si>
   <si>
+    <t xml:space="preserve">Flight Jammu → Srinagar on 16 March 2027, departing between 11:00 and 12:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">Srinagar → Avantipur → Martand → Pahalgam (union cab to valleys)</t>
   </si>
   <si>
     <t xml:space="preserve">Pahalgam</t>
   </si>
   <si>
-    <t xml:space="preserve">Pahalgam → Srinagar temples → departure</t>
+    <t xml:space="preserve">Departure from Srinagar Airport on 20 March 2027 after 14:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pahalgam → Pampore → Srinagar Airport departure</t>
   </si>
   <si>
     <t xml:space="preserve">—</t>
@@ -142,7 +154,7 @@
     <t xml:space="preserve">Days 1–3 are identical to the 4-day Vaishno Devi package; 4-day yatris leave the group at Jammu Airport on Day 4.</t>
   </si>
   <si>
-    <t xml:space="preserve">Assumptions: arrival at Jammu by 14:00 on Day 1; breakfast 07:30–08:30 and departure from the hotel at 09:00 every day; helicopter slots 12:15 (Day 2) and 12:15 (Day 3); Jammu → Srinagar flight around 12:00 on Day 4; departure from Srinagar after 18:45 on Day 8; Kashmir hotels on MAP (breakfast + dinner). Day 6 is the longest road day (~212 km); start 09:00 after breakfast; back in Srinagar about 19:15.</t>
+    <t xml:space="preserve">Assumptions: arrival at Jammu by 14:00 on Day 1; breakfast 07:30–08:30 and departure from the hotel at 09:00 every day; helicopter slots 12:15 (Day 2) and 12:15 (Day 3); Jammu → Srinagar flight 11:00–12:00 on Day 4 (plan uses 12:00; for an 11:00 flight leave Katra 08:00 with breakfast 07:00); departure from Srinagar after 14:00 on Day 8; Kashmir hotels on MAP (breakfast + dinner). Day 6 is the longest road day (~212 km); start 09:00 after breakfast; back in Srinagar about 19:15.</t>
   </si>
   <si>
     <t xml:space="preserve">8 Days Vaishno Devi &amp; Kashmir Pilgrimage – Minute-to-Minute Plan</t>
@@ -484,7 +496,7 @@
     <t xml:space="preserve">Srinagar Airport</t>
   </si>
   <si>
-    <t xml:space="preserve">Flight Jammu → Srinagar, about 50 min (time to match booked flight)</t>
+    <t xml:space="preserve">Flight Jammu → Srinagar (book the 11:00–12:00 departure; plan assumes 12:00)</t>
   </si>
   <si>
     <t xml:space="preserve">Baggage collection, meet Srinagar driver</t>
@@ -502,327 +514,333 @@
     <t xml:space="preserve">Lunch – at the hotel / houseboat after check-in; group pays</t>
   </si>
   <si>
+    <t xml:space="preserve">Hotel, Dal Lake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shankaracharya Temple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drive up Gopadri hill to the temple parking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hilltop Shiva temple, ~240 steps from the parking; views of Dal Lake (phones not allowed – leave in car)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jyeshta Devi Temple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drive to Zethyar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Darshan of Mata Jyeshta Devi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shikara ghat, Dal Lake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drive to the shikara ghat on Boulevard Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shikara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dal Lake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunset shikara ride past Char Chinari and Nehru Park; kirtan on the boat (floating market runs only at dawn)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rest; Day 5 briefing (warm clothes, overnight bag for Gulmarg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dinner – hotel on MAP plan (breakfast + dinner included)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotel restaurant, Srinagar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Breakfast – included (MAP); Amalaki Ekadashi – grain-free items</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotel, Srinagar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check-out (main luggage can stay at the Srinagar hotel for Day 6 return)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drive via Tangmarg (hire snow boots / coats at Tangmarg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gondola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gulmarg Gondola: Kongdori (Phase 1) and Apharwat (Phase 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gondola ride (optional; book tickets online in advance); Snow Point and Apharwat Peak views</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pure-veg restaurant, Gulmarg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lunch – Amalaki Ekadashi: grain-free Ekadashi prasadam (fruits, potato, sabudana), pre-ordered; group pays</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotel, Gulmarg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check-in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maharani Temple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Short drive / walk across the meadow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maharani Temple (Shiva temple), Gulmarg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Darshan at the hilltop Shiva temple in the Gulmarg meadow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sightseeing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gulmarg meadow viewpoints</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meadow walk, Himalayan views at sunset, group photo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rest, Ekadashi kirtan; Day 6 briefing (long drive)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotel restaurant, Gulmarg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dinner – included (MAP); Ekadashi grain-free menu pre-ordered with the hotel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Break fast (parana) 07:14–10:26 – breakfast included (MAP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kheer Bhawani Temple, Tulmulla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drive via Tangmarg and Ganderbal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kheer Bhawani Temple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Darshan of Mata Ragnya Devi at the sacred spring; kheer offering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tulmulla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sonamarg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scenic drive along the Sindh river</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pure-veg restaurant, Sonamarg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lunch – pure-veg dhaba / restaurant at Sonamarg market; group pays</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pony / local taxi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thajiwas Glacier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thajiwas Glacier by pony (optional, ~3 km; fixed union rates); snow play</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sindh River viewpoints, Sonamarg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sindh river banks and snow-peak viewpoints; group photo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return to Srinagar (last hour after dark – experienced driver)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dinner – included (MAP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Breakfast – included (MAP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avantipur Temple Ruins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drive on the Jammu–Srinagar highway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9th-century Avantiswami (Vishnu) temple ruins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avantipur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martand Sun Temple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Via Anantnag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8th-century Surya temple ruins on the Mattan plateau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotel, Pahalgam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drive along the Lidder river</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotel restaurant, Pahalgam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lunch – at the Pahalgam hotel; group pays</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pahalgam taxi stand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Board local union cabs (our car cannot go beyond Pahalgam)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Union cab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chandanwari</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 km by union cab (if open in March)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start point of the Amarnath route; snow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Betaab Valley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 km</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meadows and river, photo stop (entry ticket)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aru Valley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 km via Pahalgam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meadow village, pine forests, sunset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 km back to Pahalgam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lidder River banks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Short evening walk by the Lidder river; kirtan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check-out, load luggage; collect packed lunch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pampore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drive towards Srinagar along the Jhelum valley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pampore saffron and dry-fruit shops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saffron, walnuts, almonds and dry fruits from government-approved shops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drive to the airport (allow for security checkpoints)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Packed lunch at Srinagar Airport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Packed lunch from the Pahalgam hotel, eaten before security; group pays</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Departure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Farewell, Jai Mata Di! Har Har Mahadev! (departure flights after 14:00; Srinagar security takes time)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legend: yellow rows = meals; blue rows = helicopter, ropeway, flight, gondola, shikara, union cab.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meal plan (all 23 meals pure-veg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provided by</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08:00–08:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On own, while travelling to Jammu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yatri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not included</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:15–15:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotel, pre-ordered thali</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group pays</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20:15–21:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotel, pre-ordered menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07:30–08:30</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hotel</t>
   </si>
   <si>
-    <t xml:space="preserve">Shikara ghat, Dal Lake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Walk to nearest shikara ghat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shikara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dal Lake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunset shikara ride past Char Chinari and Nehru Park; kirtan on the boat (floating market runs only at dawn)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rest; Day 5 briefing (warm clothes, overnight bag for Gulmarg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dinner – hotel on MAP plan (breakfast + dinner included)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hotel restaurant, Srinagar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Breakfast – included (MAP); Amalaki Ekadashi – grain-free items</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hotel, Srinagar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check-out (main luggage can stay at the Srinagar hotel for Day 6 return)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drive via Tangmarg (hire snow boots / coats at Tangmarg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gondola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gulmarg Gondola: Kongdori (Phase 1) and Apharwat (Phase 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gondola ride (optional; book tickets online in advance); Snow Point and Apharwat Peak views</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pure-veg restaurant, Gulmarg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lunch – Amalaki Ekadashi: grain-free Ekadashi prasadam (fruits, potato, sabudana), pre-ordered; group pays</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hotel, Gulmarg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check-in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maharani Temple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Short drive / walk across the meadow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maharani Temple (Shiva temple), Gulmarg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Darshan at the hilltop Shiva temple in the Gulmarg meadow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sightseeing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gulmarg meadow viewpoints</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meadow walk, Himalayan views at sunset, group photo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rest, Ekadashi kirtan; Day 6 briefing (long drive)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hotel restaurant, Gulmarg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dinner – included (MAP); Ekadashi grain-free menu pre-ordered with the hotel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Break fast (parana) 07:14–10:26 – breakfast included (MAP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kheer Bhawani Temple, Tulmulla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drive via Tangmarg and Ganderbal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kheer Bhawani Temple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Darshan of Mata Ragnya Devi at the sacred spring; kheer offering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tulmulla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sonamarg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scenic drive along the Sindh river</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pure-veg restaurant, Sonamarg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lunch – pure-veg dhaba / restaurant at Sonamarg market; group pays</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pony / local taxi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thajiwas Glacier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thajiwas Glacier by pony (optional, ~3 km; fixed union rates); snow play</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sindh River viewpoints, Sonamarg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sindh river banks and snow-peak viewpoints; group photo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Return to Srinagar (last hour after dark – experienced driver)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dinner – included (MAP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Breakfast – included (MAP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avantipur Temple Ruins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drive on the Jammu–Srinagar highway</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9th-century Avantiswami (Vishnu) temple ruins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avantipur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Martand Sun Temple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Via Anantnag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8th-century Surya temple ruins on the Mattan plateau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Martand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hotel, Pahalgam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drive along the Lidder river</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hotel restaurant, Pahalgam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lunch – at the Pahalgam hotel; group pays</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pahalgam taxi stand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Board local union cabs (our car cannot go beyond Pahalgam)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Union cab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chandanwari</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 km by union cab (if open in March)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start point of the Amarnath route; snow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Betaab Valley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 km</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meadows and river, photo stop (entry ticket)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aru Valley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 km via Pahalgam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meadow village, pine forests, sunset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 km back to Pahalgam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lidder River banks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Short evening walk by the Lidder river; kirtan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shankaracharya Temple, Srinagar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drive to Srinagar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shankaracharya Temple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hilltop Shiva temple, ~240 steps from the parking; views of Dal Lake (phones not allowed – leave in car)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jyeshta Devi Temple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drive to Zethyar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Darshan of Mata Jyeshta Devi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pure-veg restaurant, Srinagar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lunch – pure-veg restaurant near Lal Chowk / Durganag; group pays</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lal Chowk / Polo View Market, Srinagar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saffron, dry fruits, walnut wood, pashmina (buy from government emporium for authenticity)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lal Chowk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drive to airport (allow for security checkpoints)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Departure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drop-off, farewell, Jai Mata Di! Har Har Mahadev! (book flights after 18:45; reach 2.5 hrs early)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legend: yellow rows = meals; blue rows = helicopter, ropeway, flight, gondola, shikara, union cab.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meal plan (all 23 meals pure-veg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Where</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Provided by</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08:00–08:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On own, while travelling to Jammu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yatri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not included</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:15–15:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hotel, pre-ordered thali</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Group pays</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20:15–21:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hotel, pre-ordered menu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07:30–08:30</t>
-  </si>
-  <si>
     <t xml:space="preserve">Complimentary</t>
   </si>
   <si>
@@ -877,7 +895,10 @@
     <t xml:space="preserve">Restaurant, pre-booked</t>
   </si>
   <si>
-    <t xml:space="preserve">13:45–14:45</t>
+    <t xml:space="preserve">11:45–12:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotel (Pahalgam), packed</t>
   </si>
   <si>
     <t xml:space="preserve">Pure-veg options are few in Gulmarg and Sonamarg; pre-book for the group size or carry packed lunch from the hotel. Ask every kitchen about no onion-garlic cooking.</t>
@@ -1126,7 +1147,7 @@
     <t xml:space="preserve">Reach the airport 2.5 hrs early</t>
   </si>
   <si>
-    <t xml:space="preserve">Book departure after 18:45</t>
+    <t xml:space="preserve">Book departure after 14:00 (14:30 or later preferred)</t>
   </si>
   <si>
     <t xml:space="preserve">Lost yatri in crowd</t>
@@ -1306,7 +1327,7 @@
     <t xml:space="preserve">T−45 days</t>
   </si>
   <si>
-    <t xml:space="preserve">Book flights: home → Jammu (Day 1, arriving by 14:00), Jammu → Srinagar (Day 4, around 12:00), Srinagar → home (Day 8, after 18:45)</t>
+    <t xml:space="preserve">Book flights: home → Jammu (arrive before 14:00, 13 Mar), Jammu → Srinagar (16 Mar, 11:00–12:00), Srinagar → home (20 Mar, after 14:00)</t>
   </si>
   <si>
     <t xml:space="preserve">Travel desk</t>
@@ -1753,7 +1774,7 @@
     <t xml:space="preserve">Bhairon ropeway, Atka Aarti passes</t>
   </si>
   <si>
-    <t xml:space="preserve">Vehicles: Jammu–Katra (Days 1–4) and Kashmir (Days 4–8), about 641 km</t>
+    <t xml:space="preserve">Vehicles: Jammu–Katra (Days 1–4) and Kashmir (Days 4–8), about 643 km</t>
   </si>
   <si>
     <t xml:space="preserve">Per vehicle, split by seats</t>
@@ -2618,7 +2639,7 @@
       </c>
       <c r="D8" s="7" t="n">
         <f aca="false">SUMIF('Minute-by-Minute'!$A$5:$A$121,A8,'Minute-by-Minute'!$I$5:$I$121)</f>
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>22</v>
@@ -2631,6 +2652,9 @@
         <f aca="false">_xlfn.MAXIFS('Minute-by-Minute'!$D$5:$D$121,'Minute-by-Minute'!$A$5:$A$121,A8)</f>
         <v>0.875</v>
       </c>
+      <c r="I8" s="3" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="n">
@@ -2641,14 +2665,14 @@
         <v>46463</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D9" s="7" t="n">
         <f aca="false">SUMIF('Minute-by-Minute'!$A$5:$A$121,A9,'Minute-by-Minute'!$I$5:$I$121)</f>
         <v>52</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F9" s="9" t="n">
         <f aca="false">_xlfn.MINIFS('Minute-by-Minute'!$C$5:$C$121,'Minute-by-Minute'!$A$5:$A$121,A9)</f>
@@ -2658,6 +2682,9 @@
         <f aca="false">_xlfn.MAXIFS('Minute-by-Minute'!$D$5:$D$121,'Minute-by-Minute'!$A$5:$A$121,A9)</f>
         <v>0.875</v>
       </c>
+      <c r="I9" s="2" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="n">
@@ -2668,7 +2695,7 @@
         <v>46464</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D10" s="7" t="n">
         <f aca="false">SUMIF('Minute-by-Minute'!$A$5:$A$121,A10,'Minute-by-Minute'!$I$5:$I$121)</f>
@@ -2685,6 +2712,9 @@
         <f aca="false">_xlfn.MAXIFS('Minute-by-Minute'!$D$5:$D$121,'Minute-by-Minute'!$A$5:$A$121,A10)</f>
         <v>0.875</v>
       </c>
+      <c r="I10" s="2" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="n">
@@ -2695,14 +2725,14 @@
         <v>46465</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D11" s="7" t="n">
         <f aca="false">SUMIF('Minute-by-Minute'!$A$5:$A$121,A11,'Minute-by-Minute'!$I$5:$I$121)</f>
         <v>105</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F11" s="9" t="n">
         <f aca="false">_xlfn.MINIFS('Minute-by-Minute'!$C$5:$C$121,'Minute-by-Minute'!$A$5:$A$121,A11)</f>
@@ -2712,6 +2742,9 @@
         <f aca="false">_xlfn.MAXIFS('Minute-by-Minute'!$D$5:$D$121,'Minute-by-Minute'!$A$5:$A$121,A11)</f>
         <v>0.875</v>
       </c>
+      <c r="I11" s="2" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="n">
@@ -2722,14 +2755,14 @@
         <v>46466</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D12" s="7" t="n">
         <f aca="false">SUMIF('Minute-by-Minute'!$A$5:$A$121,A12,'Minute-by-Minute'!$I$5:$I$121)</f>
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F12" s="9" t="n">
         <f aca="false">_xlfn.MINIFS('Minute-by-Minute'!$C$5:$C$121,'Minute-by-Minute'!$A$5:$A$121,A12)</f>
@@ -2737,39 +2770,39 @@
       </c>
       <c r="G12" s="9" t="n">
         <f aca="false">_xlfn.MAXIFS('Minute-by-Minute'!$D$5:$D$121,'Minute-by-Minute'!$A$5:$A$121,A12)</f>
-        <v>0.697916666666667</v>
+        <v>0.520833333333333</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D13" s="3" t="n">
         <f aca="false">SUM(D5:D12)</f>
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -2799,100 +2832,100 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>503</v>
+        <v>510</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
     </row>
   </sheetData>
@@ -2922,91 +2955,91 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>526</v>
+        <v>533</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="C2" s="23"/>
       <c r="D2" s="23"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="C3" s="23"/>
       <c r="D3" s="23"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="C4" s="23"/>
       <c r="D4" s="23"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="C5" s="23"/>
       <c r="D5" s="23"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="C6" s="23"/>
       <c r="D6" s="23"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="C7" s="23"/>
       <c r="D7" s="23"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="C8" s="23"/>
       <c r="D8" s="23"/>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="B9" s="14"/>
       <c r="C9" s="23"/>
@@ -3014,7 +3047,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="B10" s="14"/>
       <c r="C10" s="23"/>
@@ -3022,17 +3055,17 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="C11" s="23"/>
       <c r="D11" s="23"/>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="B12" s="14"/>
       <c r="C12" s="23"/>
@@ -3040,24 +3073,24 @@
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="C13" s="23"/>
       <c r="D13" s="23"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="C14" s="14"/>
       <c r="D14" s="14" t="s">
-        <v>549</v>
+        <v>556</v>
       </c>
     </row>
   </sheetData>
@@ -3087,259 +3120,259 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>555</v>
+        <v>562</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="D5" s="24"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="D6" s="24"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="D7" s="24"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="D8" s="24"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="D9" s="24"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="D10" s="24"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
+        <v>574</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>567</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>562</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>560</v>
       </c>
       <c r="D11" s="24"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="D12" s="24"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="D13" s="24"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="D14" s="24"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="D15" s="24"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="D16" s="24"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="D17" s="24"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="D18" s="24"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="D19" s="24"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="D20" s="24"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="D21" s="24"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="D22" s="24"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="D23" s="24"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>589</v>
+        <v>596</v>
       </c>
       <c r="D24" s="25" t="n">
         <f aca="false">SUMIF(C5:C23,"Yes",D5:D23)</f>
@@ -3348,10 +3381,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>590</v>
+        <v>597</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="D25" s="26" t="n">
         <v>0.05</v>
@@ -3359,7 +3392,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>592</v>
+        <v>599</v>
       </c>
       <c r="D26" s="25" t="n">
         <f aca="false">D24*(1+D25)</f>
@@ -3368,7 +3401,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>593</v>
+        <v>600</v>
       </c>
     </row>
   </sheetData>
@@ -3396,93 +3429,93 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>594</v>
+        <v>601</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="B2" s="23"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="B3" s="23"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="B4" s="23"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>598</v>
+        <v>605</v>
       </c>
       <c r="B5" s="23"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="B6" s="23"/>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>600</v>
+        <v>607</v>
       </c>
       <c r="B7" s="23"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="B8" s="23"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>602</v>
+        <v>609</v>
       </c>
       <c r="B9" s="23"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="B10" s="23"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>604</v>
+        <v>611</v>
       </c>
       <c r="B11" s="23"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>605</v>
+        <v>612</v>
       </c>
       <c r="B12" s="23"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="B13" s="23"/>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>607</v>
+        <v>614</v>
       </c>
       <c r="B14" s="23"/>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="B15" s="23"/>
     </row>
@@ -3519,12 +3552,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3535,31 +3568,31 @@
         <v>6</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I4" s="10" t="s">
         <v>8</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3581,15 +3614,15 @@
         <v>30</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H5" s="11"/>
       <c r="I5" s="11"/>
       <c r="J5" s="11" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="K5" s="11"/>
     </row>
@@ -3612,18 +3645,18 @@
         <v>30</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="H6" s="14"/>
       <c r="I6" s="14"/>
       <c r="J6" s="14" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K6" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3645,22 +3678,22 @@
         <v>20</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="I7" s="14" t="n">
         <v>7</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K7" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3682,18 +3715,18 @@
         <v>25</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H8" s="14"/>
       <c r="I8" s="14"/>
       <c r="J8" s="14" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="K8" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3715,18 +3748,18 @@
         <v>35</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="H9" s="11"/>
       <c r="I9" s="11"/>
       <c r="J9" s="11" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K9" s="18" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3748,22 +3781,22 @@
         <v>15</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="I10" s="14" t="n">
         <v>5</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K10" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3785,18 +3818,18 @@
         <v>40</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="H11" s="14"/>
       <c r="I11" s="14"/>
       <c r="J11" s="14" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="K11" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3818,22 +3851,22 @@
         <v>10</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="I12" s="14" t="n">
         <v>1</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="K12" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3855,18 +3888,18 @@
         <v>25</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H13" s="14"/>
       <c r="I13" s="14"/>
       <c r="J13" s="14" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="K13" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3888,22 +3921,22 @@
         <v>20</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="I14" s="14" t="n">
         <v>6</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3925,18 +3958,18 @@
         <v>50</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H15" s="14"/>
       <c r="I15" s="14"/>
       <c r="J15" s="14" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="K15" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3958,22 +3991,22 @@
         <v>25</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I16" s="14" t="n">
         <v>7</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="K16" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3995,18 +4028,18 @@
         <v>35</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H17" s="14"/>
       <c r="I17" s="14"/>
       <c r="J17" s="14" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="K17" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4028,22 +4061,22 @@
         <v>20</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H18" s="14" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="I18" s="14" t="n">
         <v>6</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="K18" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4065,18 +4098,18 @@
         <v>25</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H19" s="14"/>
       <c r="I19" s="14"/>
       <c r="J19" s="14" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K19" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4098,18 +4131,18 @@
         <v>60</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="H20" s="11"/>
       <c r="I20" s="11"/>
       <c r="J20" s="11" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="K20" s="18" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4131,18 +4164,18 @@
         <v>60</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="H21" s="11"/>
       <c r="I21" s="11"/>
       <c r="J21" s="11" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="K21" s="18" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4164,18 +4197,18 @@
         <v>30</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H22" s="14"/>
       <c r="I22" s="14"/>
       <c r="J22" s="14" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="K22" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4197,10 +4230,10 @@
         <v>90</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H23" s="14" t="s">
         <v>20</v>
@@ -4209,10 +4242,10 @@
         <v>50</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="K23" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4234,18 +4267,18 @@
         <v>30</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H24" s="14"/>
       <c r="I24" s="14"/>
       <c r="J24" s="14" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="K24" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4267,22 +4300,22 @@
         <v>10</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H25" s="14" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I25" s="14" t="n">
         <v>2</v>
       </c>
       <c r="J25" s="14" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="K25" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4304,18 +4337,18 @@
         <v>65</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="H26" s="14"/>
       <c r="I26" s="14"/>
       <c r="J26" s="14" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K26" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4337,20 +4370,20 @@
         <v>10</v>
       </c>
       <c r="F27" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="G27" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="G27" s="19" t="s">
-        <v>89</v>
-      </c>
       <c r="H27" s="19" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="I27" s="19"/>
       <c r="J27" s="19" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K27" s="22" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4372,20 +4405,20 @@
         <v>65</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="H28" s="14" t="s">
         <v>17</v>
       </c>
       <c r="I28" s="14"/>
       <c r="J28" s="14" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="K28" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4407,7 +4440,7 @@
         <v>30</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G29" s="14" t="s">
         <v>17</v>
@@ -4415,10 +4448,10 @@
       <c r="H29" s="14"/>
       <c r="I29" s="14"/>
       <c r="J29" s="14" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="K29" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4440,18 +4473,18 @@
         <v>45</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H30" s="11"/>
       <c r="I30" s="11"/>
       <c r="J30" s="11" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="K30" s="18" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4473,7 +4506,7 @@
         <v>105</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G31" s="14" t="s">
         <v>17</v>
@@ -4481,10 +4514,10 @@
       <c r="H31" s="14"/>
       <c r="I31" s="14"/>
       <c r="J31" s="14" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="K31" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4506,18 +4539,18 @@
         <v>90</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="H32" s="14"/>
       <c r="I32" s="14"/>
       <c r="J32" s="14" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="K32" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4539,7 +4572,7 @@
         <v>90</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="G33" s="14" t="s">
         <v>17</v>
@@ -4547,10 +4580,10 @@
       <c r="H33" s="14"/>
       <c r="I33" s="14"/>
       <c r="J33" s="14" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="K33" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4572,18 +4605,18 @@
         <v>60</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H34" s="11"/>
       <c r="I34" s="11"/>
       <c r="J34" s="11" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K34" s="18" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4605,7 +4638,7 @@
         <v>60</v>
       </c>
       <c r="F35" s="14" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G35" s="14" t="s">
         <v>17</v>
@@ -4613,10 +4646,10 @@
       <c r="H35" s="14"/>
       <c r="I35" s="14"/>
       <c r="J35" s="14" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="K35" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4638,7 +4671,7 @@
         <v>90</v>
       </c>
       <c r="F36" s="14" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="G36" s="14" t="s">
         <v>17</v>
@@ -4646,10 +4679,10 @@
       <c r="H36" s="14"/>
       <c r="I36" s="14"/>
       <c r="J36" s="14" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="K36" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4671,7 +4704,7 @@
         <v>30</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G37" s="14" t="s">
         <v>17</v>
@@ -4679,10 +4712,10 @@
       <c r="H37" s="14"/>
       <c r="I37" s="14"/>
       <c r="J37" s="14" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="K37" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4704,18 +4737,18 @@
         <v>60</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H38" s="11"/>
       <c r="I38" s="11"/>
       <c r="J38" s="11" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="K38" s="18" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4737,7 +4770,7 @@
         <v>30</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G39" s="14" t="s">
         <v>17</v>
@@ -4745,10 +4778,10 @@
       <c r="H39" s="14"/>
       <c r="I39" s="14"/>
       <c r="J39" s="14" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="K39" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4770,20 +4803,20 @@
         <v>15</v>
       </c>
       <c r="F40" s="14" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G40" s="14" t="s">
         <v>17</v>
       </c>
       <c r="H40" s="14" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="I40" s="14"/>
       <c r="J40" s="14" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K40" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4805,20 +4838,20 @@
         <v>20</v>
       </c>
       <c r="F41" s="19" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G41" s="19" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="H41" s="19" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I41" s="19"/>
       <c r="J41" s="19" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="K41" s="22" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4840,18 +4873,18 @@
         <v>40</v>
       </c>
       <c r="F42" s="14" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G42" s="14" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="H42" s="14"/>
       <c r="I42" s="14"/>
       <c r="J42" s="14" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="K42" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4873,20 +4906,20 @@
         <v>60</v>
       </c>
       <c r="F43" s="14" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G43" s="14" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="H43" s="14" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="I43" s="14"/>
       <c r="J43" s="14" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="K43" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4908,18 +4941,18 @@
         <v>60</v>
       </c>
       <c r="F44" s="14" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G44" s="14" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="H44" s="14"/>
       <c r="I44" s="14"/>
       <c r="J44" s="14" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="K44" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4941,20 +4974,20 @@
         <v>10</v>
       </c>
       <c r="F45" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="G45" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="H45" s="19" t="s">
         <v>93</v>
-      </c>
-      <c r="G45" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="H45" s="19" t="s">
-        <v>89</v>
       </c>
       <c r="I45" s="19"/>
       <c r="J45" s="19" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="K45" s="22" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4976,22 +5009,22 @@
         <v>15</v>
       </c>
       <c r="F46" s="14" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G46" s="14" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="H46" s="14" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="I46" s="14" t="n">
         <v>2</v>
       </c>
       <c r="J46" s="14" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="K46" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5013,18 +5046,18 @@
         <v>35</v>
       </c>
       <c r="F47" s="14" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G47" s="14" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="H47" s="14"/>
       <c r="I47" s="14"/>
       <c r="J47" s="14" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="K47" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5046,18 +5079,18 @@
         <v>45</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G48" s="11" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="H48" s="11"/>
       <c r="I48" s="11"/>
       <c r="J48" s="11" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="K48" s="18" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5079,18 +5112,18 @@
         <v>120</v>
       </c>
       <c r="F49" s="14" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G49" s="14" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="H49" s="14"/>
       <c r="I49" s="14"/>
       <c r="J49" s="14" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="K49" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5112,22 +5145,22 @@
         <v>15</v>
       </c>
       <c r="F50" s="14" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G50" s="14" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="H50" s="14" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="I50" s="14" t="n">
         <v>3</v>
       </c>
       <c r="J50" s="14" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="K50" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5149,18 +5182,18 @@
         <v>45</v>
       </c>
       <c r="F51" s="14" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G51" s="14" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H51" s="14"/>
       <c r="I51" s="14"/>
       <c r="J51" s="14" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="K51" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5182,22 +5215,22 @@
         <v>10</v>
       </c>
       <c r="F52" s="14" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G52" s="14" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H52" s="14" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="I52" s="14" t="n">
         <v>1</v>
       </c>
       <c r="J52" s="14" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K52" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5219,18 +5252,18 @@
         <v>30</v>
       </c>
       <c r="F53" s="14" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G53" s="14" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="H53" s="14"/>
       <c r="I53" s="14"/>
       <c r="J53" s="14" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="K53" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5252,22 +5285,22 @@
         <v>15</v>
       </c>
       <c r="F54" s="14" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G54" s="14" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="H54" s="14" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="I54" s="14" t="n">
         <v>2</v>
       </c>
       <c r="J54" s="14" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="K54" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5289,18 +5322,18 @@
         <v>95</v>
       </c>
       <c r="F55" s="14" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="G55" s="14" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="H55" s="14"/>
       <c r="I55" s="14"/>
       <c r="J55" s="14" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="K55" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5322,22 +5355,22 @@
         <v>15</v>
       </c>
       <c r="F56" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="G56" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="G56" s="14" t="s">
-        <v>136</v>
-      </c>
       <c r="H56" s="14" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="I56" s="14" t="n">
         <v>1</v>
       </c>
       <c r="J56" s="14" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="K56" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5359,18 +5392,18 @@
         <v>60</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G57" s="11" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="H57" s="11"/>
       <c r="I57" s="11"/>
       <c r="J57" s="11" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="K57" s="18" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5392,18 +5425,18 @@
         <v>60</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G58" s="11" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="H58" s="11"/>
       <c r="I58" s="11"/>
       <c r="J58" s="11" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="K58" s="18" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5425,18 +5458,18 @@
         <v>30</v>
       </c>
       <c r="F59" s="14" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G59" s="14" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="H59" s="14"/>
       <c r="I59" s="14"/>
       <c r="J59" s="14" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="K59" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5458,22 +5491,22 @@
         <v>90</v>
       </c>
       <c r="F60" s="14" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G60" s="14" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="H60" s="14" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I60" s="14" t="n">
         <v>50</v>
       </c>
       <c r="J60" s="14" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="K60" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5495,21 +5528,21 @@
         <v>90</v>
       </c>
       <c r="F61" s="14" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="G61" s="14" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H61" s="14"/>
       <c r="I61" s="14"/>
       <c r="J61" s="14" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="K61" s="17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="19" t="n">
         <v>4</v>
       </c>
@@ -5528,20 +5561,20 @@
         <v>50</v>
       </c>
       <c r="F62" s="19" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="G62" s="19" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H62" s="19" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="I62" s="19"/>
       <c r="J62" s="19" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="K62" s="22" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5563,18 +5596,18 @@
         <v>25</v>
       </c>
       <c r="F63" s="14" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="G63" s="14" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="H63" s="14"/>
       <c r="I63" s="14"/>
       <c r="J63" s="14" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="K63" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5596,22 +5629,22 @@
         <v>45</v>
       </c>
       <c r="F64" s="14" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G64" s="14" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="H64" s="14" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="I64" s="14" t="n">
         <v>14</v>
       </c>
       <c r="J64" s="14" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="K64" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5633,18 +5666,18 @@
         <v>60</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G65" s="11" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="H65" s="11"/>
       <c r="I65" s="11"/>
       <c r="J65" s="11" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="K65" s="18" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5659,28 +5692,32 @@
         <v>0.625</v>
       </c>
       <c r="D66" s="16" t="n">
-        <v>0.697916666666667</v>
+        <v>0.635416666666667</v>
       </c>
       <c r="E66" s="14" t="n">
         <f aca="false">ROUND((D66-C66)*1440,0)</f>
-        <v>105</v>
+        <v>15</v>
       </c>
       <c r="F66" s="14" t="s">
-        <v>101</v>
+        <v>57</v>
       </c>
       <c r="G66" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="H66" s="14"/>
-      <c r="I66" s="14"/>
+        <v>159</v>
+      </c>
+      <c r="H66" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="I66" s="14" t="n">
+        <v>5</v>
+      </c>
       <c r="J66" s="14" t="s">
-        <v>101</v>
+        <v>161</v>
       </c>
       <c r="K66" s="17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="14" t="n">
         <v>4</v>
       </c>
@@ -5689,63 +5726,65 @@
         <v>46462</v>
       </c>
       <c r="C67" s="16" t="n">
-        <v>0.697916666666667</v>
+        <v>0.635416666666667</v>
       </c>
       <c r="D67" s="16" t="n">
-        <v>0.708333333333333</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="E67" s="14" t="n">
         <f aca="false">ROUND((D67-C67)*1440,0)</f>
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="F67" s="14" t="s">
-        <v>113</v>
+        <v>69</v>
       </c>
       <c r="G67" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="H67" s="14" t="s">
-        <v>156</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="H67" s="14"/>
       <c r="I67" s="14"/>
       <c r="J67" s="14" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="K67" s="17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="19" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="B68" s="20" t="n">
+      <c r="B68" s="15" t="n">
         <f aca="false">Overview!$B$3+A68-1</f>
         <v>46462</v>
       </c>
-      <c r="C68" s="21" t="n">
-        <v>0.708333333333333</v>
-      </c>
-      <c r="D68" s="21" t="n">
-        <v>0.770833333333333</v>
-      </c>
-      <c r="E68" s="19" t="n">
+      <c r="C68" s="16" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="D68" s="16" t="n">
+        <v>0.677083333333333</v>
+      </c>
+      <c r="E68" s="14" t="n">
         <f aca="false">ROUND((D68-C68)*1440,0)</f>
-        <v>90</v>
-      </c>
-      <c r="F68" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="G68" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="H68" s="19"/>
-      <c r="I68" s="19"/>
-      <c r="J68" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F68" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="G68" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="K68" s="22" t="s">
-        <v>52</v>
+      <c r="H68" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="I68" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="J68" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="K68" s="17" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5757,230 +5796,230 @@
         <v>46462</v>
       </c>
       <c r="C69" s="16" t="n">
-        <v>0.770833333333333</v>
+        <v>0.677083333333333</v>
       </c>
       <c r="D69" s="16" t="n">
-        <v>0.833333333333333</v>
+        <v>0.697916666666667</v>
       </c>
       <c r="E69" s="14" t="n">
         <f aca="false">ROUND((D69-C69)*1440,0)</f>
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="F69" s="14" t="s">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="G69" s="14" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="H69" s="14"/>
       <c r="I69" s="14"/>
       <c r="J69" s="14" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K69" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="11" t="n">
+      <c r="A70" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="B70" s="12" t="n">
+      <c r="B70" s="15" t="n">
         <f aca="false">Overview!$B$3+A70-1</f>
         <v>46462</v>
       </c>
-      <c r="C70" s="13" t="n">
-        <v>0.833333333333333</v>
-      </c>
-      <c r="D70" s="13" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="E70" s="11" t="n">
+      <c r="C70" s="16" t="n">
+        <v>0.697916666666667</v>
+      </c>
+      <c r="D70" s="16" t="n">
+        <v>0.711805555555556</v>
+      </c>
+      <c r="E70" s="14" t="n">
         <f aca="false">ROUND((D70-C70)*1440,0)</f>
-        <v>60</v>
-      </c>
-      <c r="F70" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="G70" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="H70" s="11"/>
-      <c r="I70" s="11"/>
-      <c r="J70" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="K70" s="18" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="B71" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="F70" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="G70" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="H70" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="I70" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="J70" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="K70" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="B71" s="20" t="n">
         <f aca="false">Overview!$B$3+A71-1</f>
-        <v>46463</v>
-      </c>
-      <c r="C71" s="13" t="n">
-        <v>0.3125</v>
-      </c>
-      <c r="D71" s="13" t="n">
-        <v>0.354166666666667</v>
-      </c>
-      <c r="E71" s="11" t="n">
+        <v>46462</v>
+      </c>
+      <c r="C71" s="21" t="n">
+        <v>0.711805555555556</v>
+      </c>
+      <c r="D71" s="21" t="n">
+        <v>0.770833333333333</v>
+      </c>
+      <c r="E71" s="19" t="n">
         <f aca="false">ROUND((D71-C71)*1440,0)</f>
-        <v>60</v>
-      </c>
-      <c r="F71" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="G71" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="H71" s="11"/>
-      <c r="I71" s="11"/>
-      <c r="J71" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="K71" s="18" t="s">
-        <v>52</v>
+        <v>85</v>
+      </c>
+      <c r="F71" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="G71" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="H71" s="19"/>
+      <c r="I71" s="19"/>
+      <c r="J71" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="K71" s="22" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B72" s="15" t="n">
         <f aca="false">Overview!$B$3+A72-1</f>
-        <v>46463</v>
+        <v>46462</v>
       </c>
       <c r="C72" s="16" t="n">
-        <v>0.354166666666667</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="D72" s="16" t="n">
-        <v>0.375</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="E72" s="14" t="n">
         <f aca="false">ROUND((D72-C72)*1440,0)</f>
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="F72" s="14" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="G72" s="14" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="H72" s="14"/>
       <c r="I72" s="14"/>
       <c r="J72" s="14" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="K72" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="14" t="n">
+      <c r="A73" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B73" s="12" t="n">
+        <f aca="false">Overview!$B$3+A73-1</f>
+        <v>46462</v>
+      </c>
+      <c r="C73" s="13" t="n">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="D73" s="13" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="E73" s="11" t="n">
+        <f aca="false">ROUND((D73-C73)*1440,0)</f>
+        <v>60</v>
+      </c>
+      <c r="F73" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="G73" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="H73" s="11"/>
+      <c r="I73" s="11"/>
+      <c r="J73" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="K73" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="B73" s="15" t="n">
-        <f aca="false">Overview!$B$3+A73-1</f>
-        <v>46463</v>
-      </c>
-      <c r="C73" s="16" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="D73" s="16" t="n">
-        <v>0.447916666666667</v>
-      </c>
-      <c r="E73" s="14" t="n">
-        <f aca="false">ROUND((D73-C73)*1440,0)</f>
-        <v>105</v>
-      </c>
-      <c r="F73" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G73" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="H73" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="I73" s="14" t="n">
-        <v>50</v>
-      </c>
-      <c r="J73" s="14" t="s">
-        <v>167</v>
-      </c>
-      <c r="K73" s="17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="B74" s="20" t="n">
+      <c r="B74" s="12" t="n">
         <f aca="false">Overview!$B$3+A74-1</f>
         <v>46463</v>
       </c>
-      <c r="C74" s="21" t="n">
-        <v>0.447916666666667</v>
-      </c>
-      <c r="D74" s="21" t="n">
-        <v>0.572916666666667</v>
-      </c>
-      <c r="E74" s="19" t="n">
+      <c r="C74" s="13" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="D74" s="13" t="n">
+        <v>0.354166666666667</v>
+      </c>
+      <c r="E74" s="11" t="n">
         <f aca="false">ROUND((D74-C74)*1440,0)</f>
-        <v>180</v>
-      </c>
-      <c r="F74" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="G74" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="H74" s="19"/>
-      <c r="I74" s="19"/>
-      <c r="J74" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="K74" s="22" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="F74" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="G74" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="H74" s="11"/>
+      <c r="I74" s="11"/>
+      <c r="J74" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="K74" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B75" s="12" t="n">
+      <c r="B75" s="15" t="n">
         <f aca="false">Overview!$B$3+A75-1</f>
         <v>46463</v>
       </c>
-      <c r="C75" s="13" t="n">
-        <v>0.572916666666667</v>
-      </c>
-      <c r="D75" s="13" t="n">
-        <v>0.604166666666667</v>
-      </c>
-      <c r="E75" s="11" t="n">
+      <c r="C75" s="16" t="n">
+        <v>0.354166666666667</v>
+      </c>
+      <c r="D75" s="16" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="E75" s="14" t="n">
         <f aca="false">ROUND((D75-C75)*1440,0)</f>
-        <v>45</v>
-      </c>
-      <c r="F75" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="G75" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="H75" s="11"/>
-      <c r="I75" s="11"/>
-      <c r="J75" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="K75" s="18" t="s">
-        <v>52</v>
+        <v>30</v>
+      </c>
+      <c r="F75" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="G75" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="H75" s="14"/>
+      <c r="I75" s="14"/>
+      <c r="J75" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="K75" s="17" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5992,98 +6031,98 @@
         <v>46463</v>
       </c>
       <c r="C76" s="16" t="n">
-        <v>0.604166666666667</v>
+        <v>0.375</v>
       </c>
       <c r="D76" s="16" t="n">
-        <v>0.625</v>
+        <v>0.447916666666667</v>
       </c>
       <c r="E76" s="14" t="n">
         <f aca="false">ROUND((D76-C76)*1440,0)</f>
-        <v>30</v>
+        <v>105</v>
       </c>
       <c r="F76" s="14" t="s">
         <v>57</v>
       </c>
       <c r="G76" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="H76" s="14"/>
-      <c r="I76" s="14"/>
+        <v>175</v>
+      </c>
+      <c r="H76" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I76" s="14" t="n">
+        <v>50</v>
+      </c>
       <c r="J76" s="14" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="K76" s="17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="14" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="B77" s="15" t="n">
+      <c r="B77" s="20" t="n">
         <f aca="false">Overview!$B$3+A77-1</f>
         <v>46463</v>
       </c>
-      <c r="C77" s="16" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="D77" s="16" t="n">
-        <v>0.635416666666667</v>
-      </c>
-      <c r="E77" s="14" t="n">
+      <c r="C77" s="21" t="n">
+        <v>0.447916666666667</v>
+      </c>
+      <c r="D77" s="21" t="n">
+        <v>0.572916666666667</v>
+      </c>
+      <c r="E77" s="19" t="n">
         <f aca="false">ROUND((D77-C77)*1440,0)</f>
-        <v>15</v>
-      </c>
-      <c r="F77" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G77" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="H77" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="I77" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="J77" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="K77" s="17" t="s">
-        <v>52</v>
+        <v>180</v>
+      </c>
+      <c r="F77" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="G77" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="K77" s="22" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="14" t="n">
+      <c r="A78" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="B78" s="15" t="n">
+      <c r="B78" s="12" t="n">
         <f aca="false">Overview!$B$3+A78-1</f>
         <v>46463</v>
       </c>
-      <c r="C78" s="16" t="n">
-        <v>0.635416666666667</v>
-      </c>
-      <c r="D78" s="16" t="n">
-        <v>0.666666666666667</v>
-      </c>
-      <c r="E78" s="14" t="n">
+      <c r="C78" s="13" t="n">
+        <v>0.572916666666667</v>
+      </c>
+      <c r="D78" s="13" t="n">
+        <v>0.604166666666667</v>
+      </c>
+      <c r="E78" s="11" t="n">
         <f aca="false">ROUND((D78-C78)*1440,0)</f>
         <v>45</v>
       </c>
-      <c r="F78" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="G78" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="H78" s="14"/>
-      <c r="I78" s="14"/>
-      <c r="J78" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="K78" s="17" t="s">
-        <v>52</v>
+      <c r="F78" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="G78" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="H78" s="11"/>
+      <c r="I78" s="11"/>
+      <c r="J78" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="K78" s="18" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6095,28 +6134,28 @@
         <v>46463</v>
       </c>
       <c r="C79" s="16" t="n">
-        <v>0.666666666666667</v>
+        <v>0.604166666666667</v>
       </c>
       <c r="D79" s="16" t="n">
-        <v>0.729166666666667</v>
+        <v>0.625</v>
       </c>
       <c r="E79" s="14" t="n">
         <f aca="false">ROUND((D79-C79)*1440,0)</f>
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="F79" s="14" t="s">
-        <v>179</v>
+        <v>61</v>
       </c>
       <c r="G79" s="14" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="H79" s="14"/>
       <c r="I79" s="14"/>
       <c r="J79" s="14" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="K79" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6128,197 +6167,197 @@
         <v>46463</v>
       </c>
       <c r="C80" s="16" t="n">
-        <v>0.729166666666667</v>
+        <v>0.625</v>
       </c>
       <c r="D80" s="16" t="n">
-        <v>0.833333333333333</v>
+        <v>0.635416666666667</v>
       </c>
       <c r="E80" s="14" t="n">
         <f aca="false">ROUND((D80-C80)*1440,0)</f>
-        <v>150</v>
+        <v>15</v>
       </c>
       <c r="F80" s="14" t="s">
-        <v>101</v>
+        <v>57</v>
       </c>
       <c r="G80" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="H80" s="14"/>
-      <c r="I80" s="14"/>
+        <v>183</v>
+      </c>
+      <c r="H80" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="I80" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="J80" s="14" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="K80" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="11" t="n">
+      <c r="A81" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B81" s="12" t="n">
+      <c r="B81" s="15" t="n">
         <f aca="false">Overview!$B$3+A81-1</f>
         <v>46463</v>
       </c>
-      <c r="C81" s="13" t="n">
-        <v>0.833333333333333</v>
-      </c>
-      <c r="D81" s="13" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="E81" s="11" t="n">
+      <c r="C81" s="16" t="n">
+        <v>0.635416666666667</v>
+      </c>
+      <c r="D81" s="16" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="E81" s="14" t="n">
         <f aca="false">ROUND((D81-C81)*1440,0)</f>
-        <v>60</v>
-      </c>
-      <c r="F81" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="G81" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="H81" s="11"/>
-      <c r="I81" s="11"/>
-      <c r="J81" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="K81" s="18" t="s">
-        <v>52</v>
+        <v>45</v>
+      </c>
+      <c r="F81" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="G81" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="H81" s="14"/>
+      <c r="I81" s="14"/>
+      <c r="J81" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="K81" s="17" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="B82" s="12" t="n">
+      <c r="A82" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B82" s="15" t="n">
         <f aca="false">Overview!$B$3+A82-1</f>
-        <v>46464</v>
-      </c>
-      <c r="C82" s="13" t="n">
-        <v>0.3125</v>
-      </c>
-      <c r="D82" s="13" t="n">
-        <v>0.354166666666667</v>
-      </c>
-      <c r="E82" s="11" t="n">
+        <v>46463</v>
+      </c>
+      <c r="C82" s="16" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="D82" s="16" t="n">
+        <v>0.729166666666667</v>
+      </c>
+      <c r="E82" s="14" t="n">
         <f aca="false">ROUND((D82-C82)*1440,0)</f>
-        <v>60</v>
-      </c>
-      <c r="F82" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="G82" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="H82" s="11"/>
-      <c r="I82" s="11"/>
-      <c r="J82" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="K82" s="18" t="s">
-        <v>52</v>
+        <v>90</v>
+      </c>
+      <c r="F82" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="G82" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="H82" s="14"/>
+      <c r="I82" s="14"/>
+      <c r="J82" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="K82" s="17" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B83" s="15" t="n">
         <f aca="false">Overview!$B$3+A83-1</f>
-        <v>46464</v>
+        <v>46463</v>
       </c>
       <c r="C83" s="16" t="n">
-        <v>0.354166666666667</v>
+        <v>0.729166666666667</v>
       </c>
       <c r="D83" s="16" t="n">
-        <v>0.375</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="E83" s="14" t="n">
         <f aca="false">ROUND((D83-C83)*1440,0)</f>
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="F83" s="14" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="G83" s="14" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="H83" s="14"/>
       <c r="I83" s="14"/>
       <c r="J83" s="14" t="s">
-        <v>83</v>
+        <v>192</v>
       </c>
       <c r="K83" s="17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="14" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B84" s="12" t="n">
+        <f aca="false">Overview!$B$3+A84-1</f>
+        <v>46463</v>
+      </c>
+      <c r="C84" s="13" t="n">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="D84" s="13" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="E84" s="11" t="n">
+        <f aca="false">ROUND((D84-C84)*1440,0)</f>
+        <v>60</v>
+      </c>
+      <c r="F84" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="G84" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="H84" s="11"/>
+      <c r="I84" s="11"/>
+      <c r="J84" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="K84" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="B84" s="15" t="n">
-        <f aca="false">Overview!$B$3+A84-1</f>
-        <v>46464</v>
-      </c>
-      <c r="C84" s="16" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="D84" s="16" t="n">
-        <v>0.458333333333333</v>
-      </c>
-      <c r="E84" s="14" t="n">
-        <f aca="false">ROUND((D84-C84)*1440,0)</f>
-        <v>120</v>
-      </c>
-      <c r="F84" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G84" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="H84" s="14" t="s">
-        <v>186</v>
-      </c>
-      <c r="I84" s="14" t="n">
-        <v>70</v>
-      </c>
-      <c r="J84" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="K84" s="17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="B85" s="15" t="n">
+      <c r="B85" s="12" t="n">
         <f aca="false">Overview!$B$3+A85-1</f>
         <v>46464</v>
       </c>
-      <c r="C85" s="16" t="n">
-        <v>0.458333333333333</v>
-      </c>
-      <c r="D85" s="16" t="n">
-        <v>0.489583333333333</v>
-      </c>
-      <c r="E85" s="14" t="n">
+      <c r="C85" s="13" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="D85" s="13" t="n">
+        <v>0.354166666666667</v>
+      </c>
+      <c r="E85" s="11" t="n">
         <f aca="false">ROUND((D85-C85)*1440,0)</f>
-        <v>45</v>
-      </c>
-      <c r="F85" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="G85" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="H85" s="14"/>
-      <c r="I85" s="14"/>
-      <c r="J85" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="K85" s="17" t="s">
-        <v>52</v>
+        <v>60</v>
+      </c>
+      <c r="F85" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="G85" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="H85" s="11"/>
+      <c r="I85" s="11"/>
+      <c r="J85" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="K85" s="18" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6330,65 +6369,65 @@
         <v>46464</v>
       </c>
       <c r="C86" s="16" t="n">
-        <v>0.489583333333333</v>
+        <v>0.354166666666667</v>
       </c>
       <c r="D86" s="16" t="n">
-        <v>0.572916666666667</v>
+        <v>0.375</v>
       </c>
       <c r="E86" s="14" t="n">
         <f aca="false">ROUND((D86-C86)*1440,0)</f>
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="F86" s="14" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="G86" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="H86" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="I86" s="14" t="n">
-        <v>60</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="H86" s="14"/>
+      <c r="I86" s="14"/>
       <c r="J86" s="14" t="s">
-        <v>192</v>
+        <v>87</v>
       </c>
       <c r="K86" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="11" t="n">
+      <c r="A87" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B87" s="12" t="n">
+      <c r="B87" s="15" t="n">
         <f aca="false">Overview!$B$3+A87-1</f>
         <v>46464</v>
       </c>
-      <c r="C87" s="13" t="n">
-        <v>0.572916666666667</v>
-      </c>
-      <c r="D87" s="13" t="n">
-        <v>0.604166666666667</v>
-      </c>
-      <c r="E87" s="11" t="n">
+      <c r="C87" s="16" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D87" s="16" t="n">
+        <v>0.458333333333333</v>
+      </c>
+      <c r="E87" s="14" t="n">
         <f aca="false">ROUND((D87-C87)*1440,0)</f>
-        <v>45</v>
-      </c>
-      <c r="F87" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="G87" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="H87" s="11"/>
-      <c r="I87" s="11"/>
-      <c r="J87" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="K87" s="18" t="s">
-        <v>52</v>
+        <v>120</v>
+      </c>
+      <c r="F87" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="G87" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="H87" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="I87" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="J87" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="K87" s="17" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6400,30 +6439,28 @@
         <v>46464</v>
       </c>
       <c r="C88" s="16" t="n">
-        <v>0.604166666666667</v>
+        <v>0.458333333333333</v>
       </c>
       <c r="D88" s="16" t="n">
-        <v>0.65625</v>
+        <v>0.489583333333333</v>
       </c>
       <c r="E88" s="14" t="n">
         <f aca="false">ROUND((D88-C88)*1440,0)</f>
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="F88" s="14" t="s">
-        <v>195</v>
+        <v>69</v>
       </c>
       <c r="G88" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="H88" s="14" t="s">
-        <v>196</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="H88" s="14"/>
       <c r="I88" s="14"/>
       <c r="J88" s="14" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K88" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6435,65 +6472,65 @@
         <v>46464</v>
       </c>
       <c r="C89" s="16" t="n">
-        <v>0.65625</v>
+        <v>0.489583333333333</v>
       </c>
       <c r="D89" s="16" t="n">
-        <v>0.677083333333333</v>
+        <v>0.572916666666667</v>
       </c>
       <c r="E89" s="14" t="n">
         <f aca="false">ROUND((D89-C89)*1440,0)</f>
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="F89" s="14" t="s">
-        <v>179</v>
+        <v>57</v>
       </c>
       <c r="G89" s="14" t="s">
-        <v>198</v>
-      </c>
-      <c r="H89" s="14"/>
-      <c r="I89" s="14"/>
+        <v>200</v>
+      </c>
+      <c r="H89" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="I89" s="14" t="n">
+        <v>60</v>
+      </c>
       <c r="J89" s="14" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="K89" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="14" t="n">
+      <c r="A90" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="B90" s="15" t="n">
+      <c r="B90" s="12" t="n">
         <f aca="false">Overview!$B$3+A90-1</f>
         <v>46464</v>
       </c>
-      <c r="C90" s="16" t="n">
-        <v>0.677083333333333</v>
-      </c>
-      <c r="D90" s="16" t="n">
-        <v>0.802083333333333</v>
-      </c>
-      <c r="E90" s="14" t="n">
+      <c r="C90" s="13" t="n">
+        <v>0.572916666666667</v>
+      </c>
+      <c r="D90" s="13" t="n">
+        <v>0.604166666666667</v>
+      </c>
+      <c r="E90" s="11" t="n">
         <f aca="false">ROUND((D90-C90)*1440,0)</f>
-        <v>180</v>
-      </c>
-      <c r="F90" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G90" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="H90" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="I90" s="14" t="n">
-        <v>82</v>
-      </c>
-      <c r="J90" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="K90" s="17" t="s">
-        <v>52</v>
+        <v>45</v>
+      </c>
+      <c r="F90" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="G90" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="H90" s="11"/>
+      <c r="I90" s="11"/>
+      <c r="J90" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="K90" s="18" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6505,197 +6542,199 @@
         <v>46464</v>
       </c>
       <c r="C91" s="16" t="n">
-        <v>0.802083333333333</v>
+        <v>0.604166666666667</v>
       </c>
       <c r="D91" s="16" t="n">
-        <v>0.833333333333333</v>
+        <v>0.65625</v>
       </c>
       <c r="E91" s="14" t="n">
         <f aca="false">ROUND((D91-C91)*1440,0)</f>
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F91" s="14" t="s">
-        <v>101</v>
+        <v>205</v>
       </c>
       <c r="G91" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="H91" s="14"/>
+        <v>201</v>
+      </c>
+      <c r="H91" s="14" t="s">
+        <v>206</v>
+      </c>
       <c r="I91" s="14"/>
       <c r="J91" s="14" t="s">
-        <v>59</v>
+        <v>207</v>
       </c>
       <c r="K91" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="11" t="n">
+      <c r="A92" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B92" s="12" t="n">
+      <c r="B92" s="15" t="n">
         <f aca="false">Overview!$B$3+A92-1</f>
         <v>46464</v>
       </c>
-      <c r="C92" s="13" t="n">
-        <v>0.833333333333333</v>
-      </c>
-      <c r="D92" s="13" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="E92" s="11" t="n">
+      <c r="C92" s="16" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="D92" s="16" t="n">
+        <v>0.677083333333333</v>
+      </c>
+      <c r="E92" s="14" t="n">
         <f aca="false">ROUND((D92-C92)*1440,0)</f>
-        <v>60</v>
-      </c>
-      <c r="F92" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="G92" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="H92" s="11"/>
-      <c r="I92" s="11"/>
-      <c r="J92" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F92" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="G92" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="H92" s="14"/>
+      <c r="I92" s="14"/>
+      <c r="J92" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="K92" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B93" s="15" t="n">
+        <f aca="false">Overview!$B$3+A93-1</f>
+        <v>46464</v>
+      </c>
+      <c r="C93" s="16" t="n">
+        <v>0.677083333333333</v>
+      </c>
+      <c r="D93" s="16" t="n">
+        <v>0.802083333333333</v>
+      </c>
+      <c r="E93" s="14" t="n">
+        <f aca="false">ROUND((D93-C93)*1440,0)</f>
+        <v>180</v>
+      </c>
+      <c r="F93" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="G93" s="14" t="s">
         <v>201</v>
       </c>
-      <c r="K92" s="18" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="B93" s="12" t="n">
-        <f aca="false">Overview!$B$3+A93-1</f>
-        <v>46465</v>
-      </c>
-      <c r="C93" s="13" t="n">
-        <v>0.3125</v>
-      </c>
-      <c r="D93" s="13" t="n">
-        <v>0.354166666666667</v>
-      </c>
-      <c r="E93" s="11" t="n">
-        <f aca="false">ROUND((D93-C93)*1440,0)</f>
-        <v>60</v>
-      </c>
-      <c r="F93" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="G93" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="H93" s="11"/>
-      <c r="I93" s="11"/>
-      <c r="J93" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="K93" s="18" t="s">
-        <v>52</v>
+      <c r="H93" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="I93" s="14" t="n">
+        <v>82</v>
+      </c>
+      <c r="J93" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="K93" s="17" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B94" s="15" t="n">
         <f aca="false">Overview!$B$3+A94-1</f>
-        <v>46465</v>
+        <v>46464</v>
       </c>
       <c r="C94" s="16" t="n">
-        <v>0.354166666666667</v>
+        <v>0.802083333333333</v>
       </c>
       <c r="D94" s="16" t="n">
-        <v>0.375</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="E94" s="14" t="n">
         <f aca="false">ROUND((D94-C94)*1440,0)</f>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="F94" s="14" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="G94" s="14" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="H94" s="14"/>
       <c r="I94" s="14"/>
       <c r="J94" s="14" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="K94" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="B95" s="15" t="n">
+      <c r="A95" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B95" s="12" t="n">
         <f aca="false">Overview!$B$3+A95-1</f>
-        <v>46465</v>
-      </c>
-      <c r="C95" s="16" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="D95" s="16" t="n">
-        <v>0.416666666666667</v>
-      </c>
-      <c r="E95" s="14" t="n">
+        <v>46464</v>
+      </c>
+      <c r="C95" s="13" t="n">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="D95" s="13" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="E95" s="11" t="n">
         <f aca="false">ROUND((D95-C95)*1440,0)</f>
         <v>60</v>
       </c>
-      <c r="F95" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G95" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="H95" s="14" t="s">
-        <v>203</v>
-      </c>
-      <c r="I95" s="14" t="n">
-        <v>30</v>
-      </c>
-      <c r="J95" s="14" t="s">
-        <v>204</v>
-      </c>
-      <c r="K95" s="17" t="s">
-        <v>52</v>
+      <c r="F95" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="G95" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="H95" s="11"/>
+      <c r="I95" s="11"/>
+      <c r="J95" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="K95" s="18" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="14" t="n">
+      <c r="A96" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="B96" s="15" t="n">
+      <c r="B96" s="12" t="n">
         <f aca="false">Overview!$B$3+A96-1</f>
         <v>46465</v>
       </c>
-      <c r="C96" s="16" t="n">
-        <v>0.416666666666667</v>
-      </c>
-      <c r="D96" s="16" t="n">
-        <v>0.447916666666667</v>
-      </c>
-      <c r="E96" s="14" t="n">
+      <c r="C96" s="13" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="D96" s="13" t="n">
+        <v>0.354166666666667</v>
+      </c>
+      <c r="E96" s="11" t="n">
         <f aca="false">ROUND((D96-C96)*1440,0)</f>
-        <v>45</v>
-      </c>
-      <c r="F96" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="G96" s="14" t="s">
-        <v>203</v>
-      </c>
-      <c r="H96" s="14"/>
-      <c r="I96" s="14"/>
-      <c r="J96" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="K96" s="17" t="s">
-        <v>52</v>
+        <v>60</v>
+      </c>
+      <c r="F96" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="G96" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="H96" s="11"/>
+      <c r="I96" s="11"/>
+      <c r="J96" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="K96" s="18" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6707,32 +6746,28 @@
         <v>46465</v>
       </c>
       <c r="C97" s="16" t="n">
-        <v>0.447916666666667</v>
+        <v>0.354166666666667</v>
       </c>
       <c r="D97" s="16" t="n">
-        <v>0.489583333333333</v>
+        <v>0.375</v>
       </c>
       <c r="E97" s="14" t="n">
         <f aca="false">ROUND((D97-C97)*1440,0)</f>
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F97" s="14" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="G97" s="14" t="s">
-        <v>206</v>
-      </c>
-      <c r="H97" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="I97" s="14" t="n">
-        <v>35</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="H97" s="14"/>
+      <c r="I97" s="14"/>
       <c r="J97" s="14" t="s">
-        <v>208</v>
+        <v>87</v>
       </c>
       <c r="K97" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6744,28 +6779,32 @@
         <v>46465</v>
       </c>
       <c r="C98" s="16" t="n">
-        <v>0.489583333333333</v>
+        <v>0.375</v>
       </c>
       <c r="D98" s="16" t="n">
-        <v>0.520833333333333</v>
+        <v>0.416666666666667</v>
       </c>
       <c r="E98" s="14" t="n">
         <f aca="false">ROUND((D98-C98)*1440,0)</f>
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="F98" s="14" t="s">
-        <v>179</v>
+        <v>57</v>
       </c>
       <c r="G98" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="H98" s="14"/>
-      <c r="I98" s="14"/>
+        <v>175</v>
+      </c>
+      <c r="H98" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="I98" s="14" t="n">
+        <v>30</v>
+      </c>
       <c r="J98" s="14" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="K98" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6777,32 +6816,28 @@
         <v>46465</v>
       </c>
       <c r="C99" s="16" t="n">
-        <v>0.520833333333333</v>
+        <v>0.416666666666667</v>
       </c>
       <c r="D99" s="16" t="n">
-        <v>0.572916666666667</v>
+        <v>0.447916666666667</v>
       </c>
       <c r="E99" s="14" t="n">
         <f aca="false">ROUND((D99-C99)*1440,0)</f>
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="F99" s="14" t="s">
-        <v>53</v>
+        <v>189</v>
       </c>
       <c r="G99" s="14" t="s">
-        <v>210</v>
-      </c>
-      <c r="H99" s="14" t="s">
-        <v>211</v>
-      </c>
-      <c r="I99" s="14" t="n">
-        <v>40</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="H99" s="14"/>
+      <c r="I99" s="14"/>
       <c r="J99" s="14" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="K99" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6814,61 +6849,65 @@
         <v>46465</v>
       </c>
       <c r="C100" s="16" t="n">
-        <v>0.572916666666667</v>
+        <v>0.447916666666667</v>
       </c>
       <c r="D100" s="16" t="n">
-        <v>0.583333333333333</v>
+        <v>0.489583333333333</v>
       </c>
       <c r="E100" s="14" t="n">
         <f aca="false">ROUND((D100-C100)*1440,0)</f>
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="F100" s="14" t="s">
         <v>57</v>
       </c>
       <c r="G100" s="14" t="s">
-        <v>211</v>
-      </c>
-      <c r="H100" s="14"/>
-      <c r="I100" s="14"/>
+        <v>216</v>
+      </c>
+      <c r="H100" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="I100" s="14" t="n">
+        <v>35</v>
+      </c>
       <c r="J100" s="14" t="s">
-        <v>174</v>
+        <v>218</v>
       </c>
       <c r="K100" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="11" t="n">
+      <c r="A101" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="B101" s="12" t="n">
+      <c r="B101" s="15" t="n">
         <f aca="false">Overview!$B$3+A101-1</f>
         <v>46465</v>
       </c>
-      <c r="C101" s="13" t="n">
-        <v>0.583333333333333</v>
-      </c>
-      <c r="D101" s="13" t="n">
-        <v>0.614583333333333</v>
-      </c>
-      <c r="E101" s="11" t="n">
+      <c r="C101" s="16" t="n">
+        <v>0.489583333333333</v>
+      </c>
+      <c r="D101" s="16" t="n">
+        <v>0.520833333333333</v>
+      </c>
+      <c r="E101" s="14" t="n">
         <f aca="false">ROUND((D101-C101)*1440,0)</f>
         <v>45</v>
       </c>
-      <c r="F101" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="G101" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="H101" s="11"/>
-      <c r="I101" s="11"/>
-      <c r="J101" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="K101" s="18" t="s">
-        <v>52</v>
+      <c r="F101" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="G101" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="H101" s="14"/>
+      <c r="I101" s="14"/>
+      <c r="J101" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="K101" s="17" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6880,469 +6919,469 @@
         <v>46465</v>
       </c>
       <c r="C102" s="16" t="n">
-        <v>0.614583333333333</v>
+        <v>0.520833333333333</v>
       </c>
       <c r="D102" s="16" t="n">
-        <v>0.625</v>
+        <v>0.572916666666667</v>
       </c>
       <c r="E102" s="14" t="n">
         <f aca="false">ROUND((D102-C102)*1440,0)</f>
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="F102" s="14" t="s">
         <v>57</v>
       </c>
       <c r="G102" s="14" t="s">
-        <v>215</v>
-      </c>
-      <c r="H102" s="14"/>
-      <c r="I102" s="14"/>
+        <v>220</v>
+      </c>
+      <c r="H102" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="I102" s="14" t="n">
+        <v>40</v>
+      </c>
       <c r="J102" s="14" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="K102" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="19" t="n">
+      <c r="A103" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="B103" s="20" t="n">
+      <c r="B103" s="15" t="n">
         <f aca="false">Overview!$B$3+A103-1</f>
         <v>46465</v>
       </c>
-      <c r="C103" s="21" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="D103" s="21" t="n">
-        <v>0.652777777777778</v>
-      </c>
-      <c r="E103" s="19" t="n">
+      <c r="C103" s="16" t="n">
+        <v>0.572916666666667</v>
+      </c>
+      <c r="D103" s="16" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="E103" s="14" t="n">
         <f aca="false">ROUND((D103-C103)*1440,0)</f>
-        <v>40</v>
-      </c>
-      <c r="F103" s="19" t="s">
-        <v>217</v>
-      </c>
-      <c r="G103" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="H103" s="19" t="s">
-        <v>218</v>
-      </c>
-      <c r="I103" s="19"/>
-      <c r="J103" s="19" t="s">
-        <v>219</v>
-      </c>
-      <c r="K103" s="22" t="s">
-        <v>52</v>
+        <v>15</v>
+      </c>
+      <c r="F103" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="G103" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="H103" s="14"/>
+      <c r="I103" s="14"/>
+      <c r="J103" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="K103" s="17" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="14" t="n">
+      <c r="A104" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="B104" s="15" t="n">
+      <c r="B104" s="12" t="n">
         <f aca="false">Overview!$B$3+A104-1</f>
         <v>46465</v>
       </c>
-      <c r="C104" s="16" t="n">
-        <v>0.652777777777778</v>
-      </c>
-      <c r="D104" s="16" t="n">
-        <v>0.673611111111111</v>
-      </c>
-      <c r="E104" s="14" t="n">
+      <c r="C104" s="13" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="D104" s="13" t="n">
+        <v>0.614583333333333</v>
+      </c>
+      <c r="E104" s="11" t="n">
         <f aca="false">ROUND((D104-C104)*1440,0)</f>
-        <v>30</v>
-      </c>
-      <c r="F104" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="G104" s="14" t="s">
-        <v>218</v>
-      </c>
-      <c r="H104" s="14"/>
-      <c r="I104" s="14"/>
-      <c r="J104" s="14" t="s">
-        <v>220</v>
-      </c>
-      <c r="K104" s="17" t="s">
-        <v>52</v>
+        <v>45</v>
+      </c>
+      <c r="F104" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="G104" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="H104" s="11"/>
+      <c r="I104" s="11"/>
+      <c r="J104" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="K104" s="18" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="19" t="n">
+      <c r="A105" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="B105" s="20" t="n">
+      <c r="B105" s="15" t="n">
         <f aca="false">Overview!$B$3+A105-1</f>
         <v>46465</v>
       </c>
-      <c r="C105" s="21" t="n">
-        <v>0.673611111111111</v>
-      </c>
-      <c r="D105" s="21" t="n">
-        <v>0.6875</v>
-      </c>
-      <c r="E105" s="19" t="n">
+      <c r="C105" s="16" t="n">
+        <v>0.614583333333333</v>
+      </c>
+      <c r="D105" s="16" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E105" s="14" t="n">
         <f aca="false">ROUND((D105-C105)*1440,0)</f>
-        <v>20</v>
-      </c>
-      <c r="F105" s="19" t="s">
-        <v>217</v>
-      </c>
-      <c r="G105" s="19" t="s">
-        <v>218</v>
-      </c>
-      <c r="H105" s="19" t="s">
-        <v>221</v>
-      </c>
-      <c r="I105" s="19"/>
-      <c r="J105" s="19" t="s">
-        <v>222</v>
-      </c>
-      <c r="K105" s="22" t="s">
-        <v>52</v>
+        <v>15</v>
+      </c>
+      <c r="F105" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="G105" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="H105" s="14"/>
+      <c r="I105" s="14"/>
+      <c r="J105" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="K105" s="17" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="14" t="n">
+      <c r="A106" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="B106" s="15" t="n">
+      <c r="B106" s="20" t="n">
         <f aca="false">Overview!$B$3+A106-1</f>
         <v>46465</v>
       </c>
-      <c r="C106" s="16" t="n">
-        <v>0.6875</v>
-      </c>
-      <c r="D106" s="16" t="n">
-        <v>0.711805555555556</v>
-      </c>
-      <c r="E106" s="14" t="n">
+      <c r="C106" s="21" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="D106" s="21" t="n">
+        <v>0.652777777777778</v>
+      </c>
+      <c r="E106" s="19" t="n">
         <f aca="false">ROUND((D106-C106)*1440,0)</f>
-        <v>35</v>
-      </c>
-      <c r="F106" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="G106" s="14" t="s">
-        <v>221</v>
-      </c>
-      <c r="H106" s="14"/>
-      <c r="I106" s="14"/>
-      <c r="J106" s="14" t="s">
-        <v>223</v>
-      </c>
-      <c r="K106" s="17" t="s">
-        <v>52</v>
+        <v>40</v>
+      </c>
+      <c r="F106" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="G106" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="H106" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="I106" s="19"/>
+      <c r="J106" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="K106" s="22" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="19" t="n">
+      <c r="A107" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="B107" s="20" t="n">
+      <c r="B107" s="15" t="n">
         <f aca="false">Overview!$B$3+A107-1</f>
         <v>46465</v>
       </c>
-      <c r="C107" s="21" t="n">
-        <v>0.711805555555556</v>
-      </c>
-      <c r="D107" s="21" t="n">
-        <v>0.746527777777778</v>
-      </c>
-      <c r="E107" s="19" t="n">
+      <c r="C107" s="16" t="n">
+        <v>0.652777777777778</v>
+      </c>
+      <c r="D107" s="16" t="n">
+        <v>0.673611111111111</v>
+      </c>
+      <c r="E107" s="14" t="n">
         <f aca="false">ROUND((D107-C107)*1440,0)</f>
-        <v>50</v>
-      </c>
-      <c r="F107" s="19" t="s">
-        <v>217</v>
-      </c>
-      <c r="G107" s="19" t="s">
-        <v>221</v>
-      </c>
-      <c r="H107" s="19" t="s">
-        <v>224</v>
-      </c>
-      <c r="I107" s="19"/>
-      <c r="J107" s="19" t="s">
-        <v>225</v>
-      </c>
-      <c r="K107" s="22" t="s">
-        <v>52</v>
+        <v>30</v>
+      </c>
+      <c r="F107" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="G107" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="H107" s="14"/>
+      <c r="I107" s="14"/>
+      <c r="J107" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="K107" s="17" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="14" t="n">
+      <c r="A108" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="B108" s="15" t="n">
+      <c r="B108" s="20" t="n">
         <f aca="false">Overview!$B$3+A108-1</f>
         <v>46465</v>
       </c>
-      <c r="C108" s="16" t="n">
-        <v>0.746527777777778</v>
-      </c>
-      <c r="D108" s="16" t="n">
-        <v>0.767361111111111</v>
-      </c>
-      <c r="E108" s="14" t="n">
+      <c r="C108" s="21" t="n">
+        <v>0.673611111111111</v>
+      </c>
+      <c r="D108" s="21" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="E108" s="19" t="n">
         <f aca="false">ROUND((D108-C108)*1440,0)</f>
-        <v>30</v>
-      </c>
-      <c r="F108" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="G108" s="14" t="s">
-        <v>224</v>
-      </c>
-      <c r="H108" s="14"/>
-      <c r="I108" s="14"/>
-      <c r="J108" s="14" t="s">
-        <v>226</v>
-      </c>
-      <c r="K108" s="17" t="s">
-        <v>52</v>
+        <v>20</v>
+      </c>
+      <c r="F108" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="G108" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="H108" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="I108" s="19"/>
+      <c r="J108" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="K108" s="22" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="19" t="n">
+      <c r="A109" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="B109" s="20" t="n">
+      <c r="B109" s="15" t="n">
         <f aca="false">Overview!$B$3+A109-1</f>
         <v>46465</v>
       </c>
-      <c r="C109" s="21" t="n">
-        <v>0.767361111111111</v>
-      </c>
-      <c r="D109" s="21" t="n">
-        <v>0.788194444444444</v>
-      </c>
-      <c r="E109" s="19" t="n">
+      <c r="C109" s="16" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="D109" s="16" t="n">
+        <v>0.711805555555556</v>
+      </c>
+      <c r="E109" s="14" t="n">
         <f aca="false">ROUND((D109-C109)*1440,0)</f>
-        <v>30</v>
-      </c>
-      <c r="F109" s="19" t="s">
-        <v>217</v>
-      </c>
-      <c r="G109" s="19" t="s">
-        <v>224</v>
-      </c>
-      <c r="H109" s="19" t="s">
-        <v>211</v>
-      </c>
-      <c r="I109" s="19"/>
-      <c r="J109" s="19" t="s">
-        <v>227</v>
-      </c>
-      <c r="K109" s="22" t="s">
-        <v>52</v>
+        <v>35</v>
+      </c>
+      <c r="F109" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="G109" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="H109" s="14"/>
+      <c r="I109" s="14"/>
+      <c r="J109" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="K109" s="17" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="14" t="n">
+      <c r="A110" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="B110" s="15" t="n">
+      <c r="B110" s="20" t="n">
         <f aca="false">Overview!$B$3+A110-1</f>
         <v>46465</v>
       </c>
-      <c r="C110" s="16" t="n">
-        <v>0.791666666666667</v>
-      </c>
-      <c r="D110" s="16" t="n">
-        <v>0.8125</v>
-      </c>
-      <c r="E110" s="14" t="n">
+      <c r="C110" s="21" t="n">
+        <v>0.711805555555556</v>
+      </c>
+      <c r="D110" s="21" t="n">
+        <v>0.746527777777778</v>
+      </c>
+      <c r="E110" s="19" t="n">
         <f aca="false">ROUND((D110-C110)*1440,0)</f>
-        <v>30</v>
-      </c>
-      <c r="F110" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="G110" s="14" t="s">
-        <v>228</v>
-      </c>
-      <c r="H110" s="14"/>
-      <c r="I110" s="14"/>
-      <c r="J110" s="14" t="s">
-        <v>229</v>
-      </c>
-      <c r="K110" s="17" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="F110" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="G110" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="H110" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="I110" s="19"/>
+      <c r="J110" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="K110" s="22" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="11" t="n">
+      <c r="A111" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="B111" s="12" t="n">
+      <c r="B111" s="15" t="n">
         <f aca="false">Overview!$B$3+A111-1</f>
         <v>46465</v>
       </c>
-      <c r="C111" s="13" t="n">
-        <v>0.833333333333333</v>
-      </c>
-      <c r="D111" s="13" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="E111" s="11" t="n">
+      <c r="C111" s="16" t="n">
+        <v>0.746527777777778</v>
+      </c>
+      <c r="D111" s="16" t="n">
+        <v>0.767361111111111</v>
+      </c>
+      <c r="E111" s="14" t="n">
         <f aca="false">ROUND((D111-C111)*1440,0)</f>
-        <v>60</v>
-      </c>
-      <c r="F111" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="G111" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="H111" s="11"/>
-      <c r="I111" s="11"/>
-      <c r="J111" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="K111" s="18" t="s">
-        <v>52</v>
+        <v>30</v>
+      </c>
+      <c r="F111" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="G111" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="H111" s="14"/>
+      <c r="I111" s="14"/>
+      <c r="J111" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="K111" s="17" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="B112" s="12" t="n">
+      <c r="A112" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="B112" s="20" t="n">
         <f aca="false">Overview!$B$3+A112-1</f>
-        <v>46466</v>
-      </c>
-      <c r="C112" s="13" t="n">
-        <v>0.3125</v>
-      </c>
-      <c r="D112" s="13" t="n">
-        <v>0.354166666666667</v>
-      </c>
-      <c r="E112" s="11" t="n">
+        <v>46465</v>
+      </c>
+      <c r="C112" s="21" t="n">
+        <v>0.767361111111111</v>
+      </c>
+      <c r="D112" s="21" t="n">
+        <v>0.788194444444444</v>
+      </c>
+      <c r="E112" s="19" t="n">
         <f aca="false">ROUND((D112-C112)*1440,0)</f>
-        <v>60</v>
-      </c>
-      <c r="F112" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="G112" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="H112" s="11"/>
-      <c r="I112" s="11"/>
-      <c r="J112" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="K112" s="18" t="s">
-        <v>52</v>
+        <v>30</v>
+      </c>
+      <c r="F112" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="G112" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="H112" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="I112" s="19"/>
+      <c r="J112" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="K112" s="22" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B113" s="15" t="n">
         <f aca="false">Overview!$B$3+A113-1</f>
-        <v>46466</v>
+        <v>46465</v>
       </c>
       <c r="C113" s="16" t="n">
-        <v>0.354166666666667</v>
+        <v>0.791666666666667</v>
       </c>
       <c r="D113" s="16" t="n">
-        <v>0.375</v>
+        <v>0.8125</v>
       </c>
       <c r="E113" s="14" t="n">
         <f aca="false">ROUND((D113-C113)*1440,0)</f>
         <v>30</v>
       </c>
       <c r="F113" s="14" t="s">
-        <v>57</v>
+        <v>117</v>
       </c>
       <c r="G113" s="14" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="H113" s="14"/>
       <c r="I113" s="14"/>
       <c r="J113" s="14" t="s">
-        <v>83</v>
+        <v>239</v>
       </c>
       <c r="K113" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="14" t="n">
+      <c r="A114" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="B114" s="12" t="n">
+        <f aca="false">Overview!$B$3+A114-1</f>
+        <v>46465</v>
+      </c>
+      <c r="C114" s="13" t="n">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="D114" s="13" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="E114" s="11" t="n">
+        <f aca="false">ROUND((D114-C114)*1440,0)</f>
+        <v>60</v>
+      </c>
+      <c r="F114" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="G114" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="H114" s="11"/>
+      <c r="I114" s="11"/>
+      <c r="J114" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="K114" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="B114" s="15" t="n">
-        <f aca="false">Overview!$B$3+A114-1</f>
-        <v>46466</v>
-      </c>
-      <c r="C114" s="16" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="D114" s="16" t="n">
-        <v>0.489583333333333</v>
-      </c>
-      <c r="E114" s="14" t="n">
-        <f aca="false">ROUND((D114-C114)*1440,0)</f>
-        <v>165</v>
-      </c>
-      <c r="F114" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G114" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="H114" s="14" t="s">
-        <v>230</v>
-      </c>
-      <c r="I114" s="14" t="n">
-        <v>95</v>
-      </c>
-      <c r="J114" s="14" t="s">
-        <v>231</v>
-      </c>
-      <c r="K114" s="17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="115" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="B115" s="15" t="n">
+      <c r="B115" s="12" t="n">
         <f aca="false">Overview!$B$3+A115-1</f>
         <v>46466</v>
       </c>
-      <c r="C115" s="16" t="n">
-        <v>0.489583333333333</v>
-      </c>
-      <c r="D115" s="16" t="n">
-        <v>0.53125</v>
-      </c>
-      <c r="E115" s="14" t="n">
+      <c r="C115" s="13" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="D115" s="13" t="n">
+        <v>0.354166666666667</v>
+      </c>
+      <c r="E115" s="11" t="n">
         <f aca="false">ROUND((D115-C115)*1440,0)</f>
         <v>60</v>
       </c>
-      <c r="F115" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="G115" s="14" t="s">
-        <v>232</v>
-      </c>
-      <c r="H115" s="14"/>
-      <c r="I115" s="14"/>
-      <c r="J115" s="14" t="s">
-        <v>233</v>
-      </c>
-      <c r="K115" s="17" t="s">
-        <v>52</v>
+      <c r="F115" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="G115" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="H115" s="11"/>
+      <c r="I115" s="11"/>
+      <c r="J115" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="K115" s="18" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7354,32 +7393,28 @@
         <v>46466</v>
       </c>
       <c r="C116" s="16" t="n">
-        <v>0.53125</v>
+        <v>0.354166666666667</v>
       </c>
       <c r="D116" s="16" t="n">
-        <v>0.541666666666667</v>
+        <v>0.375</v>
       </c>
       <c r="E116" s="14" t="n">
         <f aca="false">ROUND((D116-C116)*1440,0)</f>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F116" s="14" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="G116" s="14" t="s">
-        <v>232</v>
-      </c>
-      <c r="H116" s="14" t="s">
-        <v>234</v>
-      </c>
-      <c r="I116" s="14" t="n">
-        <v>6</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="H116" s="14"/>
+      <c r="I116" s="14"/>
       <c r="J116" s="14" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="K116" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7391,64 +7426,68 @@
         <v>46466</v>
       </c>
       <c r="C117" s="16" t="n">
-        <v>0.541666666666667</v>
+        <v>0.375</v>
       </c>
       <c r="D117" s="16" t="n">
-        <v>0.569444444444444</v>
+        <v>0.447916666666667</v>
       </c>
       <c r="E117" s="14" t="n">
         <f aca="false">ROUND((D117-C117)*1440,0)</f>
-        <v>40</v>
+        <v>105</v>
       </c>
       <c r="F117" s="14" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="G117" s="14" t="s">
-        <v>234</v>
-      </c>
-      <c r="H117" s="14"/>
-      <c r="I117" s="14"/>
+        <v>30</v>
+      </c>
+      <c r="H117" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="I117" s="14" t="n">
+        <v>80</v>
+      </c>
       <c r="J117" s="14" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="K117" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="11" t="n">
+      <c r="A118" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="B118" s="12" t="n">
+      <c r="B118" s="15" t="n">
         <f aca="false">Overview!$B$3+A118-1</f>
         <v>46466</v>
       </c>
-      <c r="C118" s="13" t="n">
-        <v>0.572916666666667</v>
-      </c>
-      <c r="D118" s="13" t="n">
-        <v>0.614583333333333</v>
-      </c>
-      <c r="E118" s="11" t="n">
+      <c r="C118" s="16" t="n">
+        <v>0.447916666666667</v>
+      </c>
+      <c r="D118" s="16" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="E118" s="14" t="n">
         <f aca="false">ROUND((D118-C118)*1440,0)</f>
-        <v>60</v>
-      </c>
-      <c r="F118" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="G118" s="11" t="s">
-        <v>237</v>
-      </c>
-      <c r="H118" s="11"/>
-      <c r="I118" s="11"/>
-      <c r="J118" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="K118" s="18" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="119" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>30</v>
+      </c>
+      <c r="F118" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="G118" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="H118" s="14"/>
+      <c r="I118" s="14"/>
+      <c r="J118" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="K118" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="14" t="n">
         <v>8</v>
       </c>
@@ -7457,65 +7496,65 @@
         <v>46466</v>
       </c>
       <c r="C119" s="16" t="n">
-        <v>0.614583333333333</v>
+        <v>0.46875</v>
       </c>
       <c r="D119" s="16" t="n">
-        <v>0.645833333333333</v>
+        <v>0.489583333333333</v>
       </c>
       <c r="E119" s="14" t="n">
         <f aca="false">ROUND((D119-C119)*1440,0)</f>
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F119" s="14" t="s">
-        <v>138</v>
+        <v>57</v>
       </c>
       <c r="G119" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="H119" s="14"/>
-      <c r="I119" s="14"/>
+        <v>241</v>
+      </c>
+      <c r="H119" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="I119" s="14" t="n">
+        <v>20</v>
+      </c>
       <c r="J119" s="14" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="K119" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="14" t="n">
+      <c r="A120" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="B120" s="15" t="n">
+      <c r="B120" s="12" t="n">
         <f aca="false">Overview!$B$3+A120-1</f>
         <v>46466</v>
       </c>
-      <c r="C120" s="16" t="n">
-        <v>0.645833333333333</v>
-      </c>
-      <c r="D120" s="16" t="n">
-        <v>0.677083333333333</v>
-      </c>
-      <c r="E120" s="14" t="n">
+      <c r="C120" s="13" t="n">
+        <v>0.489583333333333</v>
+      </c>
+      <c r="D120" s="13" t="n">
+        <v>0.510416666666667</v>
+      </c>
+      <c r="E120" s="11" t="n">
         <f aca="false">ROUND((D120-C120)*1440,0)</f>
-        <v>45</v>
-      </c>
-      <c r="F120" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G120" s="14" t="s">
-        <v>241</v>
-      </c>
-      <c r="H120" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="I120" s="14" t="n">
-        <v>14</v>
-      </c>
-      <c r="J120" s="14" t="s">
-        <v>242</v>
-      </c>
-      <c r="K120" s="17" t="s">
-        <v>52</v>
+        <v>30</v>
+      </c>
+      <c r="F120" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="G120" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="H120" s="11"/>
+      <c r="I120" s="11"/>
+      <c r="J120" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="K120" s="18" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7527,33 +7566,33 @@
         <v>46466</v>
       </c>
       <c r="C121" s="16" t="n">
-        <v>0.677083333333333</v>
+        <v>0.510416666666667</v>
       </c>
       <c r="D121" s="16" t="n">
-        <v>0.697916666666667</v>
+        <v>0.520833333333333</v>
       </c>
       <c r="E121" s="14" t="n">
         <f aca="false">ROUND((D121-C121)*1440,0)</f>
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F121" s="14" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="G121" s="14" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="H121" s="14"/>
       <c r="I121" s="14"/>
       <c r="J121" s="14" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="K121" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="5" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -7705,7 +7744,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7713,19 +7752,19 @@
         <v>5</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7733,19 +7772,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7753,19 +7792,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7773,19 +7812,19 @@
         <v>1</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7793,19 +7832,19 @@
         <v>2</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>155</v>
+        <v>267</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7813,19 +7852,19 @@
         <v>2</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7833,19 +7872,19 @@
         <v>2</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7853,19 +7892,19 @@
         <v>3</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7873,19 +7912,19 @@
         <v>3</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7893,19 +7932,19 @@
         <v>3</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7913,19 +7952,19 @@
         <v>4</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>155</v>
+        <v>267</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7933,19 +7972,19 @@
         <v>4</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>155</v>
+        <v>267</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7953,19 +7992,19 @@
         <v>4</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7973,19 +8012,19 @@
         <v>5</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7993,19 +8032,19 @@
         <v>5</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8013,19 +8052,19 @@
         <v>5</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8033,19 +8072,19 @@
         <v>6</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C19" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="E19" s="14" t="s">
         <v>278</v>
       </c>
-      <c r="D19" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>272</v>
-      </c>
       <c r="F19" s="14" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8053,19 +8092,19 @@
         <v>6</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8073,19 +8112,19 @@
         <v>6</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8093,19 +8132,19 @@
         <v>7</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8113,19 +8152,19 @@
         <v>7</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C23" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="F23" s="14" t="s">
         <v>263</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="F23" s="14" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8133,19 +8172,19 @@
         <v>7</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8153,19 +8192,19 @@
         <v>8</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8173,24 +8212,24 @@
         <v>8</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
     </row>
   </sheetData>
@@ -8219,112 +8258,112 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
     </row>
   </sheetData>
@@ -8354,198 +8393,198 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
     </row>
   </sheetData>
@@ -8573,207 +8612,207 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="14" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="14" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
     </row>
   </sheetData>
@@ -8804,246 +8843,246 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="E4" s="23"/>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="E5" s="23"/>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="E6" s="23"/>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="E7" s="23"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="E8" s="23"/>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="E9" s="23"/>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="E10" s="23"/>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="E11" s="23"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="B12" s="14" t="s">
+        <v>438</v>
+      </c>
+      <c r="C12" s="14" t="s">
         <v>431</v>
       </c>
-      <c r="C12" s="14" t="s">
-        <v>424</v>
-      </c>
       <c r="D12" s="14" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="E12" s="23"/>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="E13" s="23"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="E14" s="23"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="E15" s="23"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
+        <v>449</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>450</v>
+      </c>
+      <c r="C16" s="14" t="s">
         <v>442</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>443</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>435</v>
       </c>
       <c r="D16" s="14"/>
       <c r="E16" s="23"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="E17" s="23"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="E18" s="23"/>
     </row>
@@ -9072,146 +9111,146 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
   </sheetData>
@@ -9239,90 +9278,90 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>489</v>
+        <v>496</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>495</v>
+        <v>502</v>
       </c>
     </row>
   </sheetData>

--- a/docs/itineraries/vaishno-devi-kashmir-8d-plan.xlsx
+++ b/docs/itineraries/vaishno-devi-kashmir-8d-plan.xlsx
@@ -35,12 +35,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1011" uniqueCount="563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="560">
   <si>
     <t xml:space="preserve">8 Days Vaishno Devi &amp; Kashmir Pilgrimage – Overview</t>
   </si>
   <si>
-    <t xml:space="preserve">Jammu – Katra – Vaishno Devi – Jammu – Srinagar – Gulmarg – Sonamarg – Pahalgam – Srinagar · 7 nights / 8 days · Departure: 13–20 March 2027</t>
+    <t xml:space="preserve">Jammu – Katra – Vaishno Devi – Jammu – Srinagar (Gulmarg, Sonamarg day trips) · 7 nights / 8 days · Departure: 13–20 March 2027</t>
   </si>
   <si>
     <t xml:space="preserve">Departure date (Day 1)</t>
@@ -106,426 +106,414 @@
     <t xml:space="preserve">Flight info</t>
   </si>
   <si>
-    <t xml:space="preserve">Srinagar → Gulmarg (gondola, Maharani Temple)</t>
+    <t xml:space="preserve">Srinagar → Gulmarg (gondola, Maharani Temple) → Srinagar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arrival at Jammu Airport on 13 March 2027 before 14:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Srinagar → Kheer Bhawani → Sonamarg → Srinagar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flight Jammu → Srinagar on 16 March 2027, departing between 11:00 and 12:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Srinagar → Avantipur → Martand → Pampore → Lal Chowk / Polo View shopping → Srinagar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Departure from Srinagar Airport on 20 March 2027 after 14:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Srinagar → Polo View shopping → Srinagar Airport departure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 nights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7N/8D: ₹1,00,000 per person + 5% GST, excluding flight charges</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other transport: 2 helicopter flights (5–8 min each), battery car Sanjichhat → Bhawan, Bhairon ropeway, flight Jammu → Srinagar (~50 min), Dal Lake shikara, Gulmarg gondola (Phase 1 and 2), Thajiwas pony ride, ~3 km downhill track on Day 3 (escorts assist seniors).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stays: Jammu (Days 1 and 3, same hotel; main luggage waits there on Day 2), Bhawan (Day 2), Srinagar (Days 4, 5, 6 and 7, same hotel; Gulmarg and Sonamarg are day trips).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days 1–3 are identical to the 4-day Vaishno Devi package; 4-day yatris leave the group at Jammu Airport on Day 4.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumptions: arrival at Jammu Airport at 14:00 on Day 1; breakfast 07:30–08:30 and departure from the hotel at 09:00 every day; helicopter slots 12:15 (Day 2) and 12:15 (Day 3); Jammu Airport by 09:20 on Day 4 for the 11:00–12:00 flight to Srinagar; Srinagar Airport by 12:30 on Day 8 for departures after 14:00. Day 6 is the longest road day (~167 km); back in Srinagar about 18:30.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 Days Vaishno Devi &amp; Kashmir Pilgrimage – Minute-to-Minute Plan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Departure: 13–20 March 2027. Draft as of 21 Oct 2026. Car km and drive times are approximate – verify on Google Maps. Edit Start/End times; Mins and totals recalculate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">End</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What we do</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Map</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arrival</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jammu Airport (IXJ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meet our representative, garland welcome, load luggage, headcount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open map</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Car</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jammu Airport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotel, Jammu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transfer to the hotel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Halt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check-in, freshen up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lunch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotel restaurant, Jammu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raghunath Temple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drive to the old-city temple complex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Darshan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Darshan of Sri Rama, Sita and Lakshmana; galleries of saligramas; group kirtan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ranbireshwar Temple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Short hop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Darshan of the 7.5 ft Shiva lingam and crystal lingams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raghunath Bazaar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Short hop to the old-city market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shopping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raghunath Bazaar, Jammu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dry fruits, Kalari cheese, Dogra handicrafts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return to the hotel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rest, kirtan; Day 2 briefing (photo ID, small bag for Bhawan; main luggage stays at this hotel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dinner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Breakfast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check-out with a small bag; main luggage stays at the Jammu hotel for Day 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Katra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drive via the Jammu–Katra highway; tea stop en route</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yatra Registration Counter, Katra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFID Yatra cards for every yatri (carry original photo ID)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Katra town</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Katra Helipad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drive to the helipad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reporting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Report for the allotted slot: ticket and ID check, baggage weighing, security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helicopter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sanjichhat Helipad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helicopter flight, about 5–8 minutes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Battery car</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5 km to Bhawan by battery car</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check-in at Bhawan accommodation; cloak room</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restaurant, Bhawan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rest, japa, group kirtan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holy Cave, Bhawan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Darshan of the three Pindis (Maha Kali, Maha Lakshmi, Maha Saraswati)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aarti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evening Aarti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wake-up, bath, get ready</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morning Aarti at the Holy Cave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rest, pack small bag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check-out, collect cloak-room items</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Walk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bhawan ropeway station</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Short walk (~300 m) to the ropeway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ropeway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bhairon Ghati</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ropeway ride, about 3 minutes plus queue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bhairon Baba Temple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Darshan of Bhairon Baba – completes the yatra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bhairon Temple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Downhill track ~3 km to the helipad (escorts assist seniors)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Report for the return slot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return flight, about 5–8 minutes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restaurant, Katra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick-up at the helipad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banganga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drive to Banganga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holy river where the Mother brought forth water with an arrow; temple darshan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Darshani Deodi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Traditional gateway of the yatra; group photo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Katra Main Bazaar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drive to the market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prasad, chunri, dry fruits, walnut and handicrafts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drive back to Jammu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check-in (same hotel as Day 1), collect main luggage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rest, kirtan; Day 4 briefing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check-out, load luggage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drive to the airport (3N/4D yatris say farewell here)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check-in and security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Srinagar Airport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flight Jammu → Srinagar (departs between 11:00 and 12:00)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baggage collection, meet the Srinagar driver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotel, Srinagar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drive to the hotel on Boulevard Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotel restaurant, Srinagar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lunch after check-in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shankaracharya Temple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drive up Gopadri hill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hilltop Shiva temple, ~240 steps; views of Dal Lake (phones not allowed – leave in car)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jyeshta Devi Temple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drive to Zethyar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Darshan of Mata Jyeshta Devi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rest, tea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shikara ghat, Dal Lake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Walk to the shikara ghat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shikara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dal Lake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunset shikara ride past Char Chinari and Nehru Park; kirtan on the boat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rest; Day 5 briefing (warm clothes for the Gulmarg day trip)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Breakfast (Amalaki Ekadashi – grain-free)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day trip – room retained; carry warm layers</t>
   </si>
   <si>
     <t xml:space="preserve">Gulmarg</t>
   </si>
   <si>
-    <t xml:space="preserve">Arrival at Jammu Airport on 13 March 2027 before 14:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gulmarg → Kheer Bhawani → Sonamarg → Srinagar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flight Jammu → Srinagar on 16 March 2027, departing between 11:00 and 12:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Srinagar → Avantipur → Martand → Pahalgam town → Srinagar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Departure from Srinagar Airport on 20 March 2027 after 14:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Srinagar → Pampore → Srinagar Airport departure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">—</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 nights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7N/8D: ₹1,00,000 per person + 5% GST, excluding flight charges</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other transport: 2 helicopter flights (5–8 min each), battery car Sanjichhat → Bhawan, Bhairon ropeway, flight Jammu → Srinagar (~50 min), Dal Lake shikara, Gulmarg gondola (Phase 1 and 2), Thajiwas pony ride, ~3 km downhill track on Day 3 (escorts assist seniors).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stays: Jammu (Days 1 and 3, same hotel; main luggage waits there on Day 2), Bhawan (Day 2), Srinagar (Days 4, 6 and 7, same hotel; main luggage waits there on Day 5), Gulmarg (Day 5).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days 1–3 are identical to the 4-day Vaishno Devi package; 4-day yatris leave the group at Jammu Airport on Day 4.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assumptions: arrival at Jammu Airport at 14:00 on Day 1; breakfast 07:30–08:30 and departure from the hotel at 09:00 every day; helicopter slots 12:15 (Day 2) and 12:15 (Day 3); Jammu Airport by 09:20 on Day 4 for the 11:00–12:00 flight to Srinagar; Srinagar Airport by 12:30 on Day 8 for departures after 14:00. Day 6 is the longest road day (~212 km); back in Srinagar about 19:15.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 Days Vaishno Devi &amp; Kashmir Pilgrimage – Minute-to-Minute Plan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Departure: 13–20 March 2027. Draft as of 21 Oct 2026. Car km and drive times are approximate – verify on Google Maps. Edit Start/End times; Mins and totals recalculate.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">End</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">From</t>
-  </si>
-  <si>
-    <t xml:space="preserve">To</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What we do</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google Map</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arrival</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jammu Airport (IXJ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meet our representative, garland welcome, load luggage, headcount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open map</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Car</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jammu Airport</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hotel, Jammu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transfer to the hotel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Halt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check-in, freshen up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lunch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hotel restaurant, Jammu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raghunath Temple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drive to the old-city temple complex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Darshan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Darshan of Sri Rama, Sita and Lakshmana; galleries of saligramas; group kirtan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ranbireshwar Temple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Short hop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Darshan of the 7.5 ft Shiva lingam and crystal lingams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bahu Fort (Bawe Wali Mata)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cross the Tawi to Bahu Fort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bawe Wali Mata Temple &amp; Bahu Fort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Darshan of Mahakali (Bawe Wali Mata); fort ramparts and Bagh-e-Bahu gardens at sunset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bahu Fort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peer Kho Cave Temple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drive along Circular Road</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cave shrine of the self-manifest Shiva lingam; evening aarti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Return to the hotel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freshen up; Day 2 briefing (photo ID, small bag for Bhawan; main luggage stays at this hotel)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dinner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Breakfast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check-out with a small bag; main luggage stays at the Jammu hotel for Day 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Katra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drive via the Jammu–Katra highway; tea stop en route</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Registration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yatra Registration Counter, Katra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RFID Yatra cards for every yatri (carry original photo ID)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Katra town</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Katra Helipad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drive to the helipad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reporting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Report for the allotted slot: ticket and ID check, baggage weighing, security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helicopter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sanjichhat Helipad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helicopter flight, about 5–8 minutes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Battery car</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5 km to Bhawan by battery car</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check-in at Bhawan accommodation; cloak room</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Restaurant, Bhawan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rest, japa, group kirtan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holy Cave, Bhawan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Darshan of the three Pindis (Maha Kali, Maha Lakshmi, Maha Saraswati)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aarti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evening Aarti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wake-up, bath, get ready</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Morning Aarti at the Holy Cave</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rest, pack small bag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check-out, collect cloak-room items</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Walk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bhawan ropeway station</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Short walk (~300 m) to the ropeway</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ropeway</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bhairon Ghati</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ropeway ride, about 3 minutes plus queue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bhairon Baba Temple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Darshan of Bhairon Baba – completes the yatra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bhairon Temple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Downhill track ~3 km to the helipad (escorts assist seniors)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Report for the return slot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Return flight, about 5–8 minutes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Restaurant, Katra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick-up at the helipad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Banganga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drive to Banganga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holy river where the Mother brought forth water with an arrow; temple darshan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Darshani Deodi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Traditional gateway of the yatra; group photo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Katra Main Bazaar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drive to the market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shopping</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prasad, chunri, dry fruits, walnut and handicrafts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drive back to Jammu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check-in (same hotel as Day 1), collect main luggage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rest, kirtan; Day 4 briefing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check-out, load luggage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drive to the airport (3N/4D yatris say farewell here)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airport</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check-in and security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Srinagar Airport</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flight Jammu → Srinagar (departs between 11:00 and 12:00)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baggage collection, meet the Srinagar driver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hotel, Srinagar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drive to the hotel on Boulevard Road</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hotel restaurant, Srinagar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lunch after check-in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shankaracharya Temple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drive up Gopadri hill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hilltop Shiva temple, ~240 steps; views of Dal Lake (phones not allowed – leave in car)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jyeshta Devi Temple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drive to Zethyar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Darshan of Mata Jyeshta Devi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rest, tea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hotel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shikara ghat, Dal Lake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Walk to the shikara ghat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shikara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dal Lake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunset shikara ride past Char Chinari and Nehru Park; kirtan on the boat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rest; Day 5 briefing (warm clothes, overnight bag for Gulmarg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Breakfast (Amalaki Ekadashi – grain-free)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check-out with an overnight bag; main luggage stays at the Srinagar hotel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Drive via Tangmarg (snow boots and coats at Tangmarg)</t>
   </si>
   <si>
@@ -544,12 +532,6 @@
     <t xml:space="preserve">Lunch – Ekadashi prasadam (fruits, potato, sabudana)</t>
   </si>
   <si>
-    <t xml:space="preserve">Hotel, Gulmarg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check-in</t>
-  </si>
-  <si>
     <t xml:space="preserve">Maharani Temple</t>
   </si>
   <si>
@@ -568,28 +550,25 @@
     <t xml:space="preserve">Gulmarg meadow viewpoints</t>
   </si>
   <si>
-    <t xml:space="preserve">Meadow walk, Himalayan views at sunset, group photo</t>
+    <t xml:space="preserve">Meadow walk, Himalayan views, group photo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return to Srinagar</t>
   </si>
   <si>
     <t xml:space="preserve">Rest, Ekadashi kirtan; Day 6 briefing</t>
   </si>
   <si>
-    <t xml:space="preserve">Hotel restaurant, Gulmarg</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dinner – Ekadashi prasadam</t>
   </si>
   <si>
     <t xml:space="preserve">Breakfast – Ekadashi parana (break fast 07:14–10:26)</t>
   </si>
   <si>
-    <t xml:space="preserve">Check-out</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kheer Bhawani Temple, Tulmulla</t>
   </si>
   <si>
-    <t xml:space="preserve">Drive via Tangmarg and Ganderbal</t>
+    <t xml:space="preserve">Drive via Ganderbal</t>
   </si>
   <si>
     <t xml:space="preserve">Kheer Bhawani Temple</t>
@@ -625,7 +604,7 @@
     <t xml:space="preserve">Sindh river banks and snow-peak views; group photo</t>
   </si>
   <si>
-    <t xml:space="preserve">Return to Srinagar</t>
+    <t xml:space="preserve">Rest, kirtan; Day 7 briefing</t>
   </si>
   <si>
     <t xml:space="preserve">Day trip – room retained</t>
@@ -655,28 +634,13 @@
     <t xml:space="preserve">Martand</t>
   </si>
   <si>
-    <t xml:space="preserve">Pahalgam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drive up the valley to Pahalgam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Restaurant, Pahalgam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pahalgam town</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stroll through Pahalgam town and market; group photo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rest, kirtan; Day 8 briefing (packing, flight ID)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pampore</t>
   </si>
   <si>
-    <t xml:space="preserve">Drive to the saffron town</t>
+    <t xml:space="preserve">Drive back towards Srinagar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restaurant, Pampore</t>
   </si>
   <si>
     <t xml:space="preserve">Pampore saffron and dry-fruit shops</t>
@@ -685,10 +649,40 @@
     <t xml:space="preserve">Saffron, walnuts, almonds and dry fruits</t>
   </si>
   <si>
+    <t xml:space="preserve">Lal Chowk, Srinagar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drive to the city centre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lal Chowk, Polo View and Residency Road markets, Srinagar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pashmina and Kashmiri shawls, papier-mâché, walnut-wood carvings, carpets, dry fruits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lal Chowk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rest; Day 8 briefing (packing, flight ID)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polo View Market, Srinagar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Short drive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Last-minute shopping: shawls, dry fruits, handicrafts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polo View Market</t>
+  </si>
+  <si>
     <t xml:space="preserve">Restaurant, Srinagar</t>
   </si>
   <si>
-    <t xml:space="preserve">Drive back towards the airport side of Srinagar</t>
+    <t xml:space="preserve">Drive towards the airport side of Srinagar</t>
   </si>
   <si>
     <t xml:space="preserve">Restaurant</t>
@@ -745,7 +739,7 @@
     <t xml:space="preserve">13:45–14:30</t>
   </si>
   <si>
-    <t xml:space="preserve">13:45–14:45</t>
+    <t xml:space="preserve">12:30–13:15</t>
   </si>
   <si>
     <t xml:space="preserve">11:15–12:15</t>
@@ -808,22 +802,22 @@
     <t xml:space="preserve">Weather and security delays at Srinagar airport</t>
   </si>
   <si>
-    <t xml:space="preserve">Night in Gulmarg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unhurried gondola, temple and sunset meadow; no return drive the same day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cold nights; limited hotel choice</t>
+    <t xml:space="preserve">Same Srinagar hotel for 4 nights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No packing and moving in Kashmir; Gulmarg and Sonamarg as day trips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">About 2 hrs each way to Gulmarg and 3 hrs back from Sonamarg</t>
   </si>
   <si>
     <t xml:space="preserve">Day 6 route</t>
   </si>
   <si>
-    <t xml:space="preserve">Kheer Bhawani and Sonamarg on the way back from Gulmarg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">About 212 km and 10 hours in the vehicle</t>
+    <t xml:space="preserve">Kheer Bhawani and Sonamarg in one day trip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">About 167 km and 6.5 hours in the vehicle</t>
   </si>
   <si>
     <t xml:space="preserve">Temple focus in Kashmir</t>
@@ -835,13 +829,13 @@
     <t xml:space="preserve">Martand and Avantipur are ruins, not living temples</t>
   </si>
   <si>
-    <t xml:space="preserve">Pahalgam day trip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avantipur, Martand and Pahalgam town in one day; back to the same Srinagar hotel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">About 200 km on the road</t>
+    <t xml:space="preserve">Day 7 temples and shopping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avantipur, Martand, Pampore saffron and a long shopping evening at Lal Chowk, Polo View and Residency Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martand and Avantipur are a long drive (about 135 km in the day)</t>
   </si>
   <si>
     <t xml:space="preserve">Food</t>
@@ -922,7 +916,7 @@
     <t xml:space="preserve">Check road status on Day 5 evening</t>
   </si>
   <si>
-    <t xml:space="preserve">Kheer Bhawani and Srinagar gardens instead; return straight from Gulmarg</t>
+    <t xml:space="preserve">Kheer Bhawani, then Srinagar gardens instead</t>
   </si>
   <si>
     <t xml:space="preserve">Gondola closed (wind) or sold out</t>
@@ -934,7 +928,7 @@
     <t xml:space="preserve">Yatra Organizers book gondola tickets early; go in the morning</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 1 only, or retry on Day 6 morning before leaving Gulmarg</t>
+    <t xml:space="preserve">Phase 1 only, or the meadow and Maharani Temple</t>
   </si>
   <si>
     <t xml:space="preserve">Long Day 6 tires seniors</t>
@@ -949,16 +943,16 @@
     <t xml:space="preserve">Skip the Thajiwas pony ride; rest at Sonamarg</t>
   </si>
   <si>
-    <t xml:space="preserve">Long Day 7 (~200 km)</t>
+    <t xml:space="preserve">Long Day 7 (~135 km, shopping until 19:00)</t>
   </si>
   <si>
     <t xml:space="preserve">Fatigue</t>
   </si>
   <si>
-    <t xml:space="preserve">Short stops at Avantipur and Martand; comfort stops</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skip Avantipur if running late</t>
+    <t xml:space="preserve">Short stops at Avantipur and Martand; rest stops while shopping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skip Avantipur if running late; shorten the shopping</t>
   </si>
   <si>
     <t xml:space="preserve">Pure-veg food hard to find in Gulmarg / Sonamarg</t>
@@ -1042,7 +1036,7 @@
     <t xml:space="preserve">Pack a small day bag for Bhawan; the main suitcase stays at the Jammu hotel</t>
   </si>
   <si>
-    <t xml:space="preserve">Pack an overnight bag for Gulmarg; the main suitcase stays at the Srinagar hotel</t>
+    <t xml:space="preserve">Carry warm layers on the Gulmarg and Sonamarg day trips</t>
   </si>
   <si>
     <t xml:space="preserve">Dress in warm layers in Kashmir, even in summer; carry a cap and gloves for Gulmarg and Sonamarg</t>
@@ -1072,7 +1066,7 @@
     <t xml:space="preserve">Rely on a prepaid SIM from outside J&amp;K – it will not work</t>
   </si>
   <si>
-    <t xml:space="preserve">Wander off alone in Srinagar or Pahalgam, especially after dark</t>
+    <t xml:space="preserve">Wander off alone in Srinagar markets, especially after dark</t>
   </si>
   <si>
     <t xml:space="preserve">Photograph security forces, checkpoints or military areas</t>
@@ -1195,7 +1189,7 @@
     <t xml:space="preserve">Group fares</t>
   </si>
   <si>
-    <t xml:space="preserve">Book hotels: Jammu (Days 1 and 3, same hotel; luggage storage on Day 2), Srinagar (Days 4, 6 and 7, same hotel; luggage storage on Day 5), Gulmarg (Day 5)</t>
+    <t xml:space="preserve">Book hotels: Jammu (Days 1 and 3, same hotel; luggage storage on Day 2), Srinagar (Days 4, 5, 6 and 7, same hotel)</t>
   </si>
   <si>
     <t xml:space="preserve">Ask for pure-veg kitchen</t>
@@ -1222,7 +1216,7 @@
     <t xml:space="preserve">T−15 days</t>
   </si>
   <si>
-    <t xml:space="preserve">Pre-book lunch restaurants (Jammu, Katra, Gulmarg, Sonamarg, Pahalgam, Srinagar)</t>
+    <t xml:space="preserve">Pre-book lunch restaurants (Jammu, Katra, Gulmarg, Sonamarg, Pampore, Srinagar)</t>
   </si>
   <si>
     <t xml:space="preserve">Tour leader</t>
@@ -1540,7 +1534,7 @@
     <t xml:space="preserve">From the ticket</t>
   </si>
   <si>
-    <t xml:space="preserve">Hotels: Jammu, Srinagar, Gulmarg</t>
+    <t xml:space="preserve">Hotels: Jammu, Srinagar</t>
   </si>
   <si>
     <t xml:space="preserve">Drivers: Jammu and Kashmir</t>
@@ -1615,10 +1609,7 @@
     <t xml:space="preserve">Per bed / room</t>
   </si>
   <si>
-    <t xml:space="preserve">Srinagar hotel, 3 nights (Days 4, 6 and 7)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gulmarg hotel, 1 night</t>
+    <t xml:space="preserve">Srinagar hotel, 4 nights (Days 4, 5, 6 and 7)</t>
   </si>
   <si>
     <t xml:space="preserve">Helicopter Katra ⇄ Sanjichhat</t>
@@ -1633,7 +1624,7 @@
     <t xml:space="preserve">Bhairon ropeway, Atka Aarti passes</t>
   </si>
   <si>
-    <t xml:space="preserve">Vehicles: Jammu–Katra (Days 1–4) and Kashmir (Days 4–8), about 689 km</t>
+    <t xml:space="preserve">Vehicles: Jammu–Katra (Days 1–4) and Kashmir (Days 4–8), about 593 km</t>
   </si>
   <si>
     <t xml:space="preserve">Per vehicle, split by seats</t>
@@ -1699,7 +1690,7 @@
     <t xml:space="preserve">Bhawan accommodation, Atka Aarti passes, Bhairon ropeway and Sanjichhat → Bhawan battery car booked</t>
   </si>
   <si>
-    <t xml:space="preserve">Hotels fixed in Jammu (Days 1 and 3), Srinagar (Days 4, 6 and 7) and Gulmarg (Day 5); replace area map links with exact pins</t>
+    <t xml:space="preserve">Hotels fixed in Jammu (Days 1 and 3) and Srinagar (Days 4, 5, 6 and 7); replace area map links with exact pins</t>
   </si>
   <si>
     <t xml:space="preserve">Kashmir DMC and vehicles fixed</t>
@@ -1708,13 +1699,13 @@
     <t xml:space="preserve">Gulmarg gondola tickets booked by Yatra Organizers (Phase 1 and Phase 2)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pure-veg lunch restaurants fixed for Gulmarg, Sonamarg and Pahalgam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify every car km and drive time on Google Maps, especially the Gulmarg → Kheer Bhawani leg on Day 6 and the Day 7 loop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Current security advisory and road status for Sonamarg and Pahalgam close to the travel date</t>
+    <t xml:space="preserve">Pure-veg lunch restaurants fixed for Gulmarg, Sonamarg and Pampore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify every car km and drive time on Google Maps, especially the Day 5 Gulmarg and Day 6 Sonamarg round trips and the Day 7 loop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current security advisory and road status for Gulmarg, Sonamarg and the Anantnag road close to the travel date</t>
   </si>
   <si>
     <t xml:space="preserve">Which 4-day yatris continue to Kashmir, and the farewell at Jammu Airport on Day 4 for those who return home</t>
@@ -2411,7 +2402,7 @@
       </c>
       <c r="D5" s="7" t="n">
         <f aca="false">SUMIF('Minute-by-Minute'!$A$5:$A$116,A5,'Minute-by-Minute'!$I$5:$I$116)</f>
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>14</v>
@@ -2534,10 +2525,10 @@
       </c>
       <c r="D9" s="7" t="n">
         <f aca="false">SUMIF('Minute-by-Minute'!$A$5:$A$116,A9,'Minute-by-Minute'!$I$5:$I$116)</f>
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F9" s="9" t="n">
         <f aca="false">_xlfn.MINIFS('Minute-by-Minute'!$C$5:$C$116,'Minute-by-Minute'!$A$5:$A$116,A9)</f>
@@ -2548,7 +2539,7 @@
         <v>0.875</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2560,11 +2551,11 @@
         <v>46464</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D10" s="7" t="n">
         <f aca="false">SUMIF('Minute-by-Minute'!$A$5:$A$116,A10,'Minute-by-Minute'!$I$5:$I$116)</f>
-        <v>212</v>
+        <v>167</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>21</v>
@@ -2578,7 +2569,7 @@
         <v>0.875</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2590,11 +2581,11 @@
         <v>46465</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D11" s="7" t="n">
         <f aca="false">SUMIF('Minute-by-Minute'!$A$5:$A$116,A11,'Minute-by-Minute'!$I$5:$I$116)</f>
-        <v>200</v>
+        <v>135</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>21</v>
@@ -2608,7 +2599,7 @@
         <v>0.875</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2620,14 +2611,14 @@
         <v>46466</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D12" s="7" t="n">
         <f aca="false">SUMIF('Minute-by-Minute'!$A$5:$A$116,A12,'Minute-by-Minute'!$I$5:$I$116)</f>
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F12" s="9" t="n">
         <f aca="false">_xlfn.MINIFS('Minute-by-Minute'!$C$5:$C$116,'Minute-by-Minute'!$A$5:$A$116,A12)</f>
@@ -2640,42 +2631,42 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D13" s="3" t="n">
         <f aca="false">SUM(D5:D12)</f>
-        <v>689</v>
+        <v>593</v>
       </c>
       <c r="E13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I14" s="10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -2705,100 +2696,100 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
+        <v>455</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>456</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>457</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="D1" s="11" t="s">
         <v>458</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>459</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>460</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>461</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="D2" s="12" t="s">
         <v>462</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>463</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
+        <v>463</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>464</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>465</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="D3" s="12" t="s">
         <v>466</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>467</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
+        <v>467</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>468</v>
+      </c>
+      <c r="C4" s="12" t="s">
         <v>469</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="D4" s="12" t="s">
         <v>470</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>471</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
+        <v>471</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>472</v>
+      </c>
+      <c r="C5" s="12" t="s">
         <v>473</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="D5" s="12" t="s">
         <v>474</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>475</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
+        <v>475</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>476</v>
+      </c>
+      <c r="C6" s="12" t="s">
         <v>477</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="D6" s="12" t="s">
         <v>478</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>479</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B7" s="12" t="s">
+        <v>479</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>480</v>
+      </c>
+      <c r="D7" s="12" t="s">
         <v>481</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>482</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>483</v>
       </c>
     </row>
   </sheetData>
@@ -2828,91 +2819,91 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
+        <v>482</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>483</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>484</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="D1" s="11" t="s">
         <v>485</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>486</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C2" s="24"/>
       <c r="D2" s="24"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C3" s="24"/>
       <c r="D3" s="24"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C4" s="24"/>
       <c r="D4" s="24"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C5" s="24"/>
       <c r="D5" s="24"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C6" s="24"/>
       <c r="D6" s="24"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C7" s="24"/>
       <c r="D7" s="24"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C8" s="24"/>
       <c r="D8" s="24"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B9" s="12"/>
       <c r="C9" s="24"/>
@@ -2920,7 +2911,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B10" s="12"/>
       <c r="C10" s="24"/>
@@ -2928,17 +2919,17 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C11" s="24"/>
       <c r="D11" s="24"/>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B12" s="12"/>
       <c r="C12" s="24"/>
@@ -2946,24 +2937,24 @@
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C13" s="24"/>
       <c r="D13" s="24"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C14" s="12"/>
       <c r="D14" s="12" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
   </sheetData>
@@ -2982,7 +2973,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50"/>
@@ -2993,257 +2984,245 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="25" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
+        <v>512</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>514</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="D4" s="6" t="s">
         <v>515</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>516</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
+        <v>516</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>517</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>518</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>519</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>520</v>
       </c>
       <c r="D5" s="26"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>520</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>521</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>522</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>523</v>
       </c>
       <c r="D6" s="26"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="D7" s="26"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="D8" s="26"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="D9" s="26"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="D10" s="26"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="D11" s="26"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>519</v>
+        <v>530</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="D12" s="26"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
+        <v>531</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>532</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>533</v>
-      </c>
       <c r="C13" s="7" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="D13" s="26"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>535</v>
+        <v>517</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="D14" s="26"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="D15" s="26"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="D16" s="26"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="D17" s="26"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="D18" s="26"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
+        <v>538</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>539</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="D19" s="26"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>519</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>523</v>
-      </c>
-      <c r="D19" s="26"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
+      <c r="D20" s="27" t="n">
+        <f aca="false">SUMIF(C5:C19,"Yes",D5:D19)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B21" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="C20" s="7" t="s">
-        <v>523</v>
-      </c>
-      <c r="D20" s="26"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
+      <c r="D21" s="28" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="D21" s="27" t="n">
-        <f aca="false">SUMIF(C5:C20,"Yes",D5:D20)</f>
+      <c r="D22" s="27" t="n">
+        <f aca="false">D20*(1+D21)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="s">
         <v>544</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="D22" s="28" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
-        <v>546</v>
-      </c>
-      <c r="D23" s="27" t="n">
-        <f aca="false">D21*(1+D22)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
-        <v>547</v>
       </c>
     </row>
   </sheetData>
@@ -3271,93 +3250,93 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B2" s="24"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="B3" s="24"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="B4" s="24"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="B5" s="24"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="B6" s="24"/>
     </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="B7" s="24"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="B8" s="24"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="B9" s="24"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="B10" s="24"/>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="B11" s="24"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B12" s="24"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B13" s="24"/>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B14" s="24"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="B15" s="24"/>
     </row>
@@ -3394,12 +3373,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3410,31 +3389,31 @@
         <v>6</v>
       </c>
       <c r="C4" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="E4" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="F4" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="G4" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="H4" s="11" t="s">
         <v>46</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>47</v>
       </c>
       <c r="I4" s="11" t="s">
         <v>8</v>
       </c>
       <c r="J4" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="K4" s="11" t="s">
         <v>48</v>
-      </c>
-      <c r="K4" s="11" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3456,18 +3435,18 @@
         <v>30</v>
       </c>
       <c r="F5" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" s="12" t="s">
         <v>50</v>
-      </c>
-      <c r="G5" s="12" t="s">
-        <v>51</v>
       </c>
       <c r="H5" s="12"/>
       <c r="I5" s="12"/>
       <c r="J5" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3489,22 +3468,22 @@
         <v>20</v>
       </c>
       <c r="F6" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="G6" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="H6" s="12" t="s">
         <v>55</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>56</v>
       </c>
       <c r="I6" s="12" t="n">
         <v>7</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K6" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3526,18 +3505,18 @@
         <v>25</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H7" s="12"/>
       <c r="I7" s="12"/>
       <c r="J7" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K7" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3559,18 +3538,18 @@
         <v>35</v>
       </c>
       <c r="F8" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="G8" s="16" t="s">
         <v>60</v>
-      </c>
-      <c r="G8" s="16" t="s">
-        <v>61</v>
       </c>
       <c r="H8" s="16"/>
       <c r="I8" s="16"/>
       <c r="J8" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K8" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3592,22 +3571,22 @@
         <v>15</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I9" s="12" t="n">
         <v>5</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3629,18 +3608,18 @@
         <v>40</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
       <c r="J10" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3662,22 +3641,22 @@
         <v>10</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>1</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3692,25 +3671,25 @@
         <v>0.704861111111111</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>0.722222222222222</v>
+        <v>0.729166666666667</v>
       </c>
       <c r="E12" s="12" t="n">
         <f aca="false">ROUND((D12-C12)*1440,0)</f>
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
       <c r="J12" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3722,35 +3701,35 @@
         <v>46459</v>
       </c>
       <c r="C13" s="14" t="n">
-        <v>0.722222222222222</v>
+        <v>0.729166666666667</v>
       </c>
       <c r="D13" s="14" t="n">
         <v>0.736111111111111</v>
       </c>
       <c r="E13" s="12" t="n">
         <f aca="false">ROUND((D13-C13)*1440,0)</f>
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H13" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="I13" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="I13" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="J13" s="12" t="s">
-        <v>70</v>
-      </c>
       <c r="K13" s="15" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="n">
         <v>1</v>
       </c>
@@ -3762,14 +3741,14 @@
         <v>0.736111111111111</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>0.770833333333333</v>
+        <v>0.777777777777778</v>
       </c>
       <c r="E14" s="12" t="n">
         <f aca="false">ROUND((D14-C14)*1440,0)</f>
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G14" s="12" t="s">
         <v>71</v>
@@ -3780,7 +3759,7 @@
         <v>72</v>
       </c>
       <c r="K14" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3792,35 +3771,35 @@
         <v>46459</v>
       </c>
       <c r="C15" s="14" t="n">
-        <v>0.770833333333333</v>
+        <v>0.777777777777778</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>0.788194444444444</v>
+        <v>0.791666666666667</v>
       </c>
       <c r="E15" s="12" t="n">
         <f aca="false">ROUND((D15-C15)*1440,0)</f>
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G15" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="I15" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="H15" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="I15" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="J15" s="12" t="s">
-        <v>75</v>
-      </c>
       <c r="K15" s="15" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="n">
         <v>1</v>
       </c>
@@ -3829,167 +3808,167 @@
         <v>46459</v>
       </c>
       <c r="C16" s="14" t="n">
-        <v>0.788194444444444</v>
+        <v>0.791666666666667</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>0.8125</v>
+        <v>0.84375</v>
       </c>
       <c r="E16" s="12" t="n">
         <f aca="false">ROUND((D16-C16)*1440,0)</f>
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="H16" s="12"/>
       <c r="I16" s="12"/>
       <c r="J16" s="12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="12" t="n">
+      <c r="A17" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B17" s="13" t="n">
+      <c r="B17" s="17" t="n">
         <f aca="false">Overview!$B$3+A17-1</f>
         <v>46459</v>
       </c>
-      <c r="C17" s="14" t="n">
-        <v>0.8125</v>
-      </c>
-      <c r="D17" s="14" t="n">
-        <v>0.826388888888889</v>
-      </c>
-      <c r="E17" s="12" t="n">
+      <c r="C17" s="18" t="n">
+        <v>0.84375</v>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>0.885416666666667</v>
+      </c>
+      <c r="E17" s="16" t="n">
         <f aca="false">ROUND((D17-C17)*1440,0)</f>
-        <v>20</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="G17" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="H17" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="I17" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="J17" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="K17" s="19" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="17" t="n">
+        <f aca="false">Overview!$B$3+A18-1</f>
+        <v>46460</v>
+      </c>
+      <c r="C18" s="18" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="D18" s="18" t="n">
+        <v>0.354166666666667</v>
+      </c>
+      <c r="E18" s="16" t="n">
+        <f aca="false">ROUND((D18-C18)*1440,0)</f>
+        <v>60</v>
+      </c>
+      <c r="F18" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="K17" s="15" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="B18" s="13" t="n">
-        <f aca="false">Overview!$B$3+A18-1</f>
-        <v>46459</v>
-      </c>
-      <c r="C18" s="14" t="n">
-        <v>0.826388888888889</v>
-      </c>
-      <c r="D18" s="14" t="n">
-        <v>0.84375</v>
-      </c>
-      <c r="E18" s="12" t="n">
-        <f aca="false">ROUND((D18-C18)*1440,0)</f>
-        <v>25</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="G18" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12" t="s">
+      <c r="G18" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K18" s="19" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="13" t="n">
+        <f aca="false">Overview!$B$3+A19-1</f>
+        <v>46460</v>
+      </c>
+      <c r="C19" s="14" t="n">
+        <v>0.354166666666667</v>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="E19" s="12" t="n">
+        <f aca="false">ROUND((D19-C19)*1440,0)</f>
+        <v>30</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="K18" s="15" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B19" s="17" t="n">
-        <f aca="false">Overview!$B$3+A19-1</f>
-        <v>46459</v>
-      </c>
-      <c r="C19" s="18" t="n">
-        <v>0.84375</v>
-      </c>
-      <c r="D19" s="18" t="n">
-        <v>0.885416666666667</v>
-      </c>
-      <c r="E19" s="16" t="n">
-        <f aca="false">ROUND((D19-C19)*1440,0)</f>
-        <v>60</v>
-      </c>
-      <c r="F19" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="G19" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="K19" s="19" t="s">
-        <v>53</v>
+      <c r="K19" s="15" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="16" t="n">
+      <c r="A20" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="B20" s="17" t="n">
+      <c r="B20" s="13" t="n">
         <f aca="false">Overview!$B$3+A20-1</f>
         <v>46460</v>
       </c>
-      <c r="C20" s="18" t="n">
-        <v>0.3125</v>
-      </c>
-      <c r="D20" s="18" t="n">
-        <v>0.354166666666667</v>
-      </c>
-      <c r="E20" s="16" t="n">
+      <c r="C20" s="14" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="E20" s="12" t="n">
         <f aca="false">ROUND((D20-C20)*1440,0)</f>
-        <v>60</v>
-      </c>
-      <c r="F20" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="I20" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="J20" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="G20" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="H20" s="16"/>
-      <c r="I20" s="16"/>
-      <c r="J20" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="K20" s="19" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K20" s="15" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="n">
         <v>2</v>
       </c>
@@ -3998,28 +3977,28 @@
         <v>46460</v>
       </c>
       <c r="C21" s="14" t="n">
-        <v>0.354166666666667</v>
+        <v>0.4375</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>0.375</v>
+        <v>0.458333333333333</v>
       </c>
       <c r="E21" s="12" t="n">
         <f aca="false">ROUND((D21-C21)*1440,0)</f>
         <v>30</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="H21" s="12"/>
       <c r="I21" s="12"/>
       <c r="J21" s="12" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="K21" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4031,35 +4010,35 @@
         <v>46460</v>
       </c>
       <c r="C22" s="14" t="n">
-        <v>0.375</v>
+        <v>0.458333333333333</v>
       </c>
       <c r="D22" s="14" t="n">
-        <v>0.4375</v>
+        <v>0.465277777777778</v>
       </c>
       <c r="E22" s="12" t="n">
         <f aca="false">ROUND((D22-C22)*1440,0)</f>
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="K22" s="15" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="n">
         <v>2</v>
       </c>
@@ -4068,17 +4047,17 @@
         <v>46460</v>
       </c>
       <c r="C23" s="14" t="n">
-        <v>0.4375</v>
+        <v>0.465277777777778</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>0.458333333333333</v>
+        <v>0.510416666666667</v>
       </c>
       <c r="E23" s="12" t="n">
         <f aca="false">ROUND((D23-C23)*1440,0)</f>
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G23" s="12" t="s">
         <v>85</v>
@@ -4086,150 +4065,146 @@
       <c r="H23" s="12"/>
       <c r="I23" s="12"/>
       <c r="J23" s="12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K23" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="12" t="n">
+      <c r="A24" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="B24" s="13" t="n">
+      <c r="B24" s="21" t="n">
         <f aca="false">Overview!$B$3+A24-1</f>
         <v>46460</v>
       </c>
-      <c r="C24" s="14" t="n">
-        <v>0.458333333333333</v>
-      </c>
-      <c r="D24" s="14" t="n">
-        <v>0.465277777777778</v>
-      </c>
-      <c r="E24" s="12" t="n">
+      <c r="C24" s="22" t="n">
+        <v>0.510416666666667</v>
+      </c>
+      <c r="D24" s="22" t="n">
+        <v>0.517361111111111</v>
+      </c>
+      <c r="E24" s="20" t="n">
         <f aca="false">ROUND((D24-C24)*1440,0)</f>
         <v>10</v>
       </c>
-      <c r="F24" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="G24" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="H24" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="I24" s="12" t="n">
+      <c r="F24" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="H24" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="I24" s="20"/>
+      <c r="J24" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="K24" s="23" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="J24" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="K24" s="15" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="B25" s="13" t="n">
+      <c r="B25" s="21" t="n">
         <f aca="false">Overview!$B$3+A25-1</f>
         <v>46460</v>
       </c>
-      <c r="C25" s="14" t="n">
-        <v>0.465277777777778</v>
-      </c>
-      <c r="D25" s="14" t="n">
-        <v>0.510416666666667</v>
-      </c>
-      <c r="E25" s="12" t="n">
+      <c r="C25" s="22" t="n">
+        <v>0.517361111111111</v>
+      </c>
+      <c r="D25" s="22" t="n">
+        <v>0.541666666666667</v>
+      </c>
+      <c r="E25" s="20" t="n">
         <f aca="false">ROUND((D25-C25)*1440,0)</f>
-        <v>65</v>
-      </c>
-      <c r="F25" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="G25" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="G25" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="H25" s="12"/>
-      <c r="I25" s="12"/>
-      <c r="J25" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="K25" s="15" t="s">
-        <v>53</v>
+      <c r="H25" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I25" s="20"/>
+      <c r="J25" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="K25" s="23" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="20" t="n">
+      <c r="A26" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="B26" s="21" t="n">
+      <c r="B26" s="13" t="n">
         <f aca="false">Overview!$B$3+A26-1</f>
         <v>46460</v>
       </c>
-      <c r="C26" s="22" t="n">
-        <v>0.510416666666667</v>
-      </c>
-      <c r="D26" s="22" t="n">
-        <v>0.517361111111111</v>
-      </c>
-      <c r="E26" s="20" t="n">
+      <c r="C26" s="14" t="n">
+        <v>0.541666666666667</v>
+      </c>
+      <c r="D26" s="14" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="E26" s="12" t="n">
         <f aca="false">ROUND((D26-C26)*1440,0)</f>
-        <v>10</v>
-      </c>
-      <c r="F26" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="G26" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="H26" s="20" t="s">
-        <v>93</v>
-      </c>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="K26" s="23" t="s">
-        <v>53</v>
+      <c r="K26" s="15" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="20" t="n">
+      <c r="A27" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="B27" s="21" t="n">
+      <c r="B27" s="17" t="n">
         <f aca="false">Overview!$B$3+A27-1</f>
         <v>46460</v>
       </c>
-      <c r="C27" s="22" t="n">
-        <v>0.517361111111111</v>
-      </c>
-      <c r="D27" s="22" t="n">
-        <v>0.541666666666667</v>
-      </c>
-      <c r="E27" s="20" t="n">
+      <c r="C27" s="18" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="D27" s="18" t="n">
+        <v>0.59375</v>
+      </c>
+      <c r="E27" s="16" t="n">
         <f aca="false">ROUND((D27-C27)*1440,0)</f>
-        <v>35</v>
-      </c>
-      <c r="F27" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="G27" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="G27" s="20" t="s">
-        <v>93</v>
-      </c>
-      <c r="H27" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="I27" s="20"/>
-      <c r="J27" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="K27" s="23" t="s">
-        <v>53</v>
+      <c r="H27" s="16"/>
+      <c r="I27" s="16"/>
+      <c r="J27" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="K27" s="19" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4241,17 +4216,17 @@
         <v>46460</v>
       </c>
       <c r="C28" s="14" t="n">
-        <v>0.541666666666667</v>
+        <v>0.59375</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>0.5625</v>
+        <v>0.6875</v>
       </c>
       <c r="E28" s="12" t="n">
         <f aca="false">ROUND((D28-C28)*1440,0)</f>
-        <v>30</v>
+        <v>135</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="G28" s="12" t="s">
         <v>17</v>
@@ -4259,43 +4234,43 @@
       <c r="H28" s="12"/>
       <c r="I28" s="12"/>
       <c r="J28" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K28" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="16" t="n">
+      <c r="A29" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="B29" s="17" t="n">
+      <c r="B29" s="13" t="n">
         <f aca="false">Overview!$B$3+A29-1</f>
         <v>46460</v>
       </c>
-      <c r="C29" s="18" t="n">
-        <v>0.5625</v>
-      </c>
-      <c r="D29" s="18" t="n">
-        <v>0.59375</v>
-      </c>
-      <c r="E29" s="16" t="n">
+      <c r="C29" s="14" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="D29" s="14" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E29" s="12" t="n">
         <f aca="false">ROUND((D29-C29)*1440,0)</f>
-        <v>45</v>
-      </c>
-      <c r="F29" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="G29" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="F29" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="G29" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="H29" s="16"/>
-      <c r="I29" s="16"/>
-      <c r="J29" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="K29" s="19" t="s">
-        <v>53</v>
+      <c r="K29" s="15" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4307,14 +4282,14 @@
         <v>46460</v>
       </c>
       <c r="C30" s="14" t="n">
-        <v>0.59375</v>
+        <v>0.75</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>0.6875</v>
+        <v>0.8125</v>
       </c>
       <c r="E30" s="12" t="n">
         <f aca="false">ROUND((D30-C30)*1440,0)</f>
-        <v>135</v>
+        <v>90</v>
       </c>
       <c r="F30" s="12" t="s">
         <v>99</v>
@@ -4328,62 +4303,62 @@
         <v>100</v>
       </c>
       <c r="K30" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="12" t="n">
+      <c r="A31" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="B31" s="13" t="n">
+      <c r="B31" s="17" t="n">
         <f aca="false">Overview!$B$3+A31-1</f>
         <v>46460</v>
       </c>
-      <c r="C31" s="14" t="n">
-        <v>0.6875</v>
-      </c>
-      <c r="D31" s="14" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E31" s="12" t="n">
+      <c r="C31" s="18" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="D31" s="18" t="n">
+        <v>0.854166666666667</v>
+      </c>
+      <c r="E31" s="16" t="n">
         <f aca="false">ROUND((D31-C31)*1440,0)</f>
-        <v>90</v>
-      </c>
-      <c r="F31" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="G31" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="K31" s="15" t="s">
-        <v>53</v>
+        <v>60</v>
+      </c>
+      <c r="F31" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G31" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="H31" s="16"/>
+      <c r="I31" s="16"/>
+      <c r="J31" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="K31" s="19" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B32" s="13" t="n">
         <f aca="false">Overview!$B$3+A32-1</f>
-        <v>46460</v>
+        <v>46461</v>
       </c>
       <c r="C32" s="14" t="n">
-        <v>0.75</v>
+        <v>0.1875</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>0.8125</v>
+        <v>0.229166666666667</v>
       </c>
       <c r="E32" s="12" t="n">
         <f aca="false">ROUND((D32-C32)*1440,0)</f>
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>103</v>
+        <v>57</v>
       </c>
       <c r="G32" s="12" t="s">
         <v>17</v>
@@ -4391,43 +4366,43 @@
       <c r="H32" s="12"/>
       <c r="I32" s="12"/>
       <c r="J32" s="12" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="K32" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="B33" s="17" t="n">
+      <c r="A33" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="B33" s="13" t="n">
         <f aca="false">Overview!$B$3+A33-1</f>
-        <v>46460</v>
-      </c>
-      <c r="C33" s="18" t="n">
-        <v>0.8125</v>
-      </c>
-      <c r="D33" s="18" t="n">
-        <v>0.854166666666667</v>
-      </c>
-      <c r="E33" s="16" t="n">
+        <v>46461</v>
+      </c>
+      <c r="C33" s="14" t="n">
+        <v>0.229166666666667</v>
+      </c>
+      <c r="D33" s="14" t="n">
+        <v>0.291666666666667</v>
+      </c>
+      <c r="E33" s="12" t="n">
         <f aca="false">ROUND((D33-C33)*1440,0)</f>
-        <v>60</v>
-      </c>
-      <c r="F33" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="G33" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="H33" s="16"/>
-      <c r="I33" s="16"/>
-      <c r="J33" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="K33" s="19" t="s">
-        <v>53</v>
+        <v>90</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="G33" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="H33" s="12"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="K33" s="15" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4439,17 +4414,17 @@
         <v>46461</v>
       </c>
       <c r="C34" s="14" t="n">
-        <v>0.1875</v>
+        <v>0.291666666666667</v>
       </c>
       <c r="D34" s="14" t="n">
-        <v>0.229166666666667</v>
+        <v>0.3125</v>
       </c>
       <c r="E34" s="12" t="n">
         <f aca="false">ROUND((D34-C34)*1440,0)</f>
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="G34" s="12" t="s">
         <v>17</v>
@@ -4457,43 +4432,43 @@
       <c r="H34" s="12"/>
       <c r="I34" s="12"/>
       <c r="J34" s="12" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K34" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="12" t="n">
+      <c r="A35" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="B35" s="13" t="n">
+      <c r="B35" s="17" t="n">
         <f aca="false">Overview!$B$3+A35-1</f>
         <v>46461</v>
       </c>
-      <c r="C35" s="14" t="n">
-        <v>0.229166666666667</v>
-      </c>
-      <c r="D35" s="14" t="n">
-        <v>0.291666666666667</v>
-      </c>
-      <c r="E35" s="12" t="n">
+      <c r="C35" s="18" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="D35" s="18" t="n">
+        <v>0.354166666666667</v>
+      </c>
+      <c r="E35" s="16" t="n">
         <f aca="false">ROUND((D35-C35)*1440,0)</f>
-        <v>90</v>
-      </c>
-      <c r="F35" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="G35" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="H35" s="12"/>
-      <c r="I35" s="12"/>
-      <c r="J35" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="K35" s="15" t="s">
-        <v>53</v>
+        <v>60</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G35" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="H35" s="16"/>
+      <c r="I35" s="16"/>
+      <c r="J35" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K35" s="19" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4505,17 +4480,17 @@
         <v>46461</v>
       </c>
       <c r="C36" s="14" t="n">
-        <v>0.291666666666667</v>
+        <v>0.354166666666667</v>
       </c>
       <c r="D36" s="14" t="n">
-        <v>0.3125</v>
+        <v>0.375</v>
       </c>
       <c r="E36" s="12" t="n">
         <f aca="false">ROUND((D36-C36)*1440,0)</f>
         <v>30</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>99</v>
+        <v>57</v>
       </c>
       <c r="G36" s="12" t="s">
         <v>17</v>
@@ -4523,76 +4498,80 @@
       <c r="H36" s="12"/>
       <c r="I36" s="12"/>
       <c r="J36" s="12" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="K36" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="16" t="n">
+      <c r="A37" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="B37" s="17" t="n">
+      <c r="B37" s="13" t="n">
         <f aca="false">Overview!$B$3+A37-1</f>
         <v>46461</v>
       </c>
-      <c r="C37" s="18" t="n">
-        <v>0.3125</v>
-      </c>
-      <c r="D37" s="18" t="n">
-        <v>0.354166666666667</v>
-      </c>
-      <c r="E37" s="16" t="n">
+      <c r="C37" s="14" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D37" s="14" t="n">
+        <v>0.385416666666667</v>
+      </c>
+      <c r="E37" s="12" t="n">
         <f aca="false">ROUND((D37-C37)*1440,0)</f>
-        <v>60</v>
-      </c>
-      <c r="F37" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="G37" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="H37" s="16"/>
-      <c r="I37" s="16"/>
-      <c r="J37" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="K37" s="19" t="s">
-        <v>53</v>
+        <v>15</v>
+      </c>
+      <c r="F37" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="H37" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="I37" s="12"/>
+      <c r="J37" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="K37" s="15" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="12" t="n">
+      <c r="A38" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="B38" s="13" t="n">
+      <c r="B38" s="21" t="n">
         <f aca="false">Overview!$B$3+A38-1</f>
         <v>46461</v>
       </c>
-      <c r="C38" s="14" t="n">
-        <v>0.354166666666667</v>
-      </c>
-      <c r="D38" s="14" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E38" s="12" t="n">
+      <c r="C38" s="22" t="n">
+        <v>0.385416666666667</v>
+      </c>
+      <c r="D38" s="22" t="n">
+        <v>0.399305555555556</v>
+      </c>
+      <c r="E38" s="20" t="n">
         <f aca="false">ROUND((D38-C38)*1440,0)</f>
-        <v>30</v>
-      </c>
-      <c r="F38" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="G38" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="H38" s="12"/>
-      <c r="I38" s="12"/>
-      <c r="J38" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F38" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="K38" s="15" t="s">
-        <v>53</v>
+      <c r="G38" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="H38" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="I38" s="20"/>
+      <c r="J38" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="K38" s="23" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4604,65 +4583,63 @@
         <v>46461</v>
       </c>
       <c r="C39" s="14" t="n">
-        <v>0.375</v>
+        <v>0.399305555555556</v>
       </c>
       <c r="D39" s="14" t="n">
-        <v>0.385416666666667</v>
+        <v>0.427083333333333</v>
       </c>
       <c r="E39" s="12" t="n">
         <f aca="false">ROUND((D39-C39)*1440,0)</f>
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>109</v>
+        <v>63</v>
       </c>
       <c r="G39" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="H39" s="12" t="s">
-        <v>110</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="H39" s="12"/>
       <c r="I39" s="12"/>
       <c r="J39" s="12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K39" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="20" t="n">
+      <c r="A40" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="B40" s="21" t="n">
+      <c r="B40" s="13" t="n">
         <f aca="false">Overview!$B$3+A40-1</f>
         <v>46461</v>
       </c>
-      <c r="C40" s="22" t="n">
-        <v>0.385416666666667</v>
-      </c>
-      <c r="D40" s="22" t="n">
-        <v>0.399305555555556</v>
-      </c>
-      <c r="E40" s="20" t="n">
+      <c r="C40" s="14" t="n">
+        <v>0.427083333333333</v>
+      </c>
+      <c r="D40" s="14" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="E40" s="12" t="n">
         <f aca="false">ROUND((D40-C40)*1440,0)</f>
-        <v>20</v>
-      </c>
-      <c r="F40" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="G40" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="H40" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="F40" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="G40" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="I40" s="20"/>
-      <c r="J40" s="20" t="s">
+      <c r="H40" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="I40" s="12"/>
+      <c r="J40" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="K40" s="23" t="s">
-        <v>53</v>
+      <c r="K40" s="15" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4674,63 +4651,63 @@
         <v>46461</v>
       </c>
       <c r="C41" s="14" t="n">
-        <v>0.399305555555556</v>
+        <v>0.46875</v>
       </c>
       <c r="D41" s="14" t="n">
-        <v>0.427083333333333</v>
+        <v>0.510416666666667</v>
       </c>
       <c r="E41" s="12" t="n">
         <f aca="false">ROUND((D41-C41)*1440,0)</f>
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="G41" s="12" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="H41" s="12"/>
       <c r="I41" s="12"/>
       <c r="J41" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K41" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="12" t="n">
+      <c r="A42" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="B42" s="13" t="n">
+      <c r="B42" s="21" t="n">
         <f aca="false">Overview!$B$3+A42-1</f>
         <v>46461</v>
       </c>
-      <c r="C42" s="14" t="n">
-        <v>0.427083333333333</v>
-      </c>
-      <c r="D42" s="14" t="n">
-        <v>0.46875</v>
-      </c>
-      <c r="E42" s="12" t="n">
+      <c r="C42" s="22" t="n">
+        <v>0.510416666666667</v>
+      </c>
+      <c r="D42" s="22" t="n">
+        <v>0.517361111111111</v>
+      </c>
+      <c r="E42" s="20" t="n">
         <f aca="false">ROUND((D42-C42)*1440,0)</f>
-        <v>60</v>
-      </c>
-      <c r="F42" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="G42" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="H42" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="I42" s="12"/>
-      <c r="J42" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="K42" s="15" t="s">
-        <v>53</v>
+        <v>10</v>
+      </c>
+      <c r="F42" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="G42" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="H42" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="I42" s="20"/>
+      <c r="J42" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="K42" s="23" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4742,63 +4719,65 @@
         <v>46461</v>
       </c>
       <c r="C43" s="14" t="n">
-        <v>0.46875</v>
+        <v>0.517361111111111</v>
       </c>
       <c r="D43" s="14" t="n">
-        <v>0.510416666666667</v>
+        <v>0.527777777777778</v>
       </c>
       <c r="E43" s="12" t="n">
         <f aca="false">ROUND((D43-C43)*1440,0)</f>
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="G43" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="H43" s="12"/>
-      <c r="I43" s="12"/>
+        <v>85</v>
+      </c>
+      <c r="H43" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="I43" s="12" t="n">
+        <v>2</v>
+      </c>
       <c r="J43" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K43" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="20" t="n">
+      <c r="A44" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="B44" s="21" t="n">
+      <c r="B44" s="17" t="n">
         <f aca="false">Overview!$B$3+A44-1</f>
         <v>46461</v>
       </c>
-      <c r="C44" s="22" t="n">
-        <v>0.510416666666667</v>
-      </c>
-      <c r="D44" s="22" t="n">
-        <v>0.517361111111111</v>
-      </c>
-      <c r="E44" s="20" t="n">
+      <c r="C44" s="18" t="n">
+        <v>0.527777777777778</v>
+      </c>
+      <c r="D44" s="18" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="E44" s="16" t="n">
         <f aca="false">ROUND((D44-C44)*1440,0)</f>
-        <v>10</v>
-      </c>
-      <c r="F44" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="G44" s="20" t="s">
-        <v>93</v>
-      </c>
-      <c r="H44" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="I44" s="20"/>
-      <c r="J44" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="K44" s="23" t="s">
-        <v>53</v>
+        <v>50</v>
+      </c>
+      <c r="F44" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="G44" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="H44" s="16"/>
+      <c r="I44" s="16"/>
+      <c r="J44" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="K44" s="19" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4810,65 +4789,65 @@
         <v>46461</v>
       </c>
       <c r="C45" s="14" t="n">
-        <v>0.517361111111111</v>
+        <v>0.5625</v>
       </c>
       <c r="D45" s="14" t="n">
-        <v>0.527777777777778</v>
+        <v>0.572916666666667</v>
       </c>
       <c r="E45" s="12" t="n">
         <f aca="false">ROUND((D45-C45)*1440,0)</f>
         <v>15</v>
       </c>
       <c r="F45" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G45" s="12" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H45" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J45" s="12" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K45" s="15" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="16" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="B46" s="17" t="n">
+      <c r="B46" s="13" t="n">
         <f aca="false">Overview!$B$3+A46-1</f>
         <v>46461</v>
       </c>
-      <c r="C46" s="18" t="n">
-        <v>0.527777777777778</v>
-      </c>
-      <c r="D46" s="18" t="n">
-        <v>0.5625</v>
-      </c>
-      <c r="E46" s="16" t="n">
+      <c r="C46" s="14" t="n">
+        <v>0.572916666666667</v>
+      </c>
+      <c r="D46" s="14" t="n">
+        <v>0.604166666666667</v>
+      </c>
+      <c r="E46" s="12" t="n">
         <f aca="false">ROUND((D46-C46)*1440,0)</f>
-        <v>50</v>
-      </c>
-      <c r="F46" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="G46" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F46" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="G46" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="H46" s="12"/>
+      <c r="I46" s="12"/>
+      <c r="J46" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="H46" s="16"/>
-      <c r="I46" s="16"/>
-      <c r="J46" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="K46" s="19" t="s">
-        <v>53</v>
+      <c r="K46" s="15" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4880,35 +4859,35 @@
         <v>46461</v>
       </c>
       <c r="C47" s="14" t="n">
-        <v>0.5625</v>
+        <v>0.604166666666667</v>
       </c>
       <c r="D47" s="14" t="n">
-        <v>0.572916666666667</v>
+        <v>0.611111111111111</v>
       </c>
       <c r="E47" s="12" t="n">
         <f aca="false">ROUND((D47-C47)*1440,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G47" s="12" t="s">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="H47" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J47" s="12" t="s">
-        <v>124</v>
+        <v>66</v>
       </c>
       <c r="K47" s="15" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="12" t="n">
         <v>3</v>
       </c>
@@ -4917,28 +4896,28 @@
         <v>46461</v>
       </c>
       <c r="C48" s="14" t="n">
-        <v>0.572916666666667</v>
+        <v>0.611111111111111</v>
       </c>
       <c r="D48" s="14" t="n">
-        <v>0.604166666666667</v>
+        <v>0.631944444444444</v>
       </c>
       <c r="E48" s="12" t="n">
         <f aca="false">ROUND((D48-C48)*1440,0)</f>
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F48" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G48" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H48" s="12"/>
       <c r="I48" s="12"/>
       <c r="J48" s="12" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K48" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4950,32 +4929,32 @@
         <v>46461</v>
       </c>
       <c r="C49" s="14" t="n">
-        <v>0.604166666666667</v>
+        <v>0.631944444444444</v>
       </c>
       <c r="D49" s="14" t="n">
-        <v>0.611111111111111</v>
+        <v>0.642361111111111</v>
       </c>
       <c r="E49" s="12" t="n">
         <f aca="false">ROUND((D49-C49)*1440,0)</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F49" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G49" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H49" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J49" s="12" t="s">
-        <v>67</v>
+        <v>125</v>
       </c>
       <c r="K49" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4987,28 +4966,28 @@
         <v>46461</v>
       </c>
       <c r="C50" s="14" t="n">
-        <v>0.611111111111111</v>
+        <v>0.642361111111111</v>
       </c>
       <c r="D50" s="14" t="n">
-        <v>0.631944444444444</v>
+        <v>0.6875</v>
       </c>
       <c r="E50" s="12" t="n">
         <f aca="false">ROUND((D50-C50)*1440,0)</f>
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="F50" s="12" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G50" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H50" s="12"/>
       <c r="I50" s="12"/>
       <c r="J50" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K50" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5020,32 +4999,32 @@
         <v>46461</v>
       </c>
       <c r="C51" s="14" t="n">
-        <v>0.631944444444444</v>
+        <v>0.6875</v>
       </c>
       <c r="D51" s="14" t="n">
-        <v>0.642361111111111</v>
+        <v>0.75</v>
       </c>
       <c r="E51" s="12" t="n">
         <f aca="false">ROUND((D51-C51)*1440,0)</f>
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="F51" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G51" s="12" t="s">
-        <v>126</v>
+        <v>79</v>
       </c>
       <c r="H51" s="12" t="s">
-        <v>128</v>
+        <v>55</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="J51" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="K51" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5057,28 +5036,28 @@
         <v>46461</v>
       </c>
       <c r="C52" s="14" t="n">
-        <v>0.642361111111111</v>
+        <v>0.75</v>
       </c>
       <c r="D52" s="14" t="n">
-        <v>0.6875</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="E52" s="12" t="n">
         <f aca="false">ROUND((D52-C52)*1440,0)</f>
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="F52" s="12" t="s">
-        <v>130</v>
+        <v>57</v>
       </c>
       <c r="G52" s="12" t="s">
-        <v>128</v>
+        <v>55</v>
       </c>
       <c r="H52" s="12"/>
       <c r="I52" s="12"/>
       <c r="J52" s="12" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="K52" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5090,164 +5069,164 @@
         <v>46461</v>
       </c>
       <c r="C53" s="14" t="n">
-        <v>0.6875</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="D53" s="14" t="n">
-        <v>0.75</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="E53" s="12" t="n">
         <f aca="false">ROUND((D53-C53)*1440,0)</f>
         <v>90</v>
       </c>
       <c r="F53" s="12" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="G53" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="H53" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="I53" s="12" t="n">
-        <v>50</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="H53" s="12"/>
+      <c r="I53" s="12"/>
       <c r="J53" s="12" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="K53" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="12" t="n">
+      <c r="A54" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="B54" s="13" t="n">
+      <c r="B54" s="17" t="n">
         <f aca="false">Overview!$B$3+A54-1</f>
         <v>46461</v>
       </c>
-      <c r="C54" s="14" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="D54" s="14" t="n">
-        <v>0.770833333333333</v>
-      </c>
-      <c r="E54" s="12" t="n">
+      <c r="C54" s="18" t="n">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="D54" s="18" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="E54" s="16" t="n">
         <f aca="false">ROUND((D54-C54)*1440,0)</f>
+        <v>60</v>
+      </c>
+      <c r="F54" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G54" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="H54" s="16"/>
+      <c r="I54" s="16"/>
+      <c r="J54" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="K54" s="19" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B55" s="17" t="n">
+        <f aca="false">Overview!$B$3+A55-1</f>
+        <v>46462</v>
+      </c>
+      <c r="C55" s="18" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="D55" s="18" t="n">
+        <v>0.354166666666667</v>
+      </c>
+      <c r="E55" s="16" t="n">
+        <f aca="false">ROUND((D55-C55)*1440,0)</f>
+        <v>60</v>
+      </c>
+      <c r="F55" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G55" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="H55" s="16"/>
+      <c r="I55" s="16"/>
+      <c r="J55" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K55" s="19" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B56" s="13" t="n">
+        <f aca="false">Overview!$B$3+A56-1</f>
+        <v>46462</v>
+      </c>
+      <c r="C56" s="14" t="n">
+        <v>0.354166666666667</v>
+      </c>
+      <c r="D56" s="14" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="E56" s="12" t="n">
+        <f aca="false">ROUND((D56-C56)*1440,0)</f>
         <v>30</v>
       </c>
-      <c r="F54" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="G54" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="H54" s="12"/>
-      <c r="I54" s="12"/>
-      <c r="J54" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="K54" s="15" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="B55" s="13" t="n">
-        <f aca="false">Overview!$B$3+A55-1</f>
-        <v>46461</v>
-      </c>
-      <c r="C55" s="14" t="n">
-        <v>0.770833333333333</v>
-      </c>
-      <c r="D55" s="14" t="n">
-        <v>0.833333333333333</v>
-      </c>
-      <c r="E55" s="12" t="n">
-        <f aca="false">ROUND((D55-C55)*1440,0)</f>
-        <v>90</v>
-      </c>
-      <c r="F55" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="G55" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="H55" s="12"/>
-      <c r="I55" s="12"/>
-      <c r="J55" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="K55" s="15" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="B56" s="17" t="n">
-        <f aca="false">Overview!$B$3+A56-1</f>
-        <v>46461</v>
-      </c>
-      <c r="C56" s="18" t="n">
-        <v>0.833333333333333</v>
-      </c>
-      <c r="D56" s="18" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="E56" s="16" t="n">
-        <f aca="false">ROUND((D56-C56)*1440,0)</f>
-        <v>60</v>
-      </c>
-      <c r="F56" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="G56" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="H56" s="16"/>
-      <c r="I56" s="16"/>
-      <c r="J56" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="K56" s="19" t="s">
-        <v>53</v>
+      <c r="F56" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="G56" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="H56" s="12"/>
+      <c r="I56" s="12"/>
+      <c r="J56" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="K56" s="15" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="16" t="n">
+      <c r="A57" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="B57" s="17" t="n">
+      <c r="B57" s="13" t="n">
         <f aca="false">Overview!$B$3+A57-1</f>
         <v>46462</v>
       </c>
-      <c r="C57" s="18" t="n">
-        <v>0.3125</v>
-      </c>
-      <c r="D57" s="18" t="n">
-        <v>0.354166666666667</v>
-      </c>
-      <c r="E57" s="16" t="n">
+      <c r="C57" s="14" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D57" s="14" t="n">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="E57" s="12" t="n">
         <f aca="false">ROUND((D57-C57)*1440,0)</f>
-        <v>60</v>
-      </c>
-      <c r="F57" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="G57" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="H57" s="16"/>
-      <c r="I57" s="16"/>
-      <c r="J57" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="K57" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="F57" s="12" t="s">
         <v>53</v>
+      </c>
+      <c r="G57" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="H57" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="I57" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J57" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="K57" s="15" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5259,65 +5238,63 @@
         <v>46462</v>
       </c>
       <c r="C58" s="14" t="n">
-        <v>0.354166666666667</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="D58" s="14" t="n">
-        <v>0.375</v>
+        <v>0.458333333333333</v>
       </c>
       <c r="E58" s="12" t="n">
         <f aca="false">ROUND((D58-C58)*1440,0)</f>
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>58</v>
+        <v>132</v>
       </c>
       <c r="G58" s="12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H58" s="12"/>
       <c r="I58" s="12"/>
       <c r="J58" s="12" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="K58" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="12" t="n">
+      <c r="A59" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="B59" s="13" t="n">
+      <c r="B59" s="21" t="n">
         <f aca="false">Overview!$B$3+A59-1</f>
         <v>46462</v>
       </c>
-      <c r="C59" s="14" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="D59" s="14" t="n">
-        <v>0.388888888888889</v>
-      </c>
-      <c r="E59" s="12" t="n">
+      <c r="C59" s="22" t="n">
+        <v>0.458333333333333</v>
+      </c>
+      <c r="D59" s="22" t="n">
+        <v>0.493055555555556</v>
+      </c>
+      <c r="E59" s="20" t="n">
         <f aca="false">ROUND((D59-C59)*1440,0)</f>
-        <v>20</v>
-      </c>
-      <c r="F59" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="F59" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="G59" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="G59" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="H59" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="I59" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="J59" s="12" t="s">
+      <c r="H59" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="I59" s="20"/>
+      <c r="J59" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="K59" s="15" t="s">
-        <v>53</v>
+      <c r="K59" s="23" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5329,96 +5306,98 @@
         <v>46462</v>
       </c>
       <c r="C60" s="14" t="n">
-        <v>0.388888888888889</v>
+        <v>0.493055555555556</v>
       </c>
       <c r="D60" s="14" t="n">
-        <v>0.458333333333333</v>
+        <v>0.510416666666667</v>
       </c>
       <c r="E60" s="12" t="n">
         <f aca="false">ROUND((D60-C60)*1440,0)</f>
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="F60" s="12" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="G60" s="12" t="s">
-        <v>55</v>
+        <v>135</v>
       </c>
       <c r="H60" s="12"/>
       <c r="I60" s="12"/>
       <c r="J60" s="12" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K60" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="20" t="n">
+      <c r="A61" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="B61" s="21" t="n">
+      <c r="B61" s="13" t="n">
         <f aca="false">Overview!$B$3+A61-1</f>
         <v>46462</v>
       </c>
-      <c r="C61" s="22" t="n">
-        <v>0.458333333333333</v>
-      </c>
-      <c r="D61" s="22" t="n">
-        <v>0.493055555555556</v>
-      </c>
-      <c r="E61" s="20" t="n">
+      <c r="C61" s="14" t="n">
+        <v>0.510416666666667</v>
+      </c>
+      <c r="D61" s="14" t="n">
+        <v>0.541666666666667</v>
+      </c>
+      <c r="E61" s="12" t="n">
         <f aca="false">ROUND((D61-C61)*1440,0)</f>
-        <v>50</v>
-      </c>
-      <c r="F61" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="F61" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="G61" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="H61" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="I61" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="J61" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="G61" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="H61" s="20" t="s">
-        <v>140</v>
-      </c>
-      <c r="I61" s="20"/>
-      <c r="J61" s="20" t="s">
-        <v>141</v>
-      </c>
-      <c r="K61" s="23" t="s">
-        <v>53</v>
+      <c r="K61" s="15" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="12" t="n">
+      <c r="A62" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="B62" s="13" t="n">
+      <c r="B62" s="17" t="n">
         <f aca="false">Overview!$B$3+A62-1</f>
         <v>46462</v>
       </c>
-      <c r="C62" s="14" t="n">
-        <v>0.493055555555556</v>
-      </c>
-      <c r="D62" s="14" t="n">
-        <v>0.510416666666667</v>
-      </c>
-      <c r="E62" s="12" t="n">
+      <c r="C62" s="18" t="n">
+        <v>0.541666666666667</v>
+      </c>
+      <c r="D62" s="18" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="E62" s="16" t="n">
         <f aca="false">ROUND((D62-C62)*1440,0)</f>
-        <v>25</v>
-      </c>
-      <c r="F62" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="G62" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="F62" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="G62" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="H62" s="12"/>
-      <c r="I62" s="12"/>
-      <c r="J62" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="K62" s="15" t="s">
-        <v>53</v>
+      <c r="H62" s="16"/>
+      <c r="I62" s="16"/>
+      <c r="J62" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="K62" s="19" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5430,65 +5409,65 @@
         <v>46462</v>
       </c>
       <c r="C63" s="14" t="n">
-        <v>0.510416666666667</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="D63" s="14" t="n">
-        <v>0.541666666666667</v>
+        <v>0.59375</v>
       </c>
       <c r="E63" s="12" t="n">
         <f aca="false">ROUND((D63-C63)*1440,0)</f>
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="F63" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G63" s="12" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H63" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="I63" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J63" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="I63" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="J63" s="12" t="s">
-        <v>144</v>
-      </c>
       <c r="K63" s="15" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="16" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="B64" s="17" t="n">
+      <c r="B64" s="13" t="n">
         <f aca="false">Overview!$B$3+A64-1</f>
         <v>46462</v>
       </c>
-      <c r="C64" s="18" t="n">
-        <v>0.541666666666667</v>
-      </c>
-      <c r="D64" s="18" t="n">
-        <v>0.583333333333333</v>
-      </c>
-      <c r="E64" s="16" t="n">
+      <c r="C64" s="14" t="n">
+        <v>0.59375</v>
+      </c>
+      <c r="D64" s="14" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E64" s="12" t="n">
         <f aca="false">ROUND((D64-C64)*1440,0)</f>
-        <v>60</v>
-      </c>
-      <c r="F64" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="G64" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="H64" s="16"/>
-      <c r="I64" s="16"/>
-      <c r="J64" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="K64" s="19" t="s">
-        <v>53</v>
+        <v>45</v>
+      </c>
+      <c r="F64" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="G64" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="H64" s="12"/>
+      <c r="I64" s="12"/>
+      <c r="J64" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="K64" s="15" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5500,35 +5479,35 @@
         <v>46462</v>
       </c>
       <c r="C65" s="14" t="n">
-        <v>0.583333333333333</v>
+        <v>0.625</v>
       </c>
       <c r="D65" s="14" t="n">
-        <v>0.59375</v>
+        <v>0.635416666666667</v>
       </c>
       <c r="E65" s="12" t="n">
         <f aca="false">ROUND((D65-C65)*1440,0)</f>
         <v>15</v>
       </c>
       <c r="F65" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G65" s="12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H65" s="12" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J65" s="12" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="K65" s="15" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="12" t="n">
         <v>4</v>
       </c>
@@ -5537,28 +5516,28 @@
         <v>46462</v>
       </c>
       <c r="C66" s="14" t="n">
-        <v>0.59375</v>
+        <v>0.635416666666667</v>
       </c>
       <c r="D66" s="14" t="n">
-        <v>0.625</v>
+        <v>0.65625</v>
       </c>
       <c r="E66" s="12" t="n">
         <f aca="false">ROUND((D66-C66)*1440,0)</f>
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F66" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G66" s="12" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H66" s="12"/>
       <c r="I66" s="12"/>
       <c r="J66" s="12" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="K66" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5570,32 +5549,32 @@
         <v>46462</v>
       </c>
       <c r="C67" s="14" t="n">
-        <v>0.625</v>
+        <v>0.65625</v>
       </c>
       <c r="D67" s="14" t="n">
-        <v>0.635416666666667</v>
+        <v>0.670138888888889</v>
       </c>
       <c r="E67" s="12" t="n">
         <f aca="false">ROUND((D67-C67)*1440,0)</f>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F67" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G67" s="12" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H67" s="12" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="I67" s="12" t="n">
         <v>6</v>
       </c>
       <c r="J67" s="12" t="s">
-        <v>151</v>
+        <v>73</v>
       </c>
       <c r="K67" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5607,28 +5586,28 @@
         <v>46462</v>
       </c>
       <c r="C68" s="14" t="n">
-        <v>0.635416666666667</v>
+        <v>0.670138888888889</v>
       </c>
       <c r="D68" s="14" t="n">
-        <v>0.65625</v>
+        <v>0.697916666666667</v>
       </c>
       <c r="E68" s="12" t="n">
         <f aca="false">ROUND((D68-C68)*1440,0)</f>
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F68" s="12" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G68" s="12" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="H68" s="12"/>
       <c r="I68" s="12"/>
       <c r="J68" s="12" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="K68" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5640,65 +5619,63 @@
         <v>46462</v>
       </c>
       <c r="C69" s="14" t="n">
-        <v>0.65625</v>
+        <v>0.697916666666667</v>
       </c>
       <c r="D69" s="14" t="n">
-        <v>0.670138888888889</v>
+        <v>0.708333333333333</v>
       </c>
       <c r="E69" s="12" t="n">
         <f aca="false">ROUND((D69-C69)*1440,0)</f>
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F69" s="12" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="G69" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="H69" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="H69" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="I69" s="12" t="n">
-        <v>6</v>
-      </c>
+      <c r="I69" s="12"/>
       <c r="J69" s="12" t="s">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="K69" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="12" t="n">
+      <c r="A70" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="B70" s="13" t="n">
+      <c r="B70" s="21" t="n">
         <f aca="false">Overview!$B$3+A70-1</f>
         <v>46462</v>
       </c>
-      <c r="C70" s="14" t="n">
-        <v>0.670138888888889</v>
-      </c>
-      <c r="D70" s="14" t="n">
-        <v>0.697916666666667</v>
-      </c>
-      <c r="E70" s="12" t="n">
+      <c r="C70" s="22" t="n">
+        <v>0.708333333333333</v>
+      </c>
+      <c r="D70" s="22" t="n">
+        <v>0.770833333333333</v>
+      </c>
+      <c r="E70" s="20" t="n">
         <f aca="false">ROUND((D70-C70)*1440,0)</f>
-        <v>40</v>
-      </c>
-      <c r="F70" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="G70" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="H70" s="12"/>
-      <c r="I70" s="12"/>
-      <c r="J70" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="F70" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="G70" s="20" t="s">
         <v>153</v>
       </c>
-      <c r="K70" s="15" t="s">
-        <v>53</v>
+      <c r="H70" s="20"/>
+      <c r="I70" s="20"/>
+      <c r="J70" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="K70" s="23" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5710,298 +5687,300 @@
         <v>46462</v>
       </c>
       <c r="C71" s="14" t="n">
-        <v>0.697916666666667</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="D71" s="14" t="n">
-        <v>0.708333333333333</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="E71" s="12" t="n">
         <f aca="false">ROUND((D71-C71)*1440,0)</f>
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="F71" s="12" t="s">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="G71" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="H71" s="12" t="s">
-        <v>155</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="H71" s="12"/>
       <c r="I71" s="12"/>
       <c r="J71" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K71" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="20" t="n">
+      <c r="A72" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="B72" s="21" t="n">
+      <c r="B72" s="17" t="n">
         <f aca="false">Overview!$B$3+A72-1</f>
         <v>46462</v>
       </c>
-      <c r="C72" s="22" t="n">
-        <v>0.708333333333333</v>
-      </c>
-      <c r="D72" s="22" t="n">
-        <v>0.770833333333333</v>
-      </c>
-      <c r="E72" s="20" t="n">
+      <c r="C72" s="18" t="n">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="D72" s="18" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="E72" s="16" t="n">
         <f aca="false">ROUND((D72-C72)*1440,0)</f>
-        <v>90</v>
-      </c>
-      <c r="F72" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="F72" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G72" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="H72" s="16"/>
+      <c r="I72" s="16"/>
+      <c r="J72" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="K72" s="19" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B73" s="17" t="n">
+        <f aca="false">Overview!$B$3+A73-1</f>
+        <v>46463</v>
+      </c>
+      <c r="C73" s="18" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="D73" s="18" t="n">
+        <v>0.354166666666667</v>
+      </c>
+      <c r="E73" s="16" t="n">
+        <f aca="false">ROUND((D73-C73)*1440,0)</f>
+        <v>60</v>
+      </c>
+      <c r="F73" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G73" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="H73" s="16"/>
+      <c r="I73" s="16"/>
+      <c r="J73" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="K73" s="19" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="B74" s="13" t="n">
+        <f aca="false">Overview!$B$3+A74-1</f>
+        <v>46463</v>
+      </c>
+      <c r="C74" s="14" t="n">
+        <v>0.354166666666667</v>
+      </c>
+      <c r="D74" s="14" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="E74" s="12" t="n">
+        <f aca="false">ROUND((D74-C74)*1440,0)</f>
+        <v>30</v>
+      </c>
+      <c r="F74" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="G74" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="H74" s="12"/>
+      <c r="I74" s="12"/>
+      <c r="J74" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="G72" s="20" t="s">
-        <v>158</v>
-      </c>
-      <c r="H72" s="20"/>
-      <c r="I72" s="20"/>
-      <c r="J72" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="K72" s="23" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="B73" s="13" t="n">
-        <f aca="false">Overview!$B$3+A73-1</f>
-        <v>46462</v>
-      </c>
-      <c r="C73" s="14" t="n">
-        <v>0.770833333333333</v>
-      </c>
-      <c r="D73" s="14" t="n">
-        <v>0.833333333333333</v>
-      </c>
-      <c r="E73" s="12" t="n">
-        <f aca="false">ROUND((D73-C73)*1440,0)</f>
-        <v>90</v>
-      </c>
-      <c r="F73" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="G73" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="H73" s="12"/>
-      <c r="I73" s="12"/>
-      <c r="J73" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="K73" s="15" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="B74" s="17" t="n">
-        <f aca="false">Overview!$B$3+A74-1</f>
-        <v>46462</v>
-      </c>
-      <c r="C74" s="18" t="n">
-        <v>0.833333333333333</v>
-      </c>
-      <c r="D74" s="18" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="E74" s="16" t="n">
-        <f aca="false">ROUND((D74-C74)*1440,0)</f>
-        <v>60</v>
-      </c>
-      <c r="F74" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="G74" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="H74" s="16"/>
-      <c r="I74" s="16"/>
-      <c r="J74" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="K74" s="19" t="s">
-        <v>53</v>
+      <c r="K74" s="15" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="16" t="n">
+      <c r="A75" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="B75" s="17" t="n">
+      <c r="B75" s="13" t="n">
         <f aca="false">Overview!$B$3+A75-1</f>
         <v>46463</v>
       </c>
-      <c r="C75" s="18" t="n">
-        <v>0.3125</v>
-      </c>
-      <c r="D75" s="18" t="n">
-        <v>0.354166666666667</v>
-      </c>
-      <c r="E75" s="16" t="n">
+      <c r="C75" s="14" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D75" s="14" t="n">
+        <v>0.447916666666667</v>
+      </c>
+      <c r="E75" s="12" t="n">
         <f aca="false">ROUND((D75-C75)*1440,0)</f>
-        <v>60</v>
-      </c>
-      <c r="F75" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="G75" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="H75" s="16"/>
-      <c r="I75" s="16"/>
-      <c r="J75" s="16" t="s">
-        <v>161</v>
-      </c>
-      <c r="K75" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="F75" s="12" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="12" t="n">
+      <c r="G75" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="H75" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="I75" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="J75" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="K75" s="15" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="B76" s="13" t="n">
+      <c r="B76" s="21" t="n">
         <f aca="false">Overview!$B$3+A76-1</f>
         <v>46463</v>
       </c>
-      <c r="C76" s="14" t="n">
-        <v>0.354166666666667</v>
-      </c>
-      <c r="D76" s="14" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E76" s="12" t="n">
+      <c r="C76" s="22" t="n">
+        <v>0.447916666666667</v>
+      </c>
+      <c r="D76" s="22" t="n">
+        <v>0.572916666666667</v>
+      </c>
+      <c r="E76" s="20" t="n">
         <f aca="false">ROUND((D76-C76)*1440,0)</f>
-        <v>30</v>
-      </c>
-      <c r="F76" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="G76" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="H76" s="12"/>
-      <c r="I76" s="12"/>
-      <c r="J76" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="F76" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="G76" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="H76" s="20"/>
+      <c r="I76" s="20"/>
+      <c r="J76" s="20" t="s">
         <v>162</v>
       </c>
-      <c r="K76" s="15" t="s">
-        <v>53</v>
+      <c r="K76" s="23" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="12" t="n">
+      <c r="A77" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="B77" s="13" t="n">
+      <c r="B77" s="17" t="n">
         <f aca="false">Overview!$B$3+A77-1</f>
         <v>46463</v>
       </c>
-      <c r="C77" s="14" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="D77" s="14" t="n">
-        <v>0.447916666666667</v>
-      </c>
-      <c r="E77" s="12" t="n">
+      <c r="C77" s="18" t="n">
+        <v>0.572916666666667</v>
+      </c>
+      <c r="D77" s="18" t="n">
+        <v>0.604166666666667</v>
+      </c>
+      <c r="E77" s="16" t="n">
         <f aca="false">ROUND((D77-C77)*1440,0)</f>
-        <v>105</v>
-      </c>
-      <c r="F77" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="G77" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="H77" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="I77" s="12" t="n">
-        <v>50</v>
-      </c>
-      <c r="J77" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="F77" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="G77" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="K77" s="15" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="20" t="n">
+      <c r="H77" s="16"/>
+      <c r="I77" s="16"/>
+      <c r="J77" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="K77" s="19" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="B78" s="21" t="n">
+      <c r="B78" s="13" t="n">
         <f aca="false">Overview!$B$3+A78-1</f>
         <v>46463</v>
       </c>
-      <c r="C78" s="22" t="n">
-        <v>0.447916666666667</v>
-      </c>
-      <c r="D78" s="22" t="n">
-        <v>0.572916666666667</v>
-      </c>
-      <c r="E78" s="20" t="n">
+      <c r="C78" s="14" t="n">
+        <v>0.604166666666667</v>
+      </c>
+      <c r="D78" s="14" t="n">
+        <v>0.614583333333333</v>
+      </c>
+      <c r="E78" s="12" t="n">
         <f aca="false">ROUND((D78-C78)*1440,0)</f>
-        <v>180</v>
-      </c>
-      <c r="F78" s="20" t="s">
-        <v>164</v>
-      </c>
-      <c r="G78" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F78" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="G78" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="H78" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="H78" s="20"/>
-      <c r="I78" s="20"/>
-      <c r="J78" s="20" t="s">
+      <c r="I78" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J78" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="K78" s="23" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="16" t="n">
+      <c r="K78" s="15" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="B79" s="17" t="n">
+      <c r="B79" s="13" t="n">
         <f aca="false">Overview!$B$3+A79-1</f>
         <v>46463</v>
       </c>
-      <c r="C79" s="18" t="n">
-        <v>0.572916666666667</v>
-      </c>
-      <c r="D79" s="18" t="n">
-        <v>0.604166666666667</v>
-      </c>
-      <c r="E79" s="16" t="n">
+      <c r="C79" s="14" t="n">
+        <v>0.614583333333333</v>
+      </c>
+      <c r="D79" s="14" t="n">
+        <v>0.645833333333333</v>
+      </c>
+      <c r="E79" s="12" t="n">
         <f aca="false">ROUND((D79-C79)*1440,0)</f>
         <v>45</v>
       </c>
-      <c r="F79" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="G79" s="16" t="s">
+      <c r="F79" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="G79" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="H79" s="16"/>
-      <c r="I79" s="16"/>
-      <c r="J79" s="16" t="s">
+      <c r="H79" s="12"/>
+      <c r="I79" s="12"/>
+      <c r="J79" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="K79" s="19" t="s">
-        <v>53</v>
+      <c r="K79" s="15" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6013,28 +5992,28 @@
         <v>46463</v>
       </c>
       <c r="C80" s="14" t="n">
-        <v>0.604166666666667</v>
+        <v>0.645833333333333</v>
       </c>
       <c r="D80" s="14" t="n">
-        <v>0.625</v>
+        <v>0.6875</v>
       </c>
       <c r="E80" s="12" t="n">
         <f aca="false">ROUND((D80-C80)*1440,0)</f>
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F80" s="12" t="s">
-        <v>58</v>
+        <v>169</v>
       </c>
       <c r="G80" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H80" s="12"/>
       <c r="I80" s="12"/>
       <c r="J80" s="12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K80" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6046,35 +6025,35 @@
         <v>46463</v>
       </c>
       <c r="C81" s="14" t="n">
-        <v>0.625</v>
+        <v>0.6875</v>
       </c>
       <c r="D81" s="14" t="n">
-        <v>0.635416666666667</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="E81" s="12" t="n">
         <f aca="false">ROUND((D81-C81)*1440,0)</f>
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="F81" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G81" s="12" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="H81" s="12" t="s">
-        <v>171</v>
+        <v>138</v>
       </c>
       <c r="I81" s="12" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="J81" s="12" t="s">
         <v>172</v>
       </c>
       <c r="K81" s="15" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="12" t="n">
         <v>5</v>
       </c>
@@ -6083,160 +6062,164 @@
         <v>46463</v>
       </c>
       <c r="C82" s="14" t="n">
-        <v>0.635416666666667</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="D82" s="14" t="n">
-        <v>0.666666666666667</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="E82" s="12" t="n">
         <f aca="false">ROUND((D82-C82)*1440,0)</f>
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="F82" s="12" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G82" s="12" t="s">
-        <v>173</v>
+        <v>138</v>
       </c>
       <c r="H82" s="12"/>
       <c r="I82" s="12"/>
       <c r="J82" s="12" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K82" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="12" t="n">
+      <c r="A83" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="B83" s="13" t="n">
+      <c r="B83" s="17" t="n">
         <f aca="false">Overview!$B$3+A83-1</f>
         <v>46463</v>
       </c>
-      <c r="C83" s="14" t="n">
-        <v>0.666666666666667</v>
-      </c>
-      <c r="D83" s="14" t="n">
-        <v>0.729166666666667</v>
-      </c>
-      <c r="E83" s="12" t="n">
+      <c r="C83" s="18" t="n">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="D83" s="18" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="E83" s="16" t="n">
         <f aca="false">ROUND((D83-C83)*1440,0)</f>
-        <v>90</v>
-      </c>
-      <c r="F83" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="F83" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G83" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="H83" s="16"/>
+      <c r="I83" s="16"/>
+      <c r="J83" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="K83" s="19" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="B84" s="17" t="n">
+        <f aca="false">Overview!$B$3+A84-1</f>
+        <v>46464</v>
+      </c>
+      <c r="C84" s="18" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="D84" s="18" t="n">
+        <v>0.354166666666667</v>
+      </c>
+      <c r="E84" s="16" t="n">
+        <f aca="false">ROUND((D84-C84)*1440,0)</f>
+        <v>60</v>
+      </c>
+      <c r="F84" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G84" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="H84" s="16"/>
+      <c r="I84" s="16"/>
+      <c r="J84" s="16" t="s">
         <v>175</v>
       </c>
-      <c r="G83" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="H83" s="12"/>
-      <c r="I83" s="12"/>
-      <c r="J83" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="K83" s="15" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="B84" s="13" t="n">
-        <f aca="false">Overview!$B$3+A84-1</f>
-        <v>46463</v>
-      </c>
-      <c r="C84" s="14" t="n">
-        <v>0.729166666666667</v>
-      </c>
-      <c r="D84" s="14" t="n">
-        <v>0.833333333333333</v>
-      </c>
-      <c r="E84" s="12" t="n">
-        <f aca="false">ROUND((D84-C84)*1440,0)</f>
-        <v>150</v>
-      </c>
-      <c r="F84" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="G84" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="H84" s="12"/>
-      <c r="I84" s="12"/>
-      <c r="J84" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="K84" s="15" t="s">
-        <v>53</v>
+      <c r="K84" s="19" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="B85" s="17" t="n">
+      <c r="A85" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B85" s="13" t="n">
         <f aca="false">Overview!$B$3+A85-1</f>
-        <v>46463</v>
-      </c>
-      <c r="C85" s="18" t="n">
-        <v>0.833333333333333</v>
-      </c>
-      <c r="D85" s="18" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="E85" s="16" t="n">
+        <v>46464</v>
+      </c>
+      <c r="C85" s="14" t="n">
+        <v>0.354166666666667</v>
+      </c>
+      <c r="D85" s="14" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="E85" s="12" t="n">
         <f aca="false">ROUND((D85-C85)*1440,0)</f>
-        <v>60</v>
-      </c>
-      <c r="F85" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="G85" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="H85" s="16"/>
-      <c r="I85" s="16"/>
-      <c r="J85" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="K85" s="19" t="s">
-        <v>53</v>
+        <v>30</v>
+      </c>
+      <c r="F85" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="G85" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="H85" s="12"/>
+      <c r="I85" s="12"/>
+      <c r="J85" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="K85" s="15" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="16" t="n">
+      <c r="A86" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B86" s="17" t="n">
+      <c r="B86" s="13" t="n">
         <f aca="false">Overview!$B$3+A86-1</f>
         <v>46464</v>
       </c>
-      <c r="C86" s="18" t="n">
-        <v>0.3125</v>
-      </c>
-      <c r="D86" s="18" t="n">
-        <v>0.354166666666667</v>
-      </c>
-      <c r="E86" s="16" t="n">
+      <c r="C86" s="14" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D86" s="14" t="n">
+        <v>0.40625</v>
+      </c>
+      <c r="E86" s="12" t="n">
         <f aca="false">ROUND((D86-C86)*1440,0)</f>
-        <v>60</v>
-      </c>
-      <c r="F86" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="G86" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="H86" s="16"/>
-      <c r="I86" s="16"/>
-      <c r="J86" s="16" t="s">
-        <v>181</v>
-      </c>
-      <c r="K86" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F86" s="12" t="s">
         <v>53</v>
+      </c>
+      <c r="G86" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="H86" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="I86" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="J86" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="K86" s="15" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6248,28 +6231,28 @@
         <v>46464</v>
       </c>
       <c r="C87" s="14" t="n">
-        <v>0.354166666666667</v>
+        <v>0.40625</v>
       </c>
       <c r="D87" s="14" t="n">
-        <v>0.375</v>
+        <v>0.4375</v>
       </c>
       <c r="E87" s="12" t="n">
         <f aca="false">ROUND((D87-C87)*1440,0)</f>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="F87" s="12" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G87" s="12" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="H87" s="12"/>
       <c r="I87" s="12"/>
       <c r="J87" s="12" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="K87" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6281,170 +6264,170 @@
         <v>46464</v>
       </c>
       <c r="C88" s="14" t="n">
-        <v>0.375</v>
+        <v>0.4375</v>
       </c>
       <c r="D88" s="14" t="n">
-        <v>0.458333333333333</v>
+        <v>0.520833333333333</v>
       </c>
       <c r="E88" s="12" t="n">
         <f aca="false">ROUND((D88-C88)*1440,0)</f>
         <v>120</v>
       </c>
       <c r="F88" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G88" s="12" t="s">
-        <v>24</v>
+        <v>180</v>
       </c>
       <c r="H88" s="12" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="J88" s="12" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="K88" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="12" t="n">
+      <c r="A89" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="B89" s="13" t="n">
+      <c r="B89" s="17" t="n">
         <f aca="false">Overview!$B$3+A89-1</f>
         <v>46464</v>
       </c>
-      <c r="C89" s="14" t="n">
-        <v>0.458333333333333</v>
-      </c>
-      <c r="D89" s="14" t="n">
-        <v>0.489583333333333</v>
-      </c>
-      <c r="E89" s="12" t="n">
+      <c r="C89" s="18" t="n">
+        <v>0.520833333333333</v>
+      </c>
+      <c r="D89" s="18" t="n">
+        <v>0.552083333333333</v>
+      </c>
+      <c r="E89" s="16" t="n">
         <f aca="false">ROUND((D89-C89)*1440,0)</f>
         <v>45</v>
       </c>
-      <c r="F89" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="G89" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="H89" s="12"/>
-      <c r="I89" s="12"/>
-      <c r="J89" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="K89" s="15" t="s">
-        <v>53</v>
+      <c r="F89" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="G89" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="H89" s="16"/>
+      <c r="I89" s="16"/>
+      <c r="J89" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="K89" s="19" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="12" t="n">
+      <c r="A90" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="B90" s="13" t="n">
+      <c r="B90" s="21" t="n">
         <f aca="false">Overview!$B$3+A90-1</f>
         <v>46464</v>
       </c>
-      <c r="C90" s="14" t="n">
-        <v>0.489583333333333</v>
-      </c>
-      <c r="D90" s="14" t="n">
-        <v>0.572916666666667</v>
-      </c>
-      <c r="E90" s="12" t="n">
+      <c r="C90" s="22" t="n">
+        <v>0.552083333333333</v>
+      </c>
+      <c r="D90" s="22" t="n">
+        <v>0.614583333333333</v>
+      </c>
+      <c r="E90" s="20" t="n">
         <f aca="false">ROUND((D90-C90)*1440,0)</f>
-        <v>120</v>
-      </c>
-      <c r="F90" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="G90" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="H90" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="I90" s="12" t="n">
-        <v>60</v>
-      </c>
-      <c r="J90" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="K90" s="15" t="s">
-        <v>53</v>
+        <v>90</v>
+      </c>
+      <c r="F90" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="G90" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="H90" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="I90" s="20"/>
+      <c r="J90" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="K90" s="23" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="16" t="n">
+      <c r="A91" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B91" s="17" t="n">
+      <c r="B91" s="13" t="n">
         <f aca="false">Overview!$B$3+A91-1</f>
         <v>46464</v>
       </c>
-      <c r="C91" s="18" t="n">
-        <v>0.572916666666667</v>
-      </c>
-      <c r="D91" s="18" t="n">
-        <v>0.604166666666667</v>
-      </c>
-      <c r="E91" s="16" t="n">
+      <c r="C91" s="14" t="n">
+        <v>0.614583333333333</v>
+      </c>
+      <c r="D91" s="14" t="n">
+        <v>0.645833333333333</v>
+      </c>
+      <c r="E91" s="12" t="n">
         <f aca="false">ROUND((D91-C91)*1440,0)</f>
         <v>45</v>
       </c>
-      <c r="F91" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="G91" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="H91" s="16"/>
-      <c r="I91" s="16"/>
-      <c r="J91" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="K91" s="19" t="s">
-        <v>53</v>
+      <c r="F91" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="G91" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="H91" s="12"/>
+      <c r="I91" s="12"/>
+      <c r="J91" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="K91" s="15" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="20" t="n">
+      <c r="A92" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B92" s="21" t="n">
+      <c r="B92" s="13" t="n">
         <f aca="false">Overview!$B$3+A92-1</f>
         <v>46464</v>
       </c>
-      <c r="C92" s="22" t="n">
-        <v>0.604166666666667</v>
-      </c>
-      <c r="D92" s="22" t="n">
-        <v>0.65625</v>
-      </c>
-      <c r="E92" s="20" t="n">
+      <c r="C92" s="14" t="n">
+        <v>0.645833333333333</v>
+      </c>
+      <c r="D92" s="14" t="n">
+        <v>0.770833333333333</v>
+      </c>
+      <c r="E92" s="12" t="n">
         <f aca="false">ROUND((D92-C92)*1440,0)</f>
-        <v>75</v>
-      </c>
-      <c r="F92" s="20" t="s">
-        <v>191</v>
-      </c>
-      <c r="G92" s="20" t="s">
-        <v>188</v>
-      </c>
-      <c r="H92" s="20" t="s">
-        <v>192</v>
-      </c>
-      <c r="I92" s="20"/>
-      <c r="J92" s="20" t="s">
-        <v>193</v>
-      </c>
-      <c r="K92" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="F92" s="12" t="s">
         <v>53</v>
+      </c>
+      <c r="G92" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="H92" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="I92" s="12" t="n">
+        <v>82</v>
+      </c>
+      <c r="J92" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="K92" s="15" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6456,164 +6439,164 @@
         <v>46464</v>
       </c>
       <c r="C93" s="14" t="n">
-        <v>0.65625</v>
+        <v>0.770833333333333</v>
       </c>
       <c r="D93" s="14" t="n">
-        <v>0.677083333333333</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="E93" s="12" t="n">
         <f aca="false">ROUND((D93-C93)*1440,0)</f>
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="F93" s="12" t="s">
-        <v>175</v>
+        <v>74</v>
       </c>
       <c r="G93" s="12" t="s">
-        <v>194</v>
+        <v>138</v>
       </c>
       <c r="H93" s="12"/>
       <c r="I93" s="12"/>
       <c r="J93" s="12" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="K93" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="12" t="n">
+      <c r="A94" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="B94" s="13" t="n">
+      <c r="B94" s="17" t="n">
         <f aca="false">Overview!$B$3+A94-1</f>
         <v>46464</v>
       </c>
-      <c r="C94" s="14" t="n">
-        <v>0.677083333333333</v>
-      </c>
-      <c r="D94" s="14" t="n">
-        <v>0.802083333333333</v>
-      </c>
-      <c r="E94" s="12" t="n">
+      <c r="C94" s="18" t="n">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="D94" s="18" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="E94" s="16" t="n">
         <f aca="false">ROUND((D94-C94)*1440,0)</f>
-        <v>180</v>
-      </c>
-      <c r="F94" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="G94" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="H94" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="I94" s="12" t="n">
-        <v>82</v>
-      </c>
-      <c r="J94" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="K94" s="15" t="s">
-        <v>53</v>
+        <v>60</v>
+      </c>
+      <c r="F94" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G94" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="H94" s="16"/>
+      <c r="I94" s="16"/>
+      <c r="J94" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="K94" s="19" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="B95" s="13" t="n">
+      <c r="A95" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="B95" s="17" t="n">
         <f aca="false">Overview!$B$3+A95-1</f>
-        <v>46464</v>
-      </c>
-      <c r="C95" s="14" t="n">
-        <v>0.802083333333333</v>
-      </c>
-      <c r="D95" s="14" t="n">
-        <v>0.833333333333333</v>
-      </c>
-      <c r="E95" s="12" t="n">
+        <v>46465</v>
+      </c>
+      <c r="C95" s="18" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="D95" s="18" t="n">
+        <v>0.354166666666667</v>
+      </c>
+      <c r="E95" s="16" t="n">
         <f aca="false">ROUND((D95-C95)*1440,0)</f>
-        <v>45</v>
-      </c>
-      <c r="F95" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="G95" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="H95" s="12"/>
-      <c r="I95" s="12"/>
-      <c r="J95" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="K95" s="15" t="s">
-        <v>53</v>
+        <v>60</v>
+      </c>
+      <c r="F95" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G95" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="H95" s="16"/>
+      <c r="I95" s="16"/>
+      <c r="J95" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K95" s="19" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="B96" s="17" t="n">
+      <c r="A96" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B96" s="13" t="n">
         <f aca="false">Overview!$B$3+A96-1</f>
-        <v>46464</v>
-      </c>
-      <c r="C96" s="18" t="n">
-        <v>0.833333333333333</v>
-      </c>
-      <c r="D96" s="18" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="E96" s="16" t="n">
+        <v>46465</v>
+      </c>
+      <c r="C96" s="14" t="n">
+        <v>0.354166666666667</v>
+      </c>
+      <c r="D96" s="14" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="E96" s="12" t="n">
         <f aca="false">ROUND((D96-C96)*1440,0)</f>
-        <v>60</v>
-      </c>
-      <c r="F96" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="G96" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="H96" s="16"/>
-      <c r="I96" s="16"/>
-      <c r="J96" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="K96" s="19" t="s">
-        <v>53</v>
+        <v>30</v>
+      </c>
+      <c r="F96" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="G96" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="H96" s="12"/>
+      <c r="I96" s="12"/>
+      <c r="J96" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="K96" s="15" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="16" t="n">
+      <c r="A97" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="B97" s="17" t="n">
+      <c r="B97" s="13" t="n">
         <f aca="false">Overview!$B$3+A97-1</f>
         <v>46465</v>
       </c>
-      <c r="C97" s="18" t="n">
-        <v>0.3125</v>
-      </c>
-      <c r="D97" s="18" t="n">
-        <v>0.354166666666667</v>
-      </c>
-      <c r="E97" s="16" t="n">
+      <c r="C97" s="14" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D97" s="14" t="n">
+        <v>0.416666666666667</v>
+      </c>
+      <c r="E97" s="12" t="n">
         <f aca="false">ROUND((D97-C97)*1440,0)</f>
         <v>60</v>
       </c>
-      <c r="F97" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="G97" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="H97" s="16"/>
-      <c r="I97" s="16"/>
-      <c r="J97" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="K97" s="19" t="s">
+      <c r="F97" s="12" t="s">
         <v>53</v>
+      </c>
+      <c r="G97" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="H97" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="I97" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="J97" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="K97" s="15" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6625,28 +6608,28 @@
         <v>46465</v>
       </c>
       <c r="C98" s="14" t="n">
-        <v>0.354166666666667</v>
+        <v>0.416666666666667</v>
       </c>
       <c r="D98" s="14" t="n">
-        <v>0.375</v>
+        <v>0.447916666666667</v>
       </c>
       <c r="E98" s="12" t="n">
         <f aca="false">ROUND((D98-C98)*1440,0)</f>
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="F98" s="12" t="s">
-        <v>58</v>
+        <v>169</v>
       </c>
       <c r="G98" s="12" t="s">
-        <v>143</v>
+        <v>191</v>
       </c>
       <c r="H98" s="12"/>
       <c r="I98" s="12"/>
       <c r="J98" s="12" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="K98" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6658,32 +6641,32 @@
         <v>46465</v>
       </c>
       <c r="C99" s="14" t="n">
-        <v>0.375</v>
+        <v>0.447916666666667</v>
       </c>
       <c r="D99" s="14" t="n">
-        <v>0.416666666666667</v>
+        <v>0.489583333333333</v>
       </c>
       <c r="E99" s="12" t="n">
         <f aca="false">ROUND((D99-C99)*1440,0)</f>
         <v>60</v>
       </c>
       <c r="F99" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G99" s="12" t="s">
-        <v>143</v>
+        <v>194</v>
       </c>
       <c r="H99" s="12" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I99" s="12" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J99" s="12" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="K99" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6695,28 +6678,28 @@
         <v>46465</v>
       </c>
       <c r="C100" s="14" t="n">
-        <v>0.416666666666667</v>
+        <v>0.489583333333333</v>
       </c>
       <c r="D100" s="14" t="n">
-        <v>0.447916666666667</v>
+        <v>0.520833333333333</v>
       </c>
       <c r="E100" s="12" t="n">
         <f aca="false">ROUND((D100-C100)*1440,0)</f>
         <v>45</v>
       </c>
       <c r="F100" s="12" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="G100" s="12" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="H100" s="12"/>
       <c r="I100" s="12"/>
       <c r="J100" s="12" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="K100" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6728,65 +6711,65 @@
         <v>46465</v>
       </c>
       <c r="C101" s="14" t="n">
-        <v>0.447916666666667</v>
+        <v>0.520833333333333</v>
       </c>
       <c r="D101" s="14" t="n">
-        <v>0.489583333333333</v>
+        <v>0.572916666666667</v>
       </c>
       <c r="E101" s="12" t="n">
         <f aca="false">ROUND((D101-C101)*1440,0)</f>
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="F101" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G101" s="12" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H101" s="12" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I101" s="12" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="J101" s="12" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K101" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="12" t="n">
+      <c r="A102" s="16" t="n">
         <v>7</v>
       </c>
-      <c r="B102" s="13" t="n">
+      <c r="B102" s="17" t="n">
         <f aca="false">Overview!$B$3+A102-1</f>
         <v>46465</v>
       </c>
-      <c r="C102" s="14" t="n">
-        <v>0.489583333333333</v>
-      </c>
-      <c r="D102" s="14" t="n">
-        <v>0.520833333333333</v>
-      </c>
-      <c r="E102" s="12" t="n">
+      <c r="C102" s="18" t="n">
+        <v>0.572916666666667</v>
+      </c>
+      <c r="D102" s="18" t="n">
+        <v>0.604166666666667</v>
+      </c>
+      <c r="E102" s="16" t="n">
         <f aca="false">ROUND((D102-C102)*1440,0)</f>
         <v>45</v>
       </c>
-      <c r="F102" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="G102" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="H102" s="12"/>
-      <c r="I102" s="12"/>
-      <c r="J102" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="K102" s="15" t="s">
-        <v>53</v>
+      <c r="F102" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="G102" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="H102" s="16"/>
+      <c r="I102" s="16"/>
+      <c r="J102" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="K102" s="19" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6798,68 +6781,68 @@
         <v>46465</v>
       </c>
       <c r="C103" s="14" t="n">
-        <v>0.520833333333333</v>
+        <v>0.604166666666667</v>
       </c>
       <c r="D103" s="14" t="n">
-        <v>0.572916666666667</v>
+        <v>0.645833333333333</v>
       </c>
       <c r="E103" s="12" t="n">
         <f aca="false">ROUND((D103-C103)*1440,0)</f>
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="F103" s="12" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="G103" s="12" t="s">
-        <v>205</v>
-      </c>
-      <c r="H103" s="12" t="s">
-        <v>206</v>
-      </c>
-      <c r="I103" s="12" t="n">
-        <v>40</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="H103" s="12"/>
+      <c r="I103" s="12"/>
       <c r="J103" s="12" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="K103" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="16" t="n">
+      <c r="A104" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="B104" s="17" t="n">
+      <c r="B104" s="13" t="n">
         <f aca="false">Overview!$B$3+A104-1</f>
         <v>46465</v>
       </c>
-      <c r="C104" s="18" t="n">
-        <v>0.572916666666667</v>
-      </c>
-      <c r="D104" s="18" t="n">
-        <v>0.614583333333333</v>
-      </c>
-      <c r="E104" s="16" t="n">
+      <c r="C104" s="14" t="n">
+        <v>0.645833333333333</v>
+      </c>
+      <c r="D104" s="14" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="E104" s="12" t="n">
         <f aca="false">ROUND((D104-C104)*1440,0)</f>
-        <v>60</v>
-      </c>
-      <c r="F104" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="G104" s="16" t="s">
-        <v>208</v>
-      </c>
-      <c r="H104" s="16"/>
-      <c r="I104" s="16"/>
-      <c r="J104" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="K104" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="F104" s="12" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G104" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="H104" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="I104" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="J104" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="K104" s="15" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="12" t="n">
         <v>7</v>
       </c>
@@ -6868,28 +6851,28 @@
         <v>46465</v>
       </c>
       <c r="C105" s="14" t="n">
-        <v>0.614583333333333</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="D105" s="14" t="n">
-        <v>0.645833333333333</v>
+        <v>0.791666666666667</v>
       </c>
       <c r="E105" s="12" t="n">
         <f aca="false">ROUND((D105-C105)*1440,0)</f>
-        <v>45</v>
+        <v>180</v>
       </c>
       <c r="F105" s="12" t="s">
-        <v>175</v>
+        <v>70</v>
       </c>
       <c r="G105" s="12" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H105" s="12"/>
       <c r="I105" s="12"/>
       <c r="J105" s="12" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="K105" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6901,32 +6884,32 @@
         <v>46465</v>
       </c>
       <c r="C106" s="14" t="n">
-        <v>0.645833333333333</v>
+        <v>0.791666666666667</v>
       </c>
       <c r="D106" s="14" t="n">
-        <v>0.760416666666667</v>
+        <v>0.802083333333333</v>
       </c>
       <c r="E106" s="12" t="n">
         <f aca="false">ROUND((D106-C106)*1440,0)</f>
-        <v>165</v>
+        <v>15</v>
       </c>
       <c r="F106" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G106" s="12" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H106" s="12" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I106" s="12" t="n">
-        <v>95</v>
+        <v>5</v>
       </c>
       <c r="J106" s="12" t="s">
-        <v>196</v>
+        <v>73</v>
       </c>
       <c r="K106" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6938,28 +6921,28 @@
         <v>46465</v>
       </c>
       <c r="C107" s="14" t="n">
-        <v>0.760416666666667</v>
+        <v>0.802083333333333</v>
       </c>
       <c r="D107" s="14" t="n">
         <v>0.833333333333333</v>
       </c>
       <c r="E107" s="12" t="n">
         <f aca="false">ROUND((D107-C107)*1440,0)</f>
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="F107" s="12" t="s">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="G107" s="12" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="H107" s="12"/>
       <c r="I107" s="12"/>
       <c r="J107" s="12" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K107" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6981,18 +6964,18 @@
         <v>60</v>
       </c>
       <c r="F108" s="16" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G108" s="16" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H108" s="16"/>
       <c r="I108" s="16"/>
       <c r="J108" s="16" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K108" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7014,18 +6997,18 @@
         <v>60</v>
       </c>
       <c r="F109" s="16" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G109" s="16" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H109" s="16"/>
       <c r="I109" s="16"/>
       <c r="J109" s="16" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K109" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7047,18 +7030,18 @@
         <v>30</v>
       </c>
       <c r="F110" s="12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G110" s="12" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="H110" s="12"/>
       <c r="I110" s="12"/>
       <c r="J110" s="12" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="K110" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7073,29 +7056,29 @@
         <v>0.375</v>
       </c>
       <c r="D111" s="14" t="n">
-        <v>0.395833333333333</v>
+        <v>0.385416666666667</v>
       </c>
       <c r="E111" s="12" t="n">
         <f aca="false">ROUND((D111-C111)*1440,0)</f>
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F111" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G111" s="12" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="H111" s="12" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="I111" s="12" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="J111" s="12" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="K111" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7107,28 +7090,28 @@
         <v>46466</v>
       </c>
       <c r="C112" s="14" t="n">
-        <v>0.395833333333333</v>
+        <v>0.385416666666667</v>
       </c>
       <c r="D112" s="14" t="n">
-        <v>0.4375</v>
+        <v>0.447916666666667</v>
       </c>
       <c r="E112" s="12" t="n">
         <f aca="false">ROUND((D112-C112)*1440,0)</f>
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F112" s="12" t="s">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="G112" s="12" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="H112" s="12"/>
       <c r="I112" s="12"/>
       <c r="J112" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K112" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7140,32 +7123,32 @@
         <v>46466</v>
       </c>
       <c r="C113" s="14" t="n">
-        <v>0.4375</v>
+        <v>0.447916666666667</v>
       </c>
       <c r="D113" s="14" t="n">
         <v>0.46875</v>
       </c>
       <c r="E113" s="12" t="n">
         <f aca="false">ROUND((D113-C113)*1440,0)</f>
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F113" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G113" s="12" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H113" s="12" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I113" s="12" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="J113" s="12" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K113" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7187,18 +7170,18 @@
         <v>60</v>
       </c>
       <c r="F114" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G114" s="16" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H114" s="16"/>
       <c r="I114" s="16"/>
       <c r="J114" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K114" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7220,22 +7203,22 @@
         <v>15</v>
       </c>
       <c r="F115" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G115" s="12" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="H115" s="12" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="I115" s="12" t="n">
         <v>5</v>
       </c>
       <c r="J115" s="12" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="K115" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7257,23 +7240,23 @@
         <v>30</v>
       </c>
       <c r="F116" s="12" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G116" s="12" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="H116" s="12"/>
       <c r="I116" s="12"/>
       <c r="J116" s="12" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="K116" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="5" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -7419,7 +7402,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7427,13 +7410,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="D3" s="11" t="s">
         <v>224</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7441,13 +7424,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="D4" s="12" t="s">
         <v>60</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7455,13 +7438,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7469,13 +7452,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7483,13 +7466,13 @@
         <v>2</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7497,13 +7480,13 @@
         <v>2</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7511,13 +7494,13 @@
         <v>3</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7525,13 +7508,13 @@
         <v>3</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7539,13 +7522,13 @@
         <v>3</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7553,13 +7536,13 @@
         <v>4</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7567,13 +7550,13 @@
         <v>4</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7581,13 +7564,13 @@
         <v>4</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7595,13 +7578,13 @@
         <v>5</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7609,13 +7592,13 @@
         <v>5</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7623,13 +7606,13 @@
         <v>5</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7637,13 +7620,13 @@
         <v>6</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7651,13 +7634,13 @@
         <v>6</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7665,13 +7648,13 @@
         <v>6</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7679,13 +7662,13 @@
         <v>7</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7693,13 +7676,13 @@
         <v>7</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7707,13 +7690,13 @@
         <v>7</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7721,13 +7704,13 @@
         <v>8</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7735,18 +7718,18 @@
         <v>8</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -7775,123 +7758,123 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>239</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>242</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>243</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>245</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>246</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="C4" s="12" t="s">
         <v>248</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="C5" s="12" t="s">
         <v>251</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>252</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="C6" s="12" t="s">
         <v>254</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="C7" s="12" t="s">
         <v>257</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>258</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C8" s="12" t="s">
         <v>260</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>261</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>263</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>264</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="C10" s="12" t="s">
         <v>266</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>267</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="C11" s="12" t="s">
         <v>269</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>270</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -7921,198 +7904,198 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="D1" s="11" t="s">
         <v>273</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>274</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>276</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="D2" s="12" t="s">
         <v>277</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>278</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>280</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="D3" s="12" t="s">
         <v>281</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>282</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="C4" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="D4" s="12" t="s">
         <v>285</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>286</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="C5" s="12" t="s">
         <v>288</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="D5" s="12" t="s">
         <v>289</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>290</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="C6" s="12" t="s">
         <v>292</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="D6" s="12" t="s">
         <v>293</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>294</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="C7" s="12" t="s">
         <v>296</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="D7" s="12" t="s">
         <v>297</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>298</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>299</v>
+      </c>
+      <c r="C8" s="12" t="s">
         <v>300</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="D8" s="12" t="s">
         <v>301</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>302</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="D9" s="12" t="s">
         <v>305</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>306</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="C10" s="12" t="s">
         <v>308</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="D10" s="12" t="s">
         <v>309</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>310</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="C11" s="12" t="s">
         <v>312</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="D11" s="12" t="s">
         <v>313</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>314</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="C12" s="12" t="s">
         <v>316</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="D12" s="12" t="s">
         <v>317</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>318</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="C13" s="12" t="s">
         <v>320</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="D13" s="12" t="s">
         <v>321</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>322</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="C14" s="12" t="s">
         <v>324</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="D14" s="12" t="s">
         <v>325</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>326</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>327</v>
       </c>
     </row>
   </sheetData>
@@ -8140,207 +8123,207 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="B5" s="12" t="s">
         <v>331</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="B14" s="12" t="s">
         <v>341</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="B21" s="12" t="s">
         <v>349</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="B26" s="12" t="s">
         <v>355</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -8371,246 +8354,246 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
+        <v>358</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="C3" s="11" t="s">
         <v>360</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="D3" s="11" t="s">
         <v>361</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="E3" s="11" t="s">
         <v>362</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>363</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="C4" s="12" t="s">
         <v>365</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="D4" s="12" t="s">
         <v>366</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>367</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>368</v>
       </c>
       <c r="E4" s="24"/>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="D5" s="12" t="s">
         <v>369</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>370</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>367</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>371</v>
       </c>
       <c r="E5" s="24"/>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="D6" s="12" t="s">
         <v>372</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>373</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>367</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>374</v>
       </c>
       <c r="E6" s="24"/>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="C7" s="12" t="s">
         <v>375</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="D7" s="12" t="s">
         <v>376</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>377</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>378</v>
       </c>
       <c r="E7" s="24"/>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>378</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="D8" s="12" t="s">
         <v>379</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>367</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>381</v>
       </c>
       <c r="E8" s="24"/>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>381</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>382</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="D9" s="12" t="s">
         <v>383</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>384</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>385</v>
       </c>
       <c r="E9" s="24"/>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>384</v>
+      </c>
+      <c r="C10" s="12" t="s">
         <v>382</v>
       </c>
-      <c r="B10" s="12" t="s">
-        <v>386</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>384</v>
-      </c>
       <c r="D10" s="12" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="E10" s="24"/>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>387</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>382</v>
+      </c>
+      <c r="D11" s="12" t="s">
         <v>388</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>389</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>384</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>390</v>
       </c>
       <c r="E11" s="24"/>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B12" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="D12" s="12" t="s">
         <v>391</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>392</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>393</v>
       </c>
       <c r="E12" s="24"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="C13" s="12" t="s">
         <v>394</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="D13" s="12" t="s">
         <v>395</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>396</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>397</v>
       </c>
       <c r="E13" s="24"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E14" s="24"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
+        <v>398</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>399</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>394</v>
+      </c>
+      <c r="D15" s="12" t="s">
         <v>400</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>401</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>396</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>402</v>
       </c>
       <c r="E15" s="24"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D16" s="12"/>
       <c r="E16" s="24"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
+        <v>403</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>404</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>394</v>
+      </c>
+      <c r="D17" s="12" t="s">
         <v>405</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>406</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>396</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>407</v>
       </c>
       <c r="E17" s="24"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
+        <v>406</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>407</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>394</v>
+      </c>
+      <c r="D18" s="12" t="s">
         <v>408</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>409</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>396</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>410</v>
       </c>
       <c r="E18" s="24"/>
     </row>
@@ -8639,146 +8622,146 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
+        <v>411</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>413</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
+        <v>418</v>
+      </c>
+      <c r="B9" s="12" t="s">
         <v>420</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
   </sheetData>
@@ -8806,90 +8789,90 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
   </sheetData>

--- a/docs/itineraries/vaishno-devi-kashmir-8d-plan.xlsx
+++ b/docs/itineraries/vaishno-devi-kashmir-8d-plan.xlsx
@@ -154,7 +154,7 @@
     <t xml:space="preserve">Assumptions: arrival at Jammu Airport at 14:00 on Day 1; breakfast 07:30–08:30 and departure from the hotel at 09:00 every day; helicopter slots 12:15 (Day 2) and 12:15 (Day 3); Jammu Airport by 09:20 on Day 4 for the 11:00–12:00 flight to Srinagar; Srinagar Airport by 12:45 on Day 8 for departures after 14:00. Day 6 is the longest road day (~167 km); back in Srinagar about 18:30.</t>
   </si>
   <si>
-    <t xml:space="preserve">Highlights: Evening &amp; Morning Atka Aarti at the Holy Cave (main temple), arranged for the group so yatris spend more time before Mata Rani; Banganga darshan on Day 3.</t>
+    <t xml:space="preserve">Highlights: Atka Aarti at the Holy Cave, arranged once for the group (evening or morning, as allotted by the Shrine Board), so yatris spend more time before Mata Rani; Banganga darshan on Day 3.</t>
   </si>
   <si>
     <t xml:space="preserve">8 Days Vaishno Devi &amp; Kashmir Pilgrimage – Minute-to-Minute Plan</t>
@@ -340,13 +340,13 @@
     <t xml:space="preserve">Aarti</t>
   </si>
   <si>
-    <t xml:space="preserve">Evening Atka Aarti at the Holy Cave (main temple) – Aarti passes arranged by the organisers so yatris sit before Mata Rani for the full Aarti</t>
+    <t xml:space="preserve">Atka Aarti at the Holy Cave (main temple), arranged once for the group – this evening or tomorrow morning, as allotted by the Shrine Board; otherwise kirtan and japa</t>
   </si>
   <si>
     <t xml:space="preserve">Wake-up, bath, get ready</t>
   </si>
   <si>
-    <t xml:space="preserve">Morning Atka Aarti at the Holy Cave (main temple) – arranged by the organisers; more time before Mata Rani</t>
+    <t xml:space="preserve">Morning Atka Aarti at the Holy Cave if this is our allotted slot; otherwise japa and early darshan</t>
   </si>
   <si>
     <t xml:space="preserve">Rest, pack small bag</t>
@@ -718,7 +718,7 @@
     <t xml:space="preserve">Farewell – Jai Mata Di! Har Har Mahadev! (departure flights after 14:00)</t>
   </si>
   <si>
-    <t xml:space="preserve">Legend: yellow rows = meals; peach rows = highlights (Evening &amp; Morning Atka Aarti, Banganga darshan); blue rows = helicopter, battery car, ropeway, flight, gondola, shikara, Thajiwas pony ride.</t>
+    <t xml:space="preserve">Legend: yellow rows = meals; peach rows = highlights (both possible Atka Aarti slots – the group gets one, as allotted by the Shrine Board; Banganga darshan); blue rows = helicopter, battery car, ropeway, flight, gondola, shikara, Thajiwas pony ride.</t>
   </si>
   <si>
     <t xml:space="preserve">Meal plan (all 22 meals pure-veg)</t>
@@ -835,7 +835,7 @@
     <t xml:space="preserve">Night at Bhawan</t>
   </si>
   <si>
-    <t xml:space="preserve">Evening and Morning Aarti; unhurried darshan</t>
+    <t xml:space="preserve">Atka Aarti at the Holy Cave, arranged once for the group (evening or morning, as allotted by the Shrine Board); unhurried darshan</t>
   </si>
   <si>
     <t xml:space="preserve">Basic shared rooms</t>
@@ -1228,7 +1228,7 @@
     <t xml:space="preserve">Booking opening day</t>
   </si>
   <si>
-    <t xml:space="preserve">Book Atka Aarti passes for the Evening &amp; Morning Atka Aarti at the Holy Cave (main temple)</t>
+    <t xml:space="preserve">Book Atka Aarti passes: Atka Aarti at the Holy Cave, arranged once for the group (evening or morning, as allotted by the Shrine Board)</t>
   </si>
   <si>
     <t xml:space="preserve">Arranged for the group so yatris spend more time before Mata Rani</t>
@@ -1684,7 +1684,7 @@
     <t xml:space="preserve">Battery car Sanjichhat → Bhawan</t>
   </si>
   <si>
-    <t xml:space="preserve">Atka Aarti passes – Evening &amp; Morning Atka Aarti at the Holy Cave, arranged for the group</t>
+    <t xml:space="preserve">Atka Aarti passes – Atka Aarti at the Holy Cave, arranged once for the group (evening or morning, as allotted by the Shrine Board)</t>
   </si>
   <si>
     <t xml:space="preserve">Bhairon ropeway</t>
@@ -1753,7 +1753,7 @@
     <t xml:space="preserve">Helicopter baggage limit; main luggage stays at the Jammu hotel on Day 2</t>
   </si>
   <si>
-    <t xml:space="preserve">Bhawan accommodation, Atka Aarti passes, Bhairon ropeway and Sanjichhat → Bhawan battery car booked</t>
+    <t xml:space="preserve">Bhawan accommodation, Bhairon ropeway and Sanjichhat → Bhawan battery car booked; Atka Aarti slot allotted (Day 2 evening or Day 3 morning)</t>
   </si>
   <si>
     <t xml:space="preserve">Hotels fixed in Jammu (Days 1 and 3) and Srinagar (Days 4, 5, 6 and 7); replace area map links with exact pins</t>
@@ -3393,7 +3393,7 @@
       </c>
       <c r="B5" s="28"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
         <v>572</v>
       </c>
@@ -4386,7 +4386,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="24" t="n">
         <v>2</v>
       </c>
@@ -8094,7 +8094,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
         <v>265</v>
       </c>
